--- a/コスト表.xlsx
+++ b/コスト表.xlsx
@@ -5,21 +5,22 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\genki\Documents\GitHub\koukiteam\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FukudaGenki\Documents\GitHub\koukiteam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60442848-B307-4AE7-B505-BD522AB4B586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFD3126C-E573-4932-86F6-77167A110C7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1020" yWindow="810" windowWidth="26025" windowHeight="14460" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="21060" windowHeight="15585" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1125_元データ" sheetId="4" r:id="rId1"/>
     <sheet name="概要" sheetId="5" r:id="rId2"/>
     <sheet name="作業工数見積もり" sheetId="1" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1125_元データ'!$B$2:$G$106</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">作業工数見積もり!$A$2:$I$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">作業工数見積もり!$A$2:$I$77</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="241">
   <si>
     <t>1コスト:3時間 (1日は基本2コスト)</t>
     <phoneticPr fontId="1"/>
@@ -951,13 +952,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>作業工数</t>
-    <rPh sb="0" eb="4">
-      <t>サギョウコウスウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ステータス</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -979,9 +973,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>全体の作業工数</t>
-  </si>
-  <si>
     <t>作成にかかる時間</t>
   </si>
   <si>
@@ -1218,16 +1209,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>経路探索（まじで余裕あれば）</t>
-    <rPh sb="0" eb="4">
-      <t>ケイロタンサク</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ヨユウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>エネミー（武器なし）</t>
     <rPh sb="5" eb="7">
       <t>ブキ</t>
@@ -1745,6 +1726,84 @@
     <t>廣田</t>
     <rPh sb="0" eb="2">
       <t>ヒロタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>見積コスト</t>
+    <rPh sb="0" eb="2">
+      <t>ミツモリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>全体の見積コスト</t>
+    <rPh sb="3" eb="5">
+      <t>ミツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>福田</t>
+    <rPh sb="0" eb="2">
+      <t>フクダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>久保田</t>
+    <rPh sb="0" eb="3">
+      <t>クボタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>廣田</t>
+    <rPh sb="0" eb="2">
+      <t>ヒロタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>松本</t>
+    <rPh sb="0" eb="2">
+      <t>マツモト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>玉利</t>
+    <rPh sb="0" eb="2">
+      <t>タマリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>月</t>
+    <rPh sb="0" eb="1">
+      <t>ゲツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>火</t>
+  </si>
+  <si>
+    <t>水</t>
+  </si>
+  <si>
+    <t>木</t>
+  </si>
+  <si>
+    <t>金</t>
+  </si>
+  <si>
+    <t>土</t>
+  </si>
+  <si>
+    <t>日</t>
+    <rPh sb="0" eb="1">
+      <t>ニチ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2056,7 +2115,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2129,6 +2188,8 @@
     <xf numFmtId="0" fontId="0" fillId="24" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="25" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -2514,11 +2575,11 @@
       </c>
       <c r="K4" s="2">
         <f ca="1">NETWORKDAYS(K5,K6)</f>
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="L4" s="3">
         <f ca="1" xml:space="preserve"> K3 / K4</f>
-        <v>5.4979253112033194E-2</v>
+        <v>5.4752066115702477E-2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2558,7 +2619,7 @@
       </c>
       <c r="K6" s="1">
         <f ca="1">TODAY()</f>
-        <v>46278</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2623,11 +2684,11 @@
       </c>
       <c r="L9" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K9)</f>
-        <v>-451</v>
+        <v>-453</v>
       </c>
       <c r="M9" s="3">
         <f ca="1">($K$2 - $K$3) / L9</f>
-        <v>-0.2039911308203991</v>
+        <v>-0.20309050772626933</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -2654,11 +2715,11 @@
       </c>
       <c r="L10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K10)</f>
-        <v>-431</v>
+        <v>-433</v>
       </c>
       <c r="M10" s="3">
         <f ca="1">($K$2 - $K$3) / L10</f>
-        <v>-0.21345707656612528</v>
+        <v>-0.21247113163972287</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2685,11 +2746,11 @@
       </c>
       <c r="L11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K11)</f>
-        <v>-420</v>
+        <v>-422</v>
       </c>
       <c r="M11" s="3">
         <f ca="1">($K$2 - $K$3) / L11</f>
-        <v>-0.21904761904761905</v>
+        <v>-0.21800947867298578</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -4217,8 +4278,8 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <f>SUM(作業工数見積もり!F3:F104)</f>
-        <v>31.75</v>
+        <f>SUM(作業工数見積もり!F3:F103)</f>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="2:5">
@@ -4226,7 +4287,7 @@
         <v>10</v>
       </c>
       <c r="C4">
-        <f>SUMIF(作業工数見積もり!H3:H47,"完了",作業工数見積もり!F3:F47)</f>
+        <f>SUMIF(作業工数見積もり!H3:H46,"完了",作業工数見積もり!F3:F46)</f>
         <v>0</v>
       </c>
       <c r="D4" t="s">
@@ -4239,7 +4300,7 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
@@ -4261,7 +4322,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46278</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -4282,11 +4343,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-451</v>
+        <v>-453</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-7.0399113082039916E-2</v>
+        <v>-9.9337748344370855E-2</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -4299,11 +4360,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-431</v>
+        <v>-433</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-7.366589327146171E-2</v>
+        <v>-0.10392609699769054</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -4316,11 +4377,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-420</v>
+        <v>-422</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-7.559523809523809E-2</v>
+        <v>-0.1066350710900474</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -4404,7 +4465,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:M78"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A2:M77"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="32.75" style="21" bestFit="1" customWidth="1"/>
@@ -4436,24 +4498,24 @@
         <v>3</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>131</v>
+        <v>227</v>
       </c>
       <c r="G2" s="27" t="s">
         <v>5</v>
       </c>
       <c r="H2" s="27" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I2" s="26" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="3" spans="2:13">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" hidden="1">
       <c r="B3" s="43" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D3" s="28" t="s">
         <v>9</v>
@@ -4465,45 +4527,49 @@
         <v>0.25</v>
       </c>
       <c r="H3" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="K3" s="34" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L3" s="21">
         <f>SUM(L4,L5,L6)</f>
-        <v>75</v>
-      </c>
-    </row>
-    <row r="4" spans="2:13">
-      <c r="B4" s="43"/>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" hidden="1">
+      <c r="B4" s="43" t="s">
+        <v>137</v>
+      </c>
       <c r="C4" s="21" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D4" s="28" t="s">
         <v>17</v>
       </c>
       <c r="E4" s="28" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F4" s="28">
         <v>0.25</v>
       </c>
       <c r="H4" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="K4" s="35" t="s">
         <v>126</v>
       </c>
       <c r="L4" s="39">
-        <f>COUNTIF(E3:E78,K4)</f>
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="2:13">
-      <c r="B5" s="43"/>
+        <f>COUNTIF(E3:E77,K4)</f>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" hidden="1">
+      <c r="B5" s="43" t="s">
+        <v>137</v>
+      </c>
       <c r="C5" s="21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D5" s="28" t="s">
         <v>9</v>
@@ -4515,22 +4581,22 @@
         <v>0.25</v>
       </c>
       <c r="H5" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="K5" s="36" t="s">
         <v>1</v>
       </c>
       <c r="L5" s="39">
-        <f>COUNTIF(E3:E78,K5)</f>
+        <f>COUNTIF(E3:E77,K5)</f>
         <v>35</v>
       </c>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="44" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D6" s="28" t="s">
         <v>9</v>
@@ -4539,26 +4605,28 @@
         <v>34</v>
       </c>
       <c r="F6" s="28">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H6" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I6" s="21" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="K6" s="37" t="s">
         <v>127</v>
       </c>
       <c r="L6" s="39">
-        <f>COUNTIF(E3:E73,K6)</f>
+        <f>COUNTIF(E3:E77,K6)</f>
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="2:13">
-      <c r="B7" s="44"/>
+      <c r="B7" s="44" t="s">
+        <v>159</v>
+      </c>
       <c r="C7" s="21" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D7" s="28" t="s">
         <v>17</v>
@@ -4566,19 +4634,24 @@
       <c r="E7" s="28" t="s">
         <v>34</v>
       </c>
+      <c r="F7" s="28">
+        <v>1</v>
+      </c>
       <c r="H7" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I7" s="21" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="K7" s="37"/>
       <c r="L7" s="39"/>
     </row>
-    <row r="8" spans="2:13">
-      <c r="B8" s="44"/>
+    <row r="8" spans="2:13" hidden="1">
+      <c r="B8" s="44" t="s">
+        <v>159</v>
+      </c>
       <c r="C8" s="21" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D8" s="28" t="s">
         <v>17</v>
@@ -4590,13 +4663,13 @@
         <v>0.25</v>
       </c>
       <c r="H8" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="K8" s="32" t="s">
         <v>35</v>
       </c>
       <c r="L8" s="39">
-        <f>COUNTIF(H3:H73,K8)</f>
+        <f>COUNTIF(H3:H77,K8)</f>
         <v>0</v>
       </c>
       <c r="M8" s="40">
@@ -4605,9 +4678,11 @@
       </c>
     </row>
     <row r="9" spans="2:13">
-      <c r="B9" s="44"/>
+      <c r="B9" s="44" t="s">
+        <v>159</v>
+      </c>
       <c r="C9" s="21" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D9" s="28" t="s">
         <v>17</v>
@@ -4619,27 +4694,29 @@
         <v>0.5</v>
       </c>
       <c r="H9" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I9" s="21" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="K9" s="33" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L9" s="39">
-        <f>COUNTIF(H3:H73,K9)</f>
-        <v>71</v>
+        <f>COUNTIF(H3:H77,K9)</f>
+        <v>75</v>
       </c>
       <c r="M9" s="31">
         <f>(L9+L10)/L3</f>
-        <v>0.94666666666666666</v>
-      </c>
-    </row>
-    <row r="10" spans="2:13">
-      <c r="B10" s="44"/>
+        <v>1.0135135135135136</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13" hidden="1">
+      <c r="B10" s="44" t="s">
+        <v>159</v>
+      </c>
       <c r="C10" s="21" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D10" s="28" t="s">
         <v>17</v>
@@ -4651,20 +4728,22 @@
         <v>0.5</v>
       </c>
       <c r="H10" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="K10" s="34" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L10" s="21">
-        <f>COUNTIF(H3:H73,K10)</f>
+        <f>COUNTIF(H3:H77,K10)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:13">
-      <c r="B11" s="44"/>
+    <row r="11" spans="2:13" hidden="1">
+      <c r="B11" s="44" t="s">
+        <v>159</v>
+      </c>
       <c r="C11" s="21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" s="28" t="s">
         <v>17</v>
@@ -4676,15 +4755,15 @@
         <v>0.5</v>
       </c>
       <c r="H11" s="28" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="12" spans="2:13">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" hidden="1">
       <c r="B12" s="45" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D12" s="28" t="s">
         <v>9</v>
@@ -4696,23 +4775,25 @@
         <v>1</v>
       </c>
       <c r="H12" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I12" s="21" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="K12" s="41" t="s">
-        <v>136</v>
+        <v>228</v>
       </c>
       <c r="L12" s="21">
-        <f>SUM(F3:F73)</f>
-        <v>31.75</v>
-      </c>
-    </row>
-    <row r="13" spans="2:13">
-      <c r="B13" s="45"/>
+        <f>SUM(F3:F77)</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" hidden="1">
+      <c r="B13" s="45" t="s">
+        <v>141</v>
+      </c>
       <c r="C13" s="21" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D13" s="28" t="s">
         <v>9</v>
@@ -4724,23 +4805,25 @@
         <v>2</v>
       </c>
       <c r="H13" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I13" s="21" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="K13" s="38" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L13" s="21">
-        <f>8*L12</f>
-        <v>254</v>
-      </c>
-    </row>
-    <row r="14" spans="2:13">
-      <c r="B14" s="45"/>
+        <f>1*L12</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" hidden="1">
+      <c r="B14" s="45" t="s">
+        <v>141</v>
+      </c>
       <c r="C14" s="21" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D14" s="28" t="s">
         <v>9</v>
@@ -4749,17 +4832,19 @@
         <v>34</v>
       </c>
       <c r="H14" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I14" s="21" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="J14" s="38"/>
     </row>
-    <row r="15" spans="2:13">
-      <c r="B15" s="45"/>
+    <row r="15" spans="2:13" hidden="1">
+      <c r="B15" s="45" t="s">
+        <v>141</v>
+      </c>
       <c r="C15" s="21" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D15" s="28" t="s">
         <v>9</v>
@@ -4771,17 +4856,26 @@
         <v>3</v>
       </c>
       <c r="H15" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I15" s="21" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="J15" s="38"/>
-    </row>
-    <row r="16" spans="2:13">
-      <c r="B16" s="45"/>
+      <c r="K15" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="L15" s="21">
+        <f>COUNTIF(I3:I77, K15)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13" hidden="1">
+      <c r="B16" s="45" t="s">
+        <v>141</v>
+      </c>
       <c r="C16" s="21" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D16" s="28" t="s">
         <v>9</v>
@@ -4793,13 +4887,22 @@
         <v>0.5</v>
       </c>
       <c r="H16" s="28" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9">
-      <c r="B17" s="45"/>
+        <v>136</v>
+      </c>
+      <c r="K16" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="L16" s="21">
+        <f>COUNTIF(I3:I77, K16)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" hidden="1">
+      <c r="B17" s="45" t="s">
+        <v>141</v>
+      </c>
       <c r="C17" s="21" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D17" s="28" t="s">
         <v>9</v>
@@ -4811,13 +4914,22 @@
         <v>1.5</v>
       </c>
       <c r="H17" s="28" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9">
-      <c r="B18" s="45"/>
+        <v>136</v>
+      </c>
+      <c r="K17" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="L17" s="21">
+        <f>COUNTIF(I3:I77, K17)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" hidden="1">
+      <c r="B18" s="45" t="s">
+        <v>141</v>
+      </c>
       <c r="C18" s="21" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D18" s="28" t="s">
         <v>9</v>
@@ -4829,13 +4941,22 @@
         <v>2.5</v>
       </c>
       <c r="H18" s="28" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9">
-      <c r="B19" s="45"/>
+        <v>136</v>
+      </c>
+      <c r="K18" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="L18" s="21">
+        <f>COUNTIF(I3:I77, K18)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" hidden="1">
+      <c r="B19" s="45" t="s">
+        <v>141</v>
+      </c>
       <c r="C19" s="21" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D19" s="28" t="s">
         <v>9</v>
@@ -4844,16 +4965,25 @@
         <v>34</v>
       </c>
       <c r="H19" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I19" s="21" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9">
-      <c r="B20" s="45"/>
+        <v>215</v>
+      </c>
+      <c r="K19" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="L19" s="21">
+        <f>COUNTIF(I3:I77, K19)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" hidden="1">
+      <c r="B20" s="45" t="s">
+        <v>141</v>
+      </c>
       <c r="C20" s="21" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D20" s="28" t="s">
         <v>9</v>
@@ -4865,13 +4995,15 @@
         <v>3.5</v>
       </c>
       <c r="H20" s="28" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9">
-      <c r="B21" s="45"/>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" hidden="1">
+      <c r="B21" s="45" t="s">
+        <v>141</v>
+      </c>
       <c r="C21" s="21" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D21" s="28" t="s">
         <v>9</v>
@@ -4883,16 +5015,18 @@
         <v>2.5</v>
       </c>
       <c r="H21" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I21" s="21" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9">
-      <c r="B22" s="45"/>
+        <v>215</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" hidden="1">
+      <c r="B22" s="45" t="s">
+        <v>141</v>
+      </c>
       <c r="C22" s="21" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D22" s="28" t="s">
         <v>9</v>
@@ -4904,16 +5038,18 @@
         <v>3.5</v>
       </c>
       <c r="H22" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I22" s="21" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9">
-      <c r="B23" s="45"/>
+        <v>215</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" hidden="1">
+      <c r="B23" s="45" t="s">
+        <v>141</v>
+      </c>
       <c r="C23" s="21" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D23" s="28" t="s">
         <v>17</v>
@@ -4925,13 +5061,15 @@
         <v>1</v>
       </c>
       <c r="H23" s="28" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9">
-      <c r="B24" s="45"/>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" hidden="1">
+      <c r="B24" s="45" t="s">
+        <v>141</v>
+      </c>
       <c r="C24" s="21" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D24" s="28" t="s">
         <v>17</v>
@@ -4943,16 +5081,18 @@
         <v>0.5</v>
       </c>
       <c r="H24" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I24" s="21" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9">
-      <c r="B25" s="45"/>
+        <v>215</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" hidden="1">
+      <c r="B25" s="45" t="s">
+        <v>141</v>
+      </c>
       <c r="C25" s="21" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D25" s="28" t="s">
         <v>17</v>
@@ -4964,13 +5104,15 @@
         <v>0.5</v>
       </c>
       <c r="H25" s="28" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="26" spans="2:9">
-      <c r="B26" s="45"/>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" hidden="1">
+      <c r="B26" s="45" t="s">
+        <v>141</v>
+      </c>
       <c r="C26" s="21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D26" s="28" t="s">
         <v>9</v>
@@ -4982,37 +5124,39 @@
         <v>0.5</v>
       </c>
       <c r="H26" s="28" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="27" spans="2:9">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12">
       <c r="B27" s="46" t="s">
+        <v>152</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="D27" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F27" s="28">
+        <v>1</v>
+      </c>
+      <c r="H27" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="I27" s="21" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12">
+      <c r="B28" s="46" t="s">
+        <v>152</v>
+      </c>
+      <c r="C28" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="C27" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="D27" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E27" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="F27" s="28">
-        <v>0.5</v>
-      </c>
-      <c r="H27" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="I27" s="21" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9">
-      <c r="B28" s="46"/>
-      <c r="C28" s="21" t="s">
-        <v>156</v>
-      </c>
       <c r="D28" s="28" t="s">
         <v>9</v>
       </c>
@@ -5020,19 +5164,21 @@
         <v>34</v>
       </c>
       <c r="F28" s="28">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H28" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I28" s="21" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="29" spans="2:9">
-      <c r="B29" s="46"/>
+        <v>214</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12">
+      <c r="B29" s="46" t="s">
+        <v>152</v>
+      </c>
       <c r="C29" s="21" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D29" s="28" t="s">
         <v>9</v>
@@ -5044,16 +5190,18 @@
         <v>1</v>
       </c>
       <c r="H29" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I29" s="21" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9">
-      <c r="B30" s="46"/>
+        <v>214</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12">
+      <c r="B30" s="46" t="s">
+        <v>152</v>
+      </c>
       <c r="C30" s="21" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D30" s="28" t="s">
         <v>9</v>
@@ -5062,19 +5210,21 @@
         <v>34</v>
       </c>
       <c r="F30" s="28">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="H30" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I30" s="21" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9">
-      <c r="B31" s="46"/>
+        <v>214</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12">
+      <c r="B31" s="46" t="s">
+        <v>152</v>
+      </c>
       <c r="C31" s="21" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D31" s="28" t="s">
         <v>17</v>
@@ -5086,16 +5236,18 @@
         <v>0.5</v>
       </c>
       <c r="H31" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I31" s="21" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="32" spans="2:9">
-      <c r="B32" s="46"/>
+        <v>214</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" hidden="1">
+      <c r="B32" s="46" t="s">
+        <v>152</v>
+      </c>
       <c r="C32" s="21" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D32" s="28" t="s">
         <v>17</v>
@@ -5107,13 +5259,15 @@
         <v>0.5</v>
       </c>
       <c r="H32" s="28" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="33" spans="2:9">
-      <c r="B33" s="46"/>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" hidden="1">
+      <c r="B33" s="46" t="s">
+        <v>152</v>
+      </c>
       <c r="C33" s="21" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D33" s="28" t="s">
         <v>9</v>
@@ -5125,13 +5279,15 @@
         <v>0.5</v>
       </c>
       <c r="H33" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34" spans="2:9">
-      <c r="B34" s="46"/>
+      <c r="B34" s="46" t="s">
+        <v>152</v>
+      </c>
       <c r="C34" s="21" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D34" s="28" t="s">
         <v>9</v>
@@ -5143,16 +5299,18 @@
         <v>0.5</v>
       </c>
       <c r="H34" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I34" s="21" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="35" spans="2:9">
-      <c r="B35" s="46"/>
+        <v>214</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" hidden="1">
+      <c r="B35" s="46" t="s">
+        <v>152</v>
+      </c>
       <c r="C35" s="21" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D35" s="28" t="s">
         <v>17</v>
@@ -5161,57 +5319,60 @@
         <v>18</v>
       </c>
       <c r="H35" s="28" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="36" spans="2:9">
-      <c r="B36" s="46"/>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" hidden="1">
+      <c r="B36" s="46" t="s">
+        <v>152</v>
+      </c>
       <c r="C36" s="21" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="D36" s="28" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="E36" s="28" t="s">
         <v>34</v>
       </c>
+      <c r="F36" s="28">
+        <v>0.5</v>
+      </c>
       <c r="H36" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I36" s="21" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="37" spans="2:9">
-      <c r="B37" s="46"/>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" hidden="1">
+      <c r="B37" s="47" t="s">
+        <v>165</v>
+      </c>
       <c r="C37" s="21" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="D37" s="28" t="s">
         <v>9</v>
       </c>
       <c r="E37" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="F37" s="28">
-        <v>0.5</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="F37" s="21"/>
+      <c r="G37" s="21"/>
       <c r="H37" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="I37" s="21" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="38" spans="2:9">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" hidden="1">
       <c r="B38" s="47" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C38" s="21" t="s">
         <v>169</v>
       </c>
       <c r="D38" s="28" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E38" s="28" t="s">
         <v>18</v>
@@ -5219,16 +5380,18 @@
       <c r="F38" s="21"/>
       <c r="G38" s="21"/>
       <c r="H38" s="28" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="39" spans="2:9">
-      <c r="B39" s="47"/>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" hidden="1">
+      <c r="B39" s="47" t="s">
+        <v>165</v>
+      </c>
       <c r="C39" s="21" t="s">
-        <v>172</v>
+        <v>145</v>
       </c>
       <c r="D39" s="28" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E39" s="28" t="s">
         <v>18</v>
@@ -5236,16 +5399,18 @@
       <c r="F39" s="21"/>
       <c r="G39" s="21"/>
       <c r="H39" s="28" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="40" spans="2:9">
-      <c r="B40" s="47"/>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" hidden="1">
+      <c r="B40" s="47" t="s">
+        <v>165</v>
+      </c>
       <c r="C40" s="21" t="s">
-        <v>147</v>
+        <v>179</v>
       </c>
       <c r="D40" s="28" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E40" s="28" t="s">
         <v>18</v>
@@ -5253,220 +5418,250 @@
       <c r="F40" s="21"/>
       <c r="G40" s="21"/>
       <c r="H40" s="28" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="41" spans="2:9">
-      <c r="B41" s="47"/>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" hidden="1">
+      <c r="B41" s="47" t="s">
+        <v>165</v>
+      </c>
       <c r="C41" s="21" t="s">
-        <v>182</v>
+        <v>156</v>
       </c>
       <c r="D41" s="28" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E41" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F41" s="21"/>
-      <c r="G41" s="21"/>
       <c r="H41" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="42" spans="2:9">
-      <c r="B42" s="47"/>
+      <c r="B42" s="48" t="s">
+        <v>167</v>
+      </c>
       <c r="C42" s="21" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="D42" s="28" t="s">
         <v>9</v>
       </c>
       <c r="E42" s="28" t="s">
-        <v>18</v>
+        <v>34</v>
+      </c>
+      <c r="F42" s="28">
+        <v>2</v>
       </c>
       <c r="H42" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
+      </c>
+      <c r="I42" s="21" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="43" spans="2:9">
       <c r="B43" s="48" t="s">
+        <v>167</v>
+      </c>
+      <c r="C43" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="C43" s="21" t="s">
+      <c r="D43" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E43" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F43" s="28">
+        <v>2</v>
+      </c>
+      <c r="H43" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="I43" s="21" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9">
+      <c r="B44" s="48" t="s">
+        <v>167</v>
+      </c>
+      <c r="C44" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="D44" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F44" s="28">
+        <v>2</v>
+      </c>
+      <c r="H44" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="I44" s="21" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9">
+      <c r="B45" s="48" t="s">
+        <v>167</v>
+      </c>
+      <c r="C45" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="D45" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E45" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F45" s="28">
+        <v>1</v>
+      </c>
+      <c r="H45" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="I45" s="21" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9">
+      <c r="B46" s="48" t="s">
+        <v>167</v>
+      </c>
+      <c r="C46" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="D46" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E46" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F46" s="28">
+        <v>2</v>
+      </c>
+      <c r="H46" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="I46" s="21" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9">
+      <c r="B47" s="48" t="s">
+        <v>167</v>
+      </c>
+      <c r="C47" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="D43" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E43" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="F43" s="28">
-        <v>0.5</v>
-      </c>
-      <c r="H43" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="I43" s="21" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="44" spans="2:9">
-      <c r="B44" s="48"/>
-      <c r="C44" s="21" t="s">
-        <v>173</v>
-      </c>
-      <c r="D44" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E44" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="F44" s="28">
-        <v>0.5</v>
-      </c>
-      <c r="H44" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="I44" s="21" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="45" spans="2:9">
-      <c r="B45" s="48"/>
-      <c r="C45" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="D45" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E45" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="F45" s="28">
-        <v>0.5</v>
-      </c>
-      <c r="H45" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="I45" s="21" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="46" spans="2:9">
-      <c r="B46" s="48"/>
-      <c r="C46" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="D46" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E46" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="H46" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="I46" s="21" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="47" spans="2:9">
-      <c r="B47" s="48"/>
-      <c r="C47" s="21" t="s">
+      <c r="D47" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E47" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F47" s="28">
+        <v>1</v>
+      </c>
+      <c r="H47" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="I47" s="21" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9" hidden="1">
+      <c r="B48" s="48" t="s">
+        <v>167</v>
+      </c>
+      <c r="C48" s="21" t="s">
         <v>178</v>
       </c>
-      <c r="D47" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E47" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="H47" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="I47" s="21" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="48" spans="2:9">
-      <c r="B48" s="48"/>
-      <c r="C48" s="21" t="s">
-        <v>174</v>
-      </c>
       <c r="D48" s="28" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E48" s="28" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="H48" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="I48" s="21" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9">
-      <c r="B49" s="48"/>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" hidden="1">
+      <c r="B49" s="48" t="s">
+        <v>167</v>
+      </c>
       <c r="C49" s="21" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="D49" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E49" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="H49" s="28" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" hidden="1">
+      <c r="A50" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="B50" s="49" t="s">
+        <v>204</v>
+      </c>
+      <c r="C50" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="D50" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="E49" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="H49" s="28" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9">
-      <c r="B50" s="48"/>
-      <c r="C50" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="D50" s="28" t="s">
-        <v>9</v>
-      </c>
       <c r="E50" s="28" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="H50" s="28" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9">
+        <v>136</v>
+      </c>
+      <c r="I50" s="21" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" hidden="1">
       <c r="A51" s="21" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="B51" s="49" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C51" s="21" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D51" s="28" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E51" s="28" t="s">
         <v>34</v>
       </c>
       <c r="H51" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I51" s="21" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9">
-      <c r="A52" s="21" t="s">
         <v>216</v>
       </c>
-      <c r="B52" s="49"/>
+    </row>
+    <row r="52" spans="1:9" hidden="1">
+      <c r="B52" s="50" t="s">
+        <v>188</v>
+      </c>
       <c r="C52" s="21" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="D52" s="28" t="s">
         <v>9</v>
@@ -5475,36 +5670,41 @@
         <v>34</v>
       </c>
       <c r="H52" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I52" s="21" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="53" spans="1:9">
       <c r="B53" s="50" t="s">
+        <v>188</v>
+      </c>
+      <c r="C53" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="C53" s="21" t="s">
-        <v>192</v>
-      </c>
       <c r="D53" s="28" t="s">
         <v>9</v>
       </c>
       <c r="E53" s="28" t="s">
         <v>34</v>
       </c>
+      <c r="F53" s="28">
+        <v>2</v>
+      </c>
       <c r="H53" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I53" s="21" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9">
-      <c r="B54" s="50"/>
+        <v>224</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" hidden="1">
+      <c r="B54" s="50" t="s">
+        <v>188</v>
+      </c>
       <c r="C54" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D54" s="28" t="s">
         <v>9</v>
@@ -5513,16 +5713,18 @@
         <v>34</v>
       </c>
       <c r="H54" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I54" s="21" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9">
-      <c r="B55" s="50"/>
+        <v>222</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" hidden="1">
+      <c r="B55" s="50" t="s">
+        <v>188</v>
+      </c>
       <c r="C55" s="21" t="s">
-        <v>193</v>
+        <v>223</v>
       </c>
       <c r="D55" s="28" t="s">
         <v>9</v>
@@ -5531,36 +5733,38 @@
         <v>34</v>
       </c>
       <c r="H55" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I55" s="21" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9">
-      <c r="B56" s="50"/>
+        <v>222</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" hidden="1">
+      <c r="B56" s="29" t="s">
+        <v>181</v>
+      </c>
       <c r="C56" s="21" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
       <c r="D56" s="28" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E56" s="28" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="H56" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I56" s="21" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" hidden="1">
       <c r="B57" s="29" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C57" s="21" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D57" s="28" t="s">
         <v>25</v>
@@ -5569,16 +5773,18 @@
         <v>18</v>
       </c>
       <c r="H57" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I57" s="21" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9">
-      <c r="B58" s="29"/>
+        <v>222</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" hidden="1">
+      <c r="B58" s="29" t="s">
+        <v>181</v>
+      </c>
       <c r="C58" s="21" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="D58" s="28" t="s">
         <v>25</v>
@@ -5587,52 +5793,58 @@
         <v>18</v>
       </c>
       <c r="H58" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I58" s="21" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9">
-      <c r="B59" s="29"/>
+        <v>222</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" hidden="1">
+      <c r="B59" s="29" t="s">
+        <v>181</v>
+      </c>
       <c r="C59" s="21" t="s">
-        <v>201</v>
+        <v>182</v>
       </c>
       <c r="D59" s="28" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="E59" s="28" t="s">
         <v>18</v>
       </c>
       <c r="H59" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I59" s="21" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
-      <c r="B60" s="29"/>
+    <row r="60" spans="1:9" hidden="1">
+      <c r="B60" s="29" t="s">
+        <v>181</v>
+      </c>
       <c r="C60" s="21" t="s">
-        <v>185</v>
+        <v>219</v>
       </c>
       <c r="D60" s="28" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="E60" s="28" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="H60" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I60" s="21" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9">
-      <c r="B61" s="29"/>
+        <v>222</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" hidden="1">
+      <c r="B61" s="29" t="s">
+        <v>181</v>
+      </c>
       <c r="C61" s="21" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D61" s="28" t="s">
         <v>25</v>
@@ -5641,204 +5853,221 @@
         <v>34</v>
       </c>
       <c r="H61" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I61" s="21" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9">
-      <c r="B62" s="29"/>
+        <v>222</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" hidden="1">
+      <c r="B62" s="43" t="s">
+        <v>186</v>
+      </c>
       <c r="C62" s="21" t="s">
-        <v>223</v>
+        <v>183</v>
       </c>
       <c r="D62" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E62" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="H62" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="I62" s="21" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" hidden="1">
+      <c r="B63" s="43" t="s">
+        <v>186</v>
+      </c>
+      <c r="C63" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="D63" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E63" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="H63" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="I63" s="21" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" hidden="1">
+      <c r="B64" s="43" t="s">
+        <v>186</v>
+      </c>
+      <c r="C64" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="D64" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E64" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="H64" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="I64" s="21" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="65" spans="2:9" hidden="1">
+      <c r="B65" s="43" t="s">
+        <v>186</v>
+      </c>
+      <c r="C65" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="D65" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="H65" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="I65" s="21" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="66" spans="2:9" hidden="1">
+      <c r="B66" s="43" t="s">
+        <v>186</v>
+      </c>
+      <c r="C66" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="D66" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E66" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="H66" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="I66" s="21" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="67" spans="2:9" hidden="1">
+      <c r="B67" s="43" t="s">
+        <v>186</v>
+      </c>
+      <c r="C67" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="D67" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E67" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="H67" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="I67" s="21" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="68" spans="2:9" hidden="1">
+      <c r="B68" s="43" t="s">
+        <v>186</v>
+      </c>
+      <c r="C68" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="D68" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="E62" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="H62" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="I62" s="21" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9">
-      <c r="B63" s="43" t="s">
-        <v>189</v>
-      </c>
-      <c r="C63" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="D63" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E63" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="H63" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="I63" s="21" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9">
-      <c r="B64" s="43"/>
-      <c r="C64" s="25" t="s">
-        <v>187</v>
-      </c>
-      <c r="D64" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="E64" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="H64" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="I64" s="21" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="65" spans="2:9">
-      <c r="B65" s="43"/>
-      <c r="C65" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="D65" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E65" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="H65" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="I65" s="21" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="66" spans="2:9">
-      <c r="B66" s="43"/>
-      <c r="C66" s="21" t="s">
-        <v>220</v>
-      </c>
-      <c r="D66" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="H66" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="I66" s="21" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="67" spans="2:9">
-      <c r="B67" s="43"/>
-      <c r="C67" s="21" t="s">
+      <c r="E68" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="H68" s="28" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="69" spans="2:9" hidden="1">
+      <c r="B69" s="44" t="s">
         <v>195</v>
       </c>
-      <c r="D67" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="E67" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="H67" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="I67" s="21" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="68" spans="2:9">
-      <c r="B68" s="43"/>
-      <c r="C68" s="21" t="s">
+      <c r="C69" s="21" t="s">
         <v>196</v>
       </c>
-      <c r="D68" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E68" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="H68" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="I68" s="21" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="69" spans="2:9">
-      <c r="B69" s="43"/>
-      <c r="C69" s="21" t="s">
+      <c r="D69" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E69" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="H69" s="28" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="70" spans="2:9" hidden="1">
+      <c r="B70" s="44" t="s">
+        <v>195</v>
+      </c>
+      <c r="C70" s="21" t="s">
         <v>197</v>
       </c>
-      <c r="D69" s="28" t="s">
+      <c r="D70" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E70" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="H70" s="28" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="71" spans="2:9" hidden="1">
+      <c r="B71" s="44" t="s">
+        <v>195</v>
+      </c>
+      <c r="C71" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="D71" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="E69" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="H69" s="28" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="70" spans="2:9">
-      <c r="B70" s="44" t="s">
-        <v>198</v>
-      </c>
-      <c r="C70" s="21" t="s">
+      <c r="E71" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="H71" s="28" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="72" spans="2:9" hidden="1">
+      <c r="B72" s="44" t="s">
+        <v>195</v>
+      </c>
+      <c r="C72" s="42" t="s">
+        <v>161</v>
+      </c>
+      <c r="D72" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E72" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="H72" s="28" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="73" spans="2:9" hidden="1">
+      <c r="B73" s="51" t="s">
         <v>199</v>
       </c>
-      <c r="D70" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E70" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="H70" s="28" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="71" spans="2:9">
-      <c r="B71" s="44"/>
-      <c r="C71" s="21" t="s">
+      <c r="C73" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="D71" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E71" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="H71" s="28" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="72" spans="2:9">
-      <c r="B72" s="44"/>
-      <c r="C72" s="21" t="s">
-        <v>214</v>
-      </c>
-      <c r="D72" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="E72" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="H72" s="28" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="73" spans="2:9">
-      <c r="B73" s="44"/>
-      <c r="C73" s="42" t="s">
-        <v>163</v>
-      </c>
       <c r="D73" s="28" t="s">
         <v>9</v>
       </c>
@@ -5846,15 +6075,15 @@
         <v>18</v>
       </c>
       <c r="H73" s="28" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="74" spans="2:9">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="74" spans="2:9" hidden="1">
       <c r="B74" s="51" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C74" s="21" t="s">
-        <v>203</v>
+        <v>156</v>
       </c>
       <c r="D74" s="28" t="s">
         <v>9</v>
@@ -5862,14 +6091,18 @@
       <c r="E74" s="28" t="s">
         <v>18</v>
       </c>
+      <c r="F74" s="21"/>
+      <c r="G74" s="21"/>
       <c r="H74" s="28" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="75" spans="2:9">
-      <c r="B75" s="51"/>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="75" spans="2:9" hidden="1">
+      <c r="B75" s="51" t="s">
+        <v>199</v>
+      </c>
       <c r="C75" s="21" t="s">
-        <v>158</v>
+        <v>201</v>
       </c>
       <c r="D75" s="28" t="s">
         <v>9</v>
@@ -5880,13 +6113,15 @@
       <c r="F75" s="21"/>
       <c r="G75" s="21"/>
       <c r="H75" s="28" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="76" spans="2:9">
-      <c r="B76" s="51"/>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="76" spans="2:9" hidden="1">
+      <c r="B76" s="51" t="s">
+        <v>199</v>
+      </c>
       <c r="C76" s="21" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D76" s="28" t="s">
         <v>9</v>
@@ -5897,13 +6132,15 @@
       <c r="F76" s="21"/>
       <c r="G76" s="21"/>
       <c r="H76" s="28" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="77" spans="2:9">
-      <c r="B77" s="51"/>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="77" spans="2:9" hidden="1">
+      <c r="B77" s="51" t="s">
+        <v>199</v>
+      </c>
       <c r="C77" s="21" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D77" s="28" t="s">
         <v>9</v>
@@ -5911,38 +6148,27 @@
       <c r="E77" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F77" s="21"/>
-      <c r="G77" s="21"/>
       <c r="H77" s="28" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="78" spans="2:9">
-      <c r="B78" s="51"/>
-      <c r="C78" s="21" t="s">
-        <v>206</v>
-      </c>
-      <c r="D78" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E78" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="H78" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:I78" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:I77" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="8">
+      <filters>
+        <filter val="福田"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H78" xr:uid="{E1CFE88F-4F87-4696-BE21-1133C2AEB8C1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H77" xr:uid="{E1CFE88F-4F87-4696-BE21-1133C2AEB8C1}">
       <formula1>"未着手,作業中,完了"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D78" xr:uid="{AF10AFEC-2E3A-4CB7-ABD8-6255C47E78C2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D77" xr:uid="{AF10AFEC-2E3A-4CB7-ABD8-6255C47E78C2}">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E78" xr:uid="{8982FD40-CA4D-4B92-93FE-B37B6B67ACD6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E77" xr:uid="{8982FD40-CA4D-4B92-93FE-B37B6B67ACD6}">
       <formula1>"プロト,アルファ,ベータ,マスタ"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5951,7 +6177,224 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402AEDD2-674B-437A-B1BD-39BBE1464A75}">
+  <dimension ref="B2:H10"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="2" spans="2:8">
+      <c r="B2" s="52" t="s">
+        <v>240</v>
+      </c>
+      <c r="C2" s="52" t="s">
+        <v>234</v>
+      </c>
+      <c r="D2" s="52" t="s">
+        <v>235</v>
+      </c>
+      <c r="E2" s="52" t="s">
+        <v>236</v>
+      </c>
+      <c r="F2" s="52" t="s">
+        <v>237</v>
+      </c>
+      <c r="G2" s="52" t="s">
+        <v>238</v>
+      </c>
+      <c r="H2" s="52" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8">
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8">
+      <c r="B4">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+      <c r="D4">
+        <v>8</v>
+      </c>
+      <c r="E4">
+        <v>9</v>
+      </c>
+      <c r="F4">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>11</v>
+      </c>
+      <c r="H4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8">
+      <c r="B5">
+        <v>13</v>
+      </c>
+      <c r="C5">
+        <v>14</v>
+      </c>
+      <c r="D5" s="53">
+        <v>15</v>
+      </c>
+      <c r="E5" s="53">
+        <v>16</v>
+      </c>
+      <c r="F5" s="53">
+        <v>17</v>
+      </c>
+      <c r="G5" s="53">
+        <v>18</v>
+      </c>
+      <c r="H5" s="53">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8">
+      <c r="B6">
+        <v>20</v>
+      </c>
+      <c r="C6">
+        <v>21</v>
+      </c>
+      <c r="D6">
+        <v>22</v>
+      </c>
+      <c r="E6">
+        <v>23</v>
+      </c>
+      <c r="F6">
+        <v>24</v>
+      </c>
+      <c r="G6">
+        <v>25</v>
+      </c>
+      <c r="H6">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8">
+      <c r="B7">
+        <v>27</v>
+      </c>
+      <c r="C7">
+        <v>28</v>
+      </c>
+      <c r="D7">
+        <v>29</v>
+      </c>
+      <c r="E7">
+        <v>30</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8">
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+      <c r="D8">
+        <v>6</v>
+      </c>
+      <c r="E8">
+        <v>7</v>
+      </c>
+      <c r="F8">
+        <v>8</v>
+      </c>
+      <c r="G8">
+        <v>9</v>
+      </c>
+      <c r="H8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8">
+      <c r="B9">
+        <v>11</v>
+      </c>
+      <c r="C9">
+        <v>12</v>
+      </c>
+      <c r="D9">
+        <v>13</v>
+      </c>
+      <c r="E9">
+        <v>14</v>
+      </c>
+      <c r="F9">
+        <v>15</v>
+      </c>
+      <c r="G9">
+        <v>16</v>
+      </c>
+      <c r="H9">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8">
+      <c r="B10">
+        <v>18</v>
+      </c>
+      <c r="C10">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -6186,27 +6629,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0A0972-5393-459A-8603-138D87B70161}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6223,23 +6665,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/コスト表.xlsx
+++ b/コスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FukudaGenki\Documents\GitHub\koukiteam\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kubotananato\Documents\GitHub\koukiteam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFD3126C-E573-4932-86F6-77167A110C7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{674FBE65-82F1-4C91-84F3-4C938CB9AA3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="21060" windowHeight="15585" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1125_元データ" sheetId="4" r:id="rId1"/>
@@ -1813,20 +1813,20 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="177" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1835,14 +1835,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1850,7 +1850,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1858,7 +1858,7 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1866,7 +1866,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1874,7 +1874,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2117,9 +2117,9 @@
   </cellStyleXfs>
   <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2158,7 +2158,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="56" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="12" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2486,18 +2486,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1662411A-9E28-47BA-80A0-FB5B8EEC7CF8}">
   <dimension ref="A1:M106"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.75" style="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.25" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.625" customWidth="1"/>
-    <col min="9" max="9" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.5703125" customWidth="1"/>
+    <col min="9" max="9" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="33" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4265,12 +4265,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{224174C6-79B8-40DF-BFBC-1FA41083861E}">
   <dimension ref="B3:E27"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="33" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:5">
@@ -4465,21 +4465,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A2:M77"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32.75" style="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.875" style="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.125" style="21" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="28" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.25" style="28" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.5" style="28" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.25" style="28" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.140625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" style="28" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" style="28" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.42578125" style="28" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" style="28" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="21"/>
-    <col min="10" max="10" width="15.625" style="21" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" style="21" customWidth="1"/>
     <col min="11" max="11" width="33" style="21" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.25" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.28515625" style="21" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="19" style="21" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="21"/>
   </cols>
@@ -4510,7 +4509,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="3" spans="2:13" hidden="1">
+    <row r="3" spans="2:13">
       <c r="B3" s="43" t="s">
         <v>137</v>
       </c>
@@ -4537,7 +4536,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="2:13" hidden="1">
+    <row r="4" spans="2:13">
       <c r="B4" s="43" t="s">
         <v>137</v>
       </c>
@@ -4564,7 +4563,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="2:13" hidden="1">
+    <row r="5" spans="2:13">
       <c r="B5" s="43" t="s">
         <v>137</v>
       </c>
@@ -4646,7 +4645,7 @@
       <c r="K7" s="37"/>
       <c r="L7" s="39"/>
     </row>
-    <row r="8" spans="2:13" hidden="1">
+    <row r="8" spans="2:13">
       <c r="B8" s="44" t="s">
         <v>159</v>
       </c>
@@ -4711,7 +4710,7 @@
         <v>1.0135135135135136</v>
       </c>
     </row>
-    <row r="10" spans="2:13" hidden="1">
+    <row r="10" spans="2:13">
       <c r="B10" s="44" t="s">
         <v>159</v>
       </c>
@@ -4738,7 +4737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:13" hidden="1">
+    <row r="11" spans="2:13">
       <c r="B11" s="44" t="s">
         <v>159</v>
       </c>
@@ -4758,7 +4757,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="12" spans="2:13" hidden="1">
+    <row r="12" spans="2:13">
       <c r="B12" s="45" t="s">
         <v>141</v>
       </c>
@@ -4788,7 +4787,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="2:13" hidden="1">
+    <row r="13" spans="2:13">
       <c r="B13" s="45" t="s">
         <v>141</v>
       </c>
@@ -4802,7 +4801,7 @@
         <v>34</v>
       </c>
       <c r="F13" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" s="28" t="s">
         <v>136</v>
@@ -4818,7 +4817,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="2:13" hidden="1">
+    <row r="14" spans="2:13">
       <c r="B14" s="45" t="s">
         <v>141</v>
       </c>
@@ -4831,6 +4830,9 @@
       <c r="E14" s="28" t="s">
         <v>34</v>
       </c>
+      <c r="F14" s="28">
+        <v>2</v>
+      </c>
       <c r="H14" s="28" t="s">
         <v>136</v>
       </c>
@@ -4839,7 +4841,7 @@
       </c>
       <c r="J14" s="38"/>
     </row>
-    <row r="15" spans="2:13" hidden="1">
+    <row r="15" spans="2:13">
       <c r="B15" s="45" t="s">
         <v>141</v>
       </c>
@@ -4853,7 +4855,7 @@
         <v>34</v>
       </c>
       <c r="F15" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H15" s="28" t="s">
         <v>136</v>
@@ -4870,7 +4872,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="2:13" hidden="1">
+    <row r="16" spans="2:13">
       <c r="B16" s="45" t="s">
         <v>141</v>
       </c>
@@ -4897,7 +4899,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="2:12" hidden="1">
+    <row r="17" spans="2:12">
       <c r="B17" s="45" t="s">
         <v>141</v>
       </c>
@@ -4924,7 +4926,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="2:12" hidden="1">
+    <row r="18" spans="2:12">
       <c r="B18" s="45" t="s">
         <v>141</v>
       </c>
@@ -4951,7 +4953,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="2:12" hidden="1">
+    <row r="19" spans="2:12">
       <c r="B19" s="45" t="s">
         <v>141</v>
       </c>
@@ -4963,6 +4965,9 @@
       </c>
       <c r="E19" s="28" t="s">
         <v>34</v>
+      </c>
+      <c r="F19" s="28">
+        <v>2</v>
       </c>
       <c r="H19" s="28" t="s">
         <v>136</v>
@@ -4978,7 +4983,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="2:12" hidden="1">
+    <row r="20" spans="2:12">
       <c r="B20" s="45" t="s">
         <v>141</v>
       </c>
@@ -4998,7 +5003,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="21" spans="2:12" hidden="1">
+    <row r="21" spans="2:12">
       <c r="B21" s="45" t="s">
         <v>141</v>
       </c>
@@ -5021,7 +5026,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="22" spans="2:12" hidden="1">
+    <row r="22" spans="2:12">
       <c r="B22" s="45" t="s">
         <v>141</v>
       </c>
@@ -5035,7 +5040,7 @@
         <v>34</v>
       </c>
       <c r="F22" s="28">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="H22" s="28" t="s">
         <v>136</v>
@@ -5044,7 +5049,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="23" spans="2:12" hidden="1">
+    <row r="23" spans="2:12">
       <c r="B23" s="45" t="s">
         <v>141</v>
       </c>
@@ -5064,7 +5069,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="24" spans="2:12" hidden="1">
+    <row r="24" spans="2:12">
       <c r="B24" s="45" t="s">
         <v>141</v>
       </c>
@@ -5078,7 +5083,7 @@
         <v>34</v>
       </c>
       <c r="F24" s="28">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H24" s="28" t="s">
         <v>136</v>
@@ -5087,7 +5092,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="25" spans="2:12" hidden="1">
+    <row r="25" spans="2:12">
       <c r="B25" s="45" t="s">
         <v>141</v>
       </c>
@@ -5107,7 +5112,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="26" spans="2:12" hidden="1">
+    <row r="26" spans="2:12">
       <c r="B26" s="45" t="s">
         <v>141</v>
       </c>
@@ -5242,7 +5247,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="32" spans="2:12" hidden="1">
+    <row r="32" spans="2:12">
       <c r="B32" s="46" t="s">
         <v>152</v>
       </c>
@@ -5262,7 +5267,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="33" spans="2:9" hidden="1">
+    <row r="33" spans="2:9">
       <c r="B33" s="46" t="s">
         <v>152</v>
       </c>
@@ -5305,7 +5310,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="35" spans="2:9" hidden="1">
+    <row r="35" spans="2:9">
       <c r="B35" s="46" t="s">
         <v>152</v>
       </c>
@@ -5322,7 +5327,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="36" spans="2:9" hidden="1">
+    <row r="36" spans="2:9">
       <c r="B36" s="46" t="s">
         <v>152</v>
       </c>
@@ -5345,7 +5350,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="37" spans="2:9" hidden="1">
+    <row r="37" spans="2:9">
       <c r="B37" s="47" t="s">
         <v>165</v>
       </c>
@@ -5364,7 +5369,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="38" spans="2:9" hidden="1">
+    <row r="38" spans="2:9">
       <c r="B38" s="47" t="s">
         <v>165</v>
       </c>
@@ -5383,7 +5388,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="39" spans="2:9" hidden="1">
+    <row r="39" spans="2:9">
       <c r="B39" s="47" t="s">
         <v>165</v>
       </c>
@@ -5402,7 +5407,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="40" spans="2:9" hidden="1">
+    <row r="40" spans="2:9">
       <c r="B40" s="47" t="s">
         <v>165</v>
       </c>
@@ -5421,7 +5426,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="41" spans="2:9" hidden="1">
+    <row r="41" spans="2:9">
       <c r="B41" s="47" t="s">
         <v>165</v>
       </c>
@@ -5576,7 +5581,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="48" spans="2:9" hidden="1">
+    <row r="48" spans="2:9">
       <c r="B48" s="48" t="s">
         <v>167</v>
       </c>
@@ -5593,7 +5598,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="49" spans="1:9" hidden="1">
+    <row r="49" spans="1:9">
       <c r="B49" s="48" t="s">
         <v>167</v>
       </c>
@@ -5610,7 +5615,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="50" spans="1:9" hidden="1">
+    <row r="50" spans="1:9">
       <c r="A50" s="21" t="s">
         <v>221</v>
       </c>
@@ -5633,7 +5638,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="51" spans="1:9" hidden="1">
+    <row r="51" spans="1:9">
       <c r="A51" s="21" t="s">
         <v>213</v>
       </c>
@@ -5656,7 +5661,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="52" spans="1:9" hidden="1">
+    <row r="52" spans="1:9">
       <c r="B52" s="50" t="s">
         <v>188</v>
       </c>
@@ -5699,7 +5704,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="54" spans="1:9" hidden="1">
+    <row r="54" spans="1:9">
       <c r="B54" s="50" t="s">
         <v>188</v>
       </c>
@@ -5719,7 +5724,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="55" spans="1:9" hidden="1">
+    <row r="55" spans="1:9">
       <c r="B55" s="50" t="s">
         <v>188</v>
       </c>
@@ -5739,7 +5744,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="56" spans="1:9" hidden="1">
+    <row r="56" spans="1:9">
       <c r="B56" s="29" t="s">
         <v>181</v>
       </c>
@@ -5759,7 +5764,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="57" spans="1:9" hidden="1">
+    <row r="57" spans="1:9">
       <c r="B57" s="29" t="s">
         <v>181</v>
       </c>
@@ -5779,7 +5784,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="58" spans="1:9" hidden="1">
+    <row r="58" spans="1:9">
       <c r="B58" s="29" t="s">
         <v>181</v>
       </c>
@@ -5799,7 +5804,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="59" spans="1:9" hidden="1">
+    <row r="59" spans="1:9">
       <c r="B59" s="29" t="s">
         <v>181</v>
       </c>
@@ -5812,6 +5817,9 @@
       <c r="E59" s="28" t="s">
         <v>18</v>
       </c>
+      <c r="F59" s="28">
+        <v>1</v>
+      </c>
       <c r="H59" s="28" t="s">
         <v>136</v>
       </c>
@@ -5819,7 +5827,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="60" spans="1:9" hidden="1">
+    <row r="60" spans="1:9">
       <c r="B60" s="29" t="s">
         <v>181</v>
       </c>
@@ -5839,7 +5847,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="61" spans="1:9" hidden="1">
+    <row r="61" spans="1:9">
       <c r="B61" s="29" t="s">
         <v>181</v>
       </c>
@@ -5859,7 +5867,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="62" spans="1:9" hidden="1">
+    <row r="62" spans="1:9">
       <c r="B62" s="43" t="s">
         <v>186</v>
       </c>
@@ -5879,7 +5887,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="63" spans="1:9" hidden="1">
+    <row r="63" spans="1:9">
       <c r="B63" s="43" t="s">
         <v>186</v>
       </c>
@@ -5899,7 +5907,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="64" spans="1:9" hidden="1">
+    <row r="64" spans="1:9">
       <c r="B64" s="43" t="s">
         <v>186</v>
       </c>
@@ -5919,7 +5927,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="65" spans="2:9" hidden="1">
+    <row r="65" spans="2:9">
       <c r="B65" s="43" t="s">
         <v>186</v>
       </c>
@@ -5936,7 +5944,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="66" spans="2:9" hidden="1">
+    <row r="66" spans="2:9">
       <c r="B66" s="43" t="s">
         <v>186</v>
       </c>
@@ -5956,7 +5964,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="67" spans="2:9" hidden="1">
+    <row r="67" spans="2:9">
       <c r="B67" s="43" t="s">
         <v>186</v>
       </c>
@@ -5976,7 +5984,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="68" spans="2:9" hidden="1">
+    <row r="68" spans="2:9">
       <c r="B68" s="43" t="s">
         <v>186</v>
       </c>
@@ -5993,7 +6001,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="69" spans="2:9" hidden="1">
+    <row r="69" spans="2:9">
       <c r="B69" s="44" t="s">
         <v>195</v>
       </c>
@@ -6010,7 +6018,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="70" spans="2:9" hidden="1">
+    <row r="70" spans="2:9">
       <c r="B70" s="44" t="s">
         <v>195</v>
       </c>
@@ -6027,7 +6035,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="71" spans="2:9" hidden="1">
+    <row r="71" spans="2:9">
       <c r="B71" s="44" t="s">
         <v>195</v>
       </c>
@@ -6044,7 +6052,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="72" spans="2:9" hidden="1">
+    <row r="72" spans="2:9" ht="18.75">
       <c r="B72" s="44" t="s">
         <v>195</v>
       </c>
@@ -6061,7 +6069,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="73" spans="2:9" hidden="1">
+    <row r="73" spans="2:9">
       <c r="B73" s="51" t="s">
         <v>199</v>
       </c>
@@ -6078,7 +6086,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="74" spans="2:9" hidden="1">
+    <row r="74" spans="2:9">
       <c r="B74" s="51" t="s">
         <v>199</v>
       </c>
@@ -6097,7 +6105,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="75" spans="2:9" hidden="1">
+    <row r="75" spans="2:9">
       <c r="B75" s="51" t="s">
         <v>199</v>
       </c>
@@ -6116,7 +6124,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="76" spans="2:9" hidden="1">
+    <row r="76" spans="2:9">
       <c r="B76" s="51" t="s">
         <v>199</v>
       </c>
@@ -6135,7 +6143,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="77" spans="2:9" hidden="1">
+    <row r="77" spans="2:9">
       <c r="B77" s="51" t="s">
         <v>199</v>
       </c>
@@ -6153,13 +6161,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:I77" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="8">
-      <filters>
-        <filter val="福田"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A2:I77" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H77" xr:uid="{E1CFE88F-4F87-4696-BE21-1133C2AEB8C1}">
@@ -6180,7 +6182,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402AEDD2-674B-437A-B1BD-39BBE1464A75}">
   <dimension ref="B2:H10"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:8">
       <c r="B2" s="52" t="s">
@@ -6375,26 +6377,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -6629,26 +6611,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0A0972-5393-459A-8603-138D87B70161}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6665,4 +6648,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/コスト表.xlsx
+++ b/コスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kubotananato\Documents\GitHub\koukiteam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{674FBE65-82F1-4C91-84F3-4C938CB9AA3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10860E37-DFE9-43B9-A39A-A09F59C4CB10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="C3">
         <f>SUM(作業工数見積もり!F3:F103)</f>
-        <v>45</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="4" spans="2:5">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-9.9337748344370855E-2</v>
+        <v>-0.11589403973509933</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.10392609699769054</v>
+        <v>-0.12124711316397228</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.1066350710900474</v>
+        <v>-0.12440758293838862</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -4784,7 +4784,7 @@
       </c>
       <c r="L12" s="21">
         <f>SUM(F3:F77)</f>
-        <v>45</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="13" spans="2:13">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="L13" s="21">
         <f>1*L12</f>
-        <v>45</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="14" spans="2:13">
@@ -4831,7 +4831,7 @@
         <v>34</v>
       </c>
       <c r="F14" s="28">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H14" s="28" t="s">
         <v>136</v>
@@ -4967,7 +4967,7 @@
         <v>34</v>
       </c>
       <c r="F19" s="28">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H19" s="28" t="s">
         <v>136</v>
@@ -5017,7 +5017,7 @@
         <v>34</v>
       </c>
       <c r="F21" s="28">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="H21" s="28" t="s">
         <v>136</v>
@@ -6377,6 +6377,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -6611,27 +6631,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0A0972-5393-459A-8603-138D87B70161}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6648,23 +6667,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/コスト表.xlsx
+++ b/コスト表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kubotananato\Documents\GitHub\koukiteam\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ooharastudent-my.sharepoint.com/personal/fko2647001_stu_o-hara_ac_jp/Documents/デスクトップ/github/koukiteam/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10860E37-DFE9-43B9-A39A-A09F59C4CB10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{10860E37-DFE9-43B9-A39A-A09F59C4CB10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C6D6FAE-542F-49D1-9A08-35E5CF20CBAA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1813,20 +1813,20 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="177" formatCode="0.000"/>
   </numFmts>
   <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="Calibri"/>
+      <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1835,14 +1835,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1850,7 +1850,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1858,7 +1858,7 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1866,7 +1866,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1874,7 +1874,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2118,8 +2118,8 @@
   <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2486,18 +2486,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1662411A-9E28-47BA-80A0-FB5B8EEC7CF8}">
   <dimension ref="A1:M106"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" style="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.5703125" customWidth="1"/>
-    <col min="9" max="9" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.75" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.25" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.625" customWidth="1"/>
+    <col min="9" max="9" width="7.125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="33" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.25" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4265,12 +4265,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{224174C6-79B8-40DF-BFBC-1FA41083861E}">
   <dimension ref="B3:E27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="33" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:5">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="C3">
         <f>SUM(作業工数見積もり!F3:F103)</f>
-        <v>52.5</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="2:5">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.11589403973509933</v>
+        <v>-0.13686534216335541</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.12124711316397228</v>
+        <v>-0.14318706697459585</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.12440758293838862</v>
+        <v>-0.14691943127962084</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -4465,20 +4465,21 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A2:M77"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="32.7109375" style="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.85546875" style="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.140625" style="21" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" style="28" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" style="28" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.42578125" style="28" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" style="28" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.75" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.875" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.125" style="21" customWidth="1"/>
+    <col min="4" max="4" width="11.75" style="28" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.25" style="28" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.375" style="28" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.25" style="28" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="21"/>
-    <col min="10" max="10" width="15.5703125" style="21" customWidth="1"/>
+    <col min="10" max="10" width="15.625" style="21" customWidth="1"/>
     <col min="11" max="11" width="33" style="21" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.28515625" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.25" style="21" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="19" style="21" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="21"/>
   </cols>
@@ -4509,7 +4510,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="3" spans="2:13">
+    <row r="3" spans="2:13" hidden="1">
       <c r="B3" s="43" t="s">
         <v>137</v>
       </c>
@@ -4536,7 +4537,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="2:13">
+    <row r="4" spans="2:13" hidden="1">
       <c r="B4" s="43" t="s">
         <v>137</v>
       </c>
@@ -4563,7 +4564,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="2:13">
+    <row r="5" spans="2:13" hidden="1">
       <c r="B5" s="43" t="s">
         <v>137</v>
       </c>
@@ -4590,7 +4591,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="2:13">
+    <row r="6" spans="2:13" hidden="1">
       <c r="B6" s="44" t="s">
         <v>159</v>
       </c>
@@ -4620,7 +4621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:13">
+    <row r="7" spans="2:13" hidden="1">
       <c r="B7" s="44" t="s">
         <v>159</v>
       </c>
@@ -4645,7 +4646,7 @@
       <c r="K7" s="37"/>
       <c r="L7" s="39"/>
     </row>
-    <row r="8" spans="2:13">
+    <row r="8" spans="2:13" hidden="1">
       <c r="B8" s="44" t="s">
         <v>159</v>
       </c>
@@ -4676,7 +4677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:13">
+    <row r="9" spans="2:13" hidden="1">
       <c r="B9" s="44" t="s">
         <v>159</v>
       </c>
@@ -4710,7 +4711,7 @@
         <v>1.0135135135135136</v>
       </c>
     </row>
-    <row r="10" spans="2:13">
+    <row r="10" spans="2:13" hidden="1">
       <c r="B10" s="44" t="s">
         <v>159</v>
       </c>
@@ -4737,7 +4738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:13">
+    <row r="11" spans="2:13" hidden="1">
       <c r="B11" s="44" t="s">
         <v>159</v>
       </c>
@@ -4757,7 +4758,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="12" spans="2:13">
+    <row r="12" spans="2:13" hidden="1">
       <c r="B12" s="45" t="s">
         <v>141</v>
       </c>
@@ -4784,10 +4785,10 @@
       </c>
       <c r="L12" s="21">
         <f>SUM(F3:F77)</f>
-        <v>52.5</v>
-      </c>
-    </row>
-    <row r="13" spans="2:13">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" hidden="1">
       <c r="B13" s="45" t="s">
         <v>141</v>
       </c>
@@ -4814,10 +4815,10 @@
       </c>
       <c r="L13" s="21">
         <f>1*L12</f>
-        <v>52.5</v>
-      </c>
-    </row>
-    <row r="14" spans="2:13">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" hidden="1">
       <c r="B14" s="45" t="s">
         <v>141</v>
       </c>
@@ -4841,7 +4842,7 @@
       </c>
       <c r="J14" s="38"/>
     </row>
-    <row r="15" spans="2:13">
+    <row r="15" spans="2:13" hidden="1">
       <c r="B15" s="45" t="s">
         <v>141</v>
       </c>
@@ -4872,7 +4873,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="2:13">
+    <row r="16" spans="2:13" hidden="1">
       <c r="B16" s="45" t="s">
         <v>141</v>
       </c>
@@ -4899,7 +4900,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="2:12">
+    <row r="17" spans="2:12" hidden="1">
       <c r="B17" s="45" t="s">
         <v>141</v>
       </c>
@@ -4926,7 +4927,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="2:12">
+    <row r="18" spans="2:12" hidden="1">
       <c r="B18" s="45" t="s">
         <v>141</v>
       </c>
@@ -4953,7 +4954,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="2:12">
+    <row r="19" spans="2:12" hidden="1">
       <c r="B19" s="45" t="s">
         <v>141</v>
       </c>
@@ -4983,7 +4984,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="2:12">
+    <row r="20" spans="2:12" hidden="1">
       <c r="B20" s="45" t="s">
         <v>141</v>
       </c>
@@ -5003,7 +5004,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="21" spans="2:12">
+    <row r="21" spans="2:12" hidden="1">
       <c r="B21" s="45" t="s">
         <v>141</v>
       </c>
@@ -5026,7 +5027,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="22" spans="2:12">
+    <row r="22" spans="2:12" hidden="1">
       <c r="B22" s="45" t="s">
         <v>141</v>
       </c>
@@ -5049,7 +5050,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="23" spans="2:12">
+    <row r="23" spans="2:12" hidden="1">
       <c r="B23" s="45" t="s">
         <v>141</v>
       </c>
@@ -5069,7 +5070,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="24" spans="2:12">
+    <row r="24" spans="2:12" hidden="1">
       <c r="B24" s="45" t="s">
         <v>141</v>
       </c>
@@ -5092,7 +5093,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="25" spans="2:12">
+    <row r="25" spans="2:12" hidden="1">
       <c r="B25" s="45" t="s">
         <v>141</v>
       </c>
@@ -5112,7 +5113,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="26" spans="2:12">
+    <row r="26" spans="2:12" hidden="1">
       <c r="B26" s="45" t="s">
         <v>141</v>
       </c>
@@ -5132,7 +5133,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="27" spans="2:12">
+    <row r="27" spans="2:12" hidden="1">
       <c r="B27" s="46" t="s">
         <v>152</v>
       </c>
@@ -5155,7 +5156,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="28" spans="2:12">
+    <row r="28" spans="2:12" hidden="1">
       <c r="B28" s="46" t="s">
         <v>152</v>
       </c>
@@ -5178,7 +5179,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="29" spans="2:12">
+    <row r="29" spans="2:12" hidden="1">
       <c r="B29" s="46" t="s">
         <v>152</v>
       </c>
@@ -5201,7 +5202,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="30" spans="2:12">
+    <row r="30" spans="2:12" hidden="1">
       <c r="B30" s="46" t="s">
         <v>152</v>
       </c>
@@ -5224,7 +5225,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="31" spans="2:12">
+    <row r="31" spans="2:12" hidden="1">
       <c r="B31" s="46" t="s">
         <v>152</v>
       </c>
@@ -5247,7 +5248,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="32" spans="2:12">
+    <row r="32" spans="2:12" hidden="1">
       <c r="B32" s="46" t="s">
         <v>152</v>
       </c>
@@ -5267,7 +5268,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="33" spans="2:9">
+    <row r="33" spans="2:9" hidden="1">
       <c r="B33" s="46" t="s">
         <v>152</v>
       </c>
@@ -5287,7 +5288,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="34" spans="2:9">
+    <row r="34" spans="2:9" hidden="1">
       <c r="B34" s="46" t="s">
         <v>152</v>
       </c>
@@ -5310,7 +5311,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="35" spans="2:9">
+    <row r="35" spans="2:9" hidden="1">
       <c r="B35" s="46" t="s">
         <v>152</v>
       </c>
@@ -5327,7 +5328,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="36" spans="2:9">
+    <row r="36" spans="2:9" hidden="1">
       <c r="B36" s="46" t="s">
         <v>152</v>
       </c>
@@ -5350,7 +5351,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="37" spans="2:9">
+    <row r="37" spans="2:9" hidden="1">
       <c r="B37" s="47" t="s">
         <v>165</v>
       </c>
@@ -5369,7 +5370,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="38" spans="2:9">
+    <row r="38" spans="2:9" hidden="1">
       <c r="B38" s="47" t="s">
         <v>165</v>
       </c>
@@ -5388,7 +5389,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="39" spans="2:9">
+    <row r="39" spans="2:9" hidden="1">
       <c r="B39" s="47" t="s">
         <v>165</v>
       </c>
@@ -5407,7 +5408,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="40" spans="2:9">
+    <row r="40" spans="2:9" hidden="1">
       <c r="B40" s="47" t="s">
         <v>165</v>
       </c>
@@ -5426,7 +5427,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="41" spans="2:9">
+    <row r="41" spans="2:9" hidden="1">
       <c r="B41" s="47" t="s">
         <v>165</v>
       </c>
@@ -5443,7 +5444,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="42" spans="2:9">
+    <row r="42" spans="2:9" hidden="1">
       <c r="B42" s="48" t="s">
         <v>167</v>
       </c>
@@ -5466,7 +5467,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="43" spans="2:9">
+    <row r="43" spans="2:9" hidden="1">
       <c r="B43" s="48" t="s">
         <v>167</v>
       </c>
@@ -5489,7 +5490,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="44" spans="2:9">
+    <row r="44" spans="2:9" hidden="1">
       <c r="B44" s="48" t="s">
         <v>167</v>
       </c>
@@ -5512,7 +5513,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="45" spans="2:9">
+    <row r="45" spans="2:9" hidden="1">
       <c r="B45" s="48" t="s">
         <v>167</v>
       </c>
@@ -5535,7 +5536,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="46" spans="2:9">
+    <row r="46" spans="2:9" hidden="1">
       <c r="B46" s="48" t="s">
         <v>167</v>
       </c>
@@ -5558,7 +5559,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="47" spans="2:9">
+    <row r="47" spans="2:9" hidden="1">
       <c r="B47" s="48" t="s">
         <v>167</v>
       </c>
@@ -5581,7 +5582,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="48" spans="2:9">
+    <row r="48" spans="2:9" hidden="1">
       <c r="B48" s="48" t="s">
         <v>167</v>
       </c>
@@ -5598,7 +5599,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:9" hidden="1">
       <c r="B49" s="48" t="s">
         <v>167</v>
       </c>
@@ -5615,7 +5616,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:9" hidden="1">
       <c r="A50" s="21" t="s">
         <v>221</v>
       </c>
@@ -5638,7 +5639,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:9" hidden="1">
       <c r="A51" s="21" t="s">
         <v>213</v>
       </c>
@@ -5661,7 +5662,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:9" hidden="1">
       <c r="B52" s="50" t="s">
         <v>188</v>
       </c>
@@ -5681,7 +5682,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:9" hidden="1">
       <c r="B53" s="50" t="s">
         <v>188</v>
       </c>
@@ -5704,7 +5705,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:9" hidden="1">
       <c r="B54" s="50" t="s">
         <v>188</v>
       </c>
@@ -5724,7 +5725,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:9" hidden="1">
       <c r="B55" s="50" t="s">
         <v>188</v>
       </c>
@@ -5744,7 +5745,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" hidden="1">
       <c r="B56" s="29" t="s">
         <v>181</v>
       </c>
@@ -5764,7 +5765,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:9" hidden="1">
       <c r="B57" s="29" t="s">
         <v>181</v>
       </c>
@@ -5784,7 +5785,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:9" hidden="1">
       <c r="B58" s="29" t="s">
         <v>181</v>
       </c>
@@ -5804,7 +5805,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:9" hidden="1">
       <c r="B59" s="29" t="s">
         <v>181</v>
       </c>
@@ -5827,7 +5828,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:9" hidden="1">
       <c r="B60" s="29" t="s">
         <v>181</v>
       </c>
@@ -5847,7 +5848,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:9" hidden="1">
       <c r="B61" s="29" t="s">
         <v>181</v>
       </c>
@@ -5880,6 +5881,9 @@
       <c r="E62" s="28" t="s">
         <v>34</v>
       </c>
+      <c r="F62" s="28">
+        <v>2</v>
+      </c>
       <c r="H62" s="28" t="s">
         <v>136</v>
       </c>
@@ -5900,6 +5904,9 @@
       <c r="E63" s="28" t="s">
         <v>34</v>
       </c>
+      <c r="F63" s="28">
+        <v>2</v>
+      </c>
       <c r="H63" s="28" t="s">
         <v>136</v>
       </c>
@@ -5920,6 +5927,9 @@
       <c r="E64" s="28" t="s">
         <v>34</v>
       </c>
+      <c r="F64" s="28">
+        <v>1.5</v>
+      </c>
       <c r="H64" s="28" t="s">
         <v>136</v>
       </c>
@@ -5927,7 +5937,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="65" spans="2:9">
+    <row r="65" spans="2:9" hidden="1">
       <c r="B65" s="43" t="s">
         <v>186</v>
       </c>
@@ -5957,6 +5967,9 @@
       <c r="E66" s="28" t="s">
         <v>34</v>
       </c>
+      <c r="F66" s="28">
+        <v>2</v>
+      </c>
       <c r="H66" s="28" t="s">
         <v>136</v>
       </c>
@@ -5977,6 +5990,9 @@
       <c r="E67" s="28" t="s">
         <v>34</v>
       </c>
+      <c r="F67" s="28">
+        <v>2</v>
+      </c>
       <c r="H67" s="28" t="s">
         <v>136</v>
       </c>
@@ -5984,7 +6000,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="68" spans="2:9">
+    <row r="68" spans="2:9" hidden="1">
       <c r="B68" s="43" t="s">
         <v>186</v>
       </c>
@@ -6001,7 +6017,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="69" spans="2:9">
+    <row r="69" spans="2:9" hidden="1">
       <c r="B69" s="44" t="s">
         <v>195</v>
       </c>
@@ -6018,7 +6034,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="70" spans="2:9">
+    <row r="70" spans="2:9" hidden="1">
       <c r="B70" s="44" t="s">
         <v>195</v>
       </c>
@@ -6035,7 +6051,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="71" spans="2:9">
+    <row r="71" spans="2:9" hidden="1">
       <c r="B71" s="44" t="s">
         <v>195</v>
       </c>
@@ -6052,7 +6068,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="72" spans="2:9" ht="18.75">
+    <row r="72" spans="2:9" hidden="1">
       <c r="B72" s="44" t="s">
         <v>195</v>
       </c>
@@ -6069,7 +6085,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="73" spans="2:9">
+    <row r="73" spans="2:9" hidden="1">
       <c r="B73" s="51" t="s">
         <v>199</v>
       </c>
@@ -6086,7 +6102,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="74" spans="2:9">
+    <row r="74" spans="2:9" hidden="1">
       <c r="B74" s="51" t="s">
         <v>199</v>
       </c>
@@ -6105,7 +6121,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="75" spans="2:9">
+    <row r="75" spans="2:9" hidden="1">
       <c r="B75" s="51" t="s">
         <v>199</v>
       </c>
@@ -6124,7 +6140,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="76" spans="2:9">
+    <row r="76" spans="2:9" hidden="1">
       <c r="B76" s="51" t="s">
         <v>199</v>
       </c>
@@ -6143,7 +6159,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="77" spans="2:9">
+    <row r="77" spans="2:9" hidden="1">
       <c r="B77" s="51" t="s">
         <v>199</v>
       </c>
@@ -6161,7 +6177,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:I77" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:I77" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="8">
+      <filters>
+        <filter val="廣田"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H77" xr:uid="{E1CFE88F-4F87-4696-BE21-1133C2AEB8C1}">
@@ -6182,7 +6204,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402AEDD2-674B-437A-B1BD-39BBE1464A75}">
   <dimension ref="B2:H10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="2:8">
       <c r="B2" s="52" t="s">
@@ -6377,26 +6399,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -6631,26 +6633,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0A0972-5393-459A-8603-138D87B70161}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6667,4 +6670,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/コスト表.xlsx
+++ b/コスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ooharastudent-my.sharepoint.com/personal/fko2647001_stu_o-hara_ac_jp/Documents/デスクトップ/github/koukiteam/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{10860E37-DFE9-43B9-A39A-A09F59C4CB10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C6D6FAE-542F-49D1-9A08-35E5CF20CBAA}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{10860E37-DFE9-43B9-A39A-A09F59C4CB10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B175608E-258E-47B6-B089-FC1530D93876}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2222,6 +2222,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -4279,7 +4283,7 @@
       </c>
       <c r="C3">
         <f>SUM(作業工数見積もり!F3:F103)</f>
-        <v>62</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="2:5">
@@ -4347,7 +4351,7 @@
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.13686534216335541</v>
+        <v>-0.10816777041942605</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -4364,7 +4368,7 @@
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.14318706697459585</v>
+        <v>-0.11316397228637413</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -4381,7 +4385,7 @@
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.14691943127962084</v>
+        <v>-0.11611374407582939</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -4510,7 +4514,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="3" spans="2:13" hidden="1">
+    <row r="3" spans="2:13">
       <c r="B3" s="43" t="s">
         <v>137</v>
       </c>
@@ -4522,9 +4526,6 @@
       </c>
       <c r="E3" s="28" t="s">
         <v>18</v>
-      </c>
-      <c r="F3" s="28">
-        <v>0.25</v>
       </c>
       <c r="H3" s="28" t="s">
         <v>136</v>
@@ -4537,7 +4538,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="2:13" hidden="1">
+    <row r="4" spans="2:13">
       <c r="B4" s="43" t="s">
         <v>137</v>
       </c>
@@ -4549,9 +4550,6 @@
       </c>
       <c r="E4" s="28" t="s">
         <v>207</v>
-      </c>
-      <c r="F4" s="28">
-        <v>0.25</v>
       </c>
       <c r="H4" s="28" t="s">
         <v>136</v>
@@ -4564,7 +4562,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="2:13" hidden="1">
+    <row r="5" spans="2:13">
       <c r="B5" s="43" t="s">
         <v>137</v>
       </c>
@@ -4576,9 +4574,6 @@
       </c>
       <c r="E5" s="28" t="s">
         <v>34</v>
-      </c>
-      <c r="F5" s="28">
-        <v>0.25</v>
       </c>
       <c r="H5" s="28" t="s">
         <v>136</v>
@@ -4646,7 +4641,7 @@
       <c r="K7" s="37"/>
       <c r="L7" s="39"/>
     </row>
-    <row r="8" spans="2:13" hidden="1">
+    <row r="8" spans="2:13">
       <c r="B8" s="44" t="s">
         <v>159</v>
       </c>
@@ -4658,9 +4653,6 @@
       </c>
       <c r="E8" s="28" t="s">
         <v>18</v>
-      </c>
-      <c r="F8" s="28">
-        <v>0.25</v>
       </c>
       <c r="H8" s="28" t="s">
         <v>136</v>
@@ -4711,7 +4703,7 @@
         <v>1.0135135135135136</v>
       </c>
     </row>
-    <row r="10" spans="2:13" hidden="1">
+    <row r="10" spans="2:13">
       <c r="B10" s="44" t="s">
         <v>159</v>
       </c>
@@ -4723,9 +4715,6 @@
       </c>
       <c r="E10" s="28" t="s">
         <v>18</v>
-      </c>
-      <c r="F10" s="28">
-        <v>0.5</v>
       </c>
       <c r="H10" s="28" t="s">
         <v>136</v>
@@ -4738,7 +4727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:13" hidden="1">
+    <row r="11" spans="2:13">
       <c r="B11" s="44" t="s">
         <v>159</v>
       </c>
@@ -4750,9 +4739,6 @@
       </c>
       <c r="E11" s="28" t="s">
         <v>18</v>
-      </c>
-      <c r="F11" s="28">
-        <v>0.5</v>
       </c>
       <c r="H11" s="28" t="s">
         <v>136</v>
@@ -4785,7 +4771,7 @@
       </c>
       <c r="L12" s="21">
         <f>SUM(F3:F77)</f>
-        <v>62</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="2:13" hidden="1">
@@ -4815,7 +4801,7 @@
       </c>
       <c r="L13" s="21">
         <f>1*L12</f>
-        <v>62</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="2:13" hidden="1">
@@ -4873,7 +4859,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="2:13" hidden="1">
+    <row r="16" spans="2:13">
       <c r="B16" s="45" t="s">
         <v>141</v>
       </c>
@@ -4886,9 +4872,6 @@
       <c r="E16" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F16" s="28">
-        <v>0.5</v>
-      </c>
       <c r="H16" s="28" t="s">
         <v>136</v>
       </c>
@@ -4900,7 +4883,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="2:12" hidden="1">
+    <row r="17" spans="2:12">
       <c r="B17" s="45" t="s">
         <v>141</v>
       </c>
@@ -4912,9 +4895,6 @@
       </c>
       <c r="E17" s="28" t="s">
         <v>18</v>
-      </c>
-      <c r="F17" s="28">
-        <v>1.5</v>
       </c>
       <c r="H17" s="28" t="s">
         <v>136</v>
@@ -4927,7 +4907,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="2:12" hidden="1">
+    <row r="18" spans="2:12">
       <c r="B18" s="45" t="s">
         <v>141</v>
       </c>
@@ -4939,9 +4919,6 @@
       </c>
       <c r="E18" s="28" t="s">
         <v>18</v>
-      </c>
-      <c r="F18" s="28">
-        <v>2.5</v>
       </c>
       <c r="H18" s="28" t="s">
         <v>136</v>
@@ -4984,7 +4961,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="2:12" hidden="1">
+    <row r="20" spans="2:12">
       <c r="B20" s="45" t="s">
         <v>141</v>
       </c>
@@ -4996,9 +4973,6 @@
       </c>
       <c r="E20" s="28" t="s">
         <v>18</v>
-      </c>
-      <c r="F20" s="28">
-        <v>3.5</v>
       </c>
       <c r="H20" s="28" t="s">
         <v>136</v>
@@ -5050,7 +5024,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="23" spans="2:12" hidden="1">
+    <row r="23" spans="2:12">
       <c r="B23" s="45" t="s">
         <v>141</v>
       </c>
@@ -5062,9 +5036,6 @@
       </c>
       <c r="E23" s="28" t="s">
         <v>18</v>
-      </c>
-      <c r="F23" s="28">
-        <v>1</v>
       </c>
       <c r="H23" s="28" t="s">
         <v>136</v>
@@ -5093,7 +5064,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="25" spans="2:12" hidden="1">
+    <row r="25" spans="2:12">
       <c r="B25" s="45" t="s">
         <v>141</v>
       </c>
@@ -5106,14 +5077,11 @@
       <c r="E25" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F25" s="28">
-        <v>0.5</v>
-      </c>
       <c r="H25" s="28" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="26" spans="2:12" hidden="1">
+    <row r="26" spans="2:12">
       <c r="B26" s="45" t="s">
         <v>141</v>
       </c>
@@ -5125,9 +5093,6 @@
       </c>
       <c r="E26" s="28" t="s">
         <v>18</v>
-      </c>
-      <c r="F26" s="28">
-        <v>0.5</v>
       </c>
       <c r="H26" s="28" t="s">
         <v>136</v>
@@ -5248,7 +5213,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="32" spans="2:12" hidden="1">
+    <row r="32" spans="2:12">
       <c r="B32" s="46" t="s">
         <v>152</v>
       </c>
@@ -5261,14 +5226,11 @@
       <c r="E32" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F32" s="28">
-        <v>0.5</v>
-      </c>
       <c r="H32" s="28" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="33" spans="2:9" hidden="1">
+    <row r="33" spans="2:9">
       <c r="B33" s="46" t="s">
         <v>152</v>
       </c>
@@ -5280,9 +5242,6 @@
       </c>
       <c r="E33" s="28" t="s">
         <v>18</v>
-      </c>
-      <c r="F33" s="28">
-        <v>0.5</v>
       </c>
       <c r="H33" s="28" t="s">
         <v>136</v>
@@ -5311,7 +5270,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="35" spans="2:9" hidden="1">
+    <row r="35" spans="2:9">
       <c r="B35" s="46" t="s">
         <v>152</v>
       </c>
@@ -5351,7 +5310,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="37" spans="2:9" hidden="1">
+    <row r="37" spans="2:9">
       <c r="B37" s="47" t="s">
         <v>165</v>
       </c>
@@ -5370,7 +5329,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="38" spans="2:9" hidden="1">
+    <row r="38" spans="2:9">
       <c r="B38" s="47" t="s">
         <v>165</v>
       </c>
@@ -5389,7 +5348,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="39" spans="2:9" hidden="1">
+    <row r="39" spans="2:9">
       <c r="B39" s="47" t="s">
         <v>165</v>
       </c>
@@ -5408,7 +5367,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="40" spans="2:9" hidden="1">
+    <row r="40" spans="2:9">
       <c r="B40" s="47" t="s">
         <v>165</v>
       </c>
@@ -5427,7 +5386,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="41" spans="2:9" hidden="1">
+    <row r="41" spans="2:9">
       <c r="B41" s="47" t="s">
         <v>165</v>
       </c>
@@ -5582,7 +5541,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="48" spans="2:9" hidden="1">
+    <row r="48" spans="2:9">
       <c r="B48" s="48" t="s">
         <v>167</v>
       </c>
@@ -5599,7 +5558,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="49" spans="1:9" hidden="1">
+    <row r="49" spans="1:9">
       <c r="B49" s="48" t="s">
         <v>167</v>
       </c>
@@ -5868,7 +5827,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:9" hidden="1">
       <c r="B62" s="43" t="s">
         <v>186</v>
       </c>
@@ -5891,7 +5850,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:9" hidden="1">
       <c r="B63" s="43" t="s">
         <v>186</v>
       </c>
@@ -5914,7 +5873,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:9" hidden="1">
       <c r="B64" s="43" t="s">
         <v>186</v>
       </c>
@@ -5954,7 +5913,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="66" spans="2:9">
+    <row r="66" spans="2:9" hidden="1">
       <c r="B66" s="43" t="s">
         <v>186</v>
       </c>
@@ -5977,7 +5936,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="67" spans="2:9">
+    <row r="67" spans="2:9" hidden="1">
       <c r="B67" s="43" t="s">
         <v>186</v>
       </c>
@@ -6000,7 +5959,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="68" spans="2:9" hidden="1">
+    <row r="68" spans="2:9">
       <c r="B68" s="43" t="s">
         <v>186</v>
       </c>
@@ -6017,7 +5976,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="69" spans="2:9" hidden="1">
+    <row r="69" spans="2:9">
       <c r="B69" s="44" t="s">
         <v>195</v>
       </c>
@@ -6034,7 +5993,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="70" spans="2:9" hidden="1">
+    <row r="70" spans="2:9">
       <c r="B70" s="44" t="s">
         <v>195</v>
       </c>
@@ -6051,7 +6010,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="71" spans="2:9" hidden="1">
+    <row r="71" spans="2:9">
       <c r="B71" s="44" t="s">
         <v>195</v>
       </c>
@@ -6068,7 +6027,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="72" spans="2:9" hidden="1">
+    <row r="72" spans="2:9">
       <c r="B72" s="44" t="s">
         <v>195</v>
       </c>
@@ -6085,7 +6044,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="73" spans="2:9" hidden="1">
+    <row r="73" spans="2:9">
       <c r="B73" s="51" t="s">
         <v>199</v>
       </c>
@@ -6102,7 +6061,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="74" spans="2:9" hidden="1">
+    <row r="74" spans="2:9">
       <c r="B74" s="51" t="s">
         <v>199</v>
       </c>
@@ -6121,7 +6080,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="75" spans="2:9" hidden="1">
+    <row r="75" spans="2:9">
       <c r="B75" s="51" t="s">
         <v>199</v>
       </c>
@@ -6140,7 +6099,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="76" spans="2:9" hidden="1">
+    <row r="76" spans="2:9">
       <c r="B76" s="51" t="s">
         <v>199</v>
       </c>
@@ -6159,7 +6118,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="77" spans="2:9" hidden="1">
+    <row r="77" spans="2:9">
       <c r="B77" s="51" t="s">
         <v>199</v>
       </c>
@@ -6179,9 +6138,7 @@
   </sheetData>
   <autoFilter ref="A2:I77" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="8">
-      <filters>
-        <filter val="廣田"/>
-      </filters>
+      <filters blank="1"/>
     </filterColumn>
   </autoFilter>
   <phoneticPr fontId="1"/>
@@ -6399,6 +6356,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -6633,27 +6610,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0A0972-5393-459A-8603-138D87B70161}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6670,23 +6646,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/コスト表.xlsx
+++ b/コスト表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ooharastudent-my.sharepoint.com/personal/fko2647001_stu_o-hara_ac_jp/Documents/デスクトップ/github/koukiteam/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kubotananato\Documents\GitHub\koukiteam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{10860E37-DFE9-43B9-A39A-A09F59C4CB10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B175608E-258E-47B6-B089-FC1530D93876}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1248DC54-57BF-4749-B53B-41ACD4A06E99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1813,20 +1813,20 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="177" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1835,14 +1835,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1850,7 +1850,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1858,7 +1858,7 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1866,7 +1866,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1874,7 +1874,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2118,8 +2118,8 @@
   <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2220,10 +2220,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2490,18 +2486,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1662411A-9E28-47BA-80A0-FB5B8EEC7CF8}">
   <dimension ref="A1:M106"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.75" style="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.25" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.625" customWidth="1"/>
-    <col min="9" max="9" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.5703125" customWidth="1"/>
+    <col min="9" max="9" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="33" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4269,12 +4265,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{224174C6-79B8-40DF-BFBC-1FA41083861E}">
   <dimension ref="B3:E27"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="33" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:5">
@@ -4283,7 +4279,7 @@
       </c>
       <c r="C3">
         <f>SUM(作業工数見積もり!F3:F103)</f>
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="2:5">
@@ -4351,7 +4347,7 @@
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.10816777041942605</v>
+        <v>-0.10154525386313466</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -4368,7 +4364,7 @@
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.11316397228637413</v>
+        <v>-0.10623556581986143</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -4385,7 +4381,7 @@
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.11611374407582939</v>
+        <v>-0.10900473933649289</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -4469,21 +4465,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A2:M77"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32.75" style="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.875" style="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.125" style="21" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="28" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.25" style="28" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.375" style="28" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.25" style="28" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.140625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" style="28" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" style="28" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.42578125" style="28" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" style="28" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="21"/>
-    <col min="10" max="10" width="15.625" style="21" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" style="21" customWidth="1"/>
     <col min="11" max="11" width="33" style="21" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.25" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.28515625" style="21" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="19" style="21" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="21"/>
   </cols>
@@ -4586,7 +4581,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="2:13" hidden="1">
+    <row r="6" spans="2:13">
       <c r="B6" s="44" t="s">
         <v>159</v>
       </c>
@@ -4616,7 +4611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:13" hidden="1">
+    <row r="7" spans="2:13">
       <c r="B7" s="44" t="s">
         <v>159</v>
       </c>
@@ -4669,7 +4664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:13" hidden="1">
+    <row r="9" spans="2:13">
       <c r="B9" s="44" t="s">
         <v>159</v>
       </c>
@@ -4744,7 +4739,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="12" spans="2:13" hidden="1">
+    <row r="12" spans="2:13">
       <c r="B12" s="45" t="s">
         <v>141</v>
       </c>
@@ -4771,10 +4766,10 @@
       </c>
       <c r="L12" s="21">
         <f>SUM(F3:F77)</f>
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" spans="2:13" hidden="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13">
       <c r="B13" s="45" t="s">
         <v>141</v>
       </c>
@@ -4801,10 +4796,10 @@
       </c>
       <c r="L13" s="21">
         <f>1*L12</f>
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" spans="2:13" hidden="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13">
       <c r="B14" s="45" t="s">
         <v>141</v>
       </c>
@@ -4818,7 +4813,7 @@
         <v>34</v>
       </c>
       <c r="F14" s="28">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H14" s="28" t="s">
         <v>136</v>
@@ -4828,7 +4823,7 @@
       </c>
       <c r="J14" s="38"/>
     </row>
-    <row r="15" spans="2:13" hidden="1">
+    <row r="15" spans="2:13">
       <c r="B15" s="45" t="s">
         <v>141</v>
       </c>
@@ -4931,7 +4926,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="2:12" hidden="1">
+    <row r="19" spans="2:12">
       <c r="B19" s="45" t="s">
         <v>141</v>
       </c>
@@ -4945,7 +4940,7 @@
         <v>34</v>
       </c>
       <c r="F19" s="28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H19" s="28" t="s">
         <v>136</v>
@@ -4978,7 +4973,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="21" spans="2:12" hidden="1">
+    <row r="21" spans="2:12">
       <c r="B21" s="45" t="s">
         <v>141</v>
       </c>
@@ -5001,7 +4996,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="22" spans="2:12" hidden="1">
+    <row r="22" spans="2:12">
       <c r="B22" s="45" t="s">
         <v>141</v>
       </c>
@@ -5041,7 +5036,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="24" spans="2:12" hidden="1">
+    <row r="24" spans="2:12">
       <c r="B24" s="45" t="s">
         <v>141</v>
       </c>
@@ -5098,7 +5093,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="27" spans="2:12" hidden="1">
+    <row r="27" spans="2:12">
       <c r="B27" s="46" t="s">
         <v>152</v>
       </c>
@@ -5121,7 +5116,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="28" spans="2:12" hidden="1">
+    <row r="28" spans="2:12">
       <c r="B28" s="46" t="s">
         <v>152</v>
       </c>
@@ -5144,7 +5139,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="29" spans="2:12" hidden="1">
+    <row r="29" spans="2:12">
       <c r="B29" s="46" t="s">
         <v>152</v>
       </c>
@@ -5167,7 +5162,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="30" spans="2:12" hidden="1">
+    <row r="30" spans="2:12">
       <c r="B30" s="46" t="s">
         <v>152</v>
       </c>
@@ -5190,7 +5185,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="31" spans="2:12" hidden="1">
+    <row r="31" spans="2:12">
       <c r="B31" s="46" t="s">
         <v>152</v>
       </c>
@@ -5247,7 +5242,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="34" spans="2:9" hidden="1">
+    <row r="34" spans="2:9">
       <c r="B34" s="46" t="s">
         <v>152</v>
       </c>
@@ -5287,7 +5282,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="36" spans="2:9" hidden="1">
+    <row r="36" spans="2:9">
       <c r="B36" s="46" t="s">
         <v>152</v>
       </c>
@@ -5403,7 +5398,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="42" spans="2:9" hidden="1">
+    <row r="42" spans="2:9">
       <c r="B42" s="48" t="s">
         <v>167</v>
       </c>
@@ -5426,7 +5421,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="43" spans="2:9" hidden="1">
+    <row r="43" spans="2:9">
       <c r="B43" s="48" t="s">
         <v>167</v>
       </c>
@@ -5449,7 +5444,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="44" spans="2:9" hidden="1">
+    <row r="44" spans="2:9">
       <c r="B44" s="48" t="s">
         <v>167</v>
       </c>
@@ -5472,7 +5467,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="45" spans="2:9" hidden="1">
+    <row r="45" spans="2:9">
       <c r="B45" s="48" t="s">
         <v>167</v>
       </c>
@@ -5495,7 +5490,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="46" spans="2:9" hidden="1">
+    <row r="46" spans="2:9">
       <c r="B46" s="48" t="s">
         <v>167</v>
       </c>
@@ -5518,7 +5513,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="47" spans="2:9" hidden="1">
+    <row r="47" spans="2:9">
       <c r="B47" s="48" t="s">
         <v>167</v>
       </c>
@@ -5575,7 +5570,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="50" spans="1:9" hidden="1">
+    <row r="50" spans="1:9">
       <c r="A50" s="21" t="s">
         <v>221</v>
       </c>
@@ -5598,7 +5593,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="51" spans="1:9" hidden="1">
+    <row r="51" spans="1:9">
       <c r="A51" s="21" t="s">
         <v>213</v>
       </c>
@@ -5621,7 +5616,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="52" spans="1:9" hidden="1">
+    <row r="52" spans="1:9">
       <c r="B52" s="50" t="s">
         <v>188</v>
       </c>
@@ -5641,7 +5636,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="53" spans="1:9" hidden="1">
+    <row r="53" spans="1:9">
       <c r="B53" s="50" t="s">
         <v>188</v>
       </c>
@@ -5664,7 +5659,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="54" spans="1:9" hidden="1">
+    <row r="54" spans="1:9">
       <c r="B54" s="50" t="s">
         <v>188</v>
       </c>
@@ -5684,7 +5679,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="55" spans="1:9" hidden="1">
+    <row r="55" spans="1:9">
       <c r="B55" s="50" t="s">
         <v>188</v>
       </c>
@@ -5704,7 +5699,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="56" spans="1:9" hidden="1">
+    <row r="56" spans="1:9">
       <c r="B56" s="29" t="s">
         <v>181</v>
       </c>
@@ -5724,7 +5719,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="57" spans="1:9" hidden="1">
+    <row r="57" spans="1:9">
       <c r="B57" s="29" t="s">
         <v>181</v>
       </c>
@@ -5744,7 +5739,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="58" spans="1:9" hidden="1">
+    <row r="58" spans="1:9">
       <c r="B58" s="29" t="s">
         <v>181</v>
       </c>
@@ -5764,7 +5759,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="59" spans="1:9" hidden="1">
+    <row r="59" spans="1:9">
       <c r="B59" s="29" t="s">
         <v>181</v>
       </c>
@@ -5787,7 +5782,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="60" spans="1:9" hidden="1">
+    <row r="60" spans="1:9">
       <c r="B60" s="29" t="s">
         <v>181</v>
       </c>
@@ -5807,7 +5802,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="61" spans="1:9" hidden="1">
+    <row r="61" spans="1:9">
       <c r="B61" s="29" t="s">
         <v>181</v>
       </c>
@@ -5827,7 +5822,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="62" spans="1:9" hidden="1">
+    <row r="62" spans="1:9">
       <c r="B62" s="43" t="s">
         <v>186</v>
       </c>
@@ -5850,7 +5845,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="63" spans="1:9" hidden="1">
+    <row r="63" spans="1:9">
       <c r="B63" s="43" t="s">
         <v>186</v>
       </c>
@@ -5873,7 +5868,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="64" spans="1:9" hidden="1">
+    <row r="64" spans="1:9">
       <c r="B64" s="43" t="s">
         <v>186</v>
       </c>
@@ -5896,7 +5891,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="65" spans="2:9" hidden="1">
+    <row r="65" spans="2:9">
       <c r="B65" s="43" t="s">
         <v>186</v>
       </c>
@@ -5913,7 +5908,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="66" spans="2:9" hidden="1">
+    <row r="66" spans="2:9">
       <c r="B66" s="43" t="s">
         <v>186</v>
       </c>
@@ -5936,7 +5931,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="67" spans="2:9" hidden="1">
+    <row r="67" spans="2:9">
       <c r="B67" s="43" t="s">
         <v>186</v>
       </c>
@@ -6027,7 +6022,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="72" spans="2:9">
+    <row r="72" spans="2:9" ht="18.75">
       <c r="B72" s="44" t="s">
         <v>195</v>
       </c>
@@ -6136,11 +6131,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:I77" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="8">
-      <filters blank="1"/>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A2:I77" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H77" xr:uid="{E1CFE88F-4F87-4696-BE21-1133C2AEB8C1}">
@@ -6161,7 +6152,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402AEDD2-674B-437A-B1BD-39BBE1464A75}">
   <dimension ref="B2:H10"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:8">
       <c r="B2" s="52" t="s">
@@ -6367,15 +6358,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -6610,6 +6592,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
@@ -6622,14 +6613,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0A0972-5393-459A-8603-138D87B70161}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6646,4 +6629,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/コスト表.xlsx
+++ b/コスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kubotananato\Documents\GitHub\koukiteam\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\genki\Documents\GitHub\koukiteam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1248DC54-57BF-4749-B53B-41ACD4A06E99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DEB384F-77D0-4D5A-9E90-F183A32DF056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1020" yWindow="810" windowWidth="26025" windowHeight="14460" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1125_元データ" sheetId="4" r:id="rId1"/>
@@ -1813,20 +1813,20 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="177" formatCode="0.000"/>
   </numFmts>
   <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="Calibri"/>
+      <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1835,14 +1835,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1850,7 +1850,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1858,7 +1858,7 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1866,7 +1866,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1874,7 +1874,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2118,8 +2118,8 @@
   <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2486,18 +2486,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1662411A-9E28-47BA-80A0-FB5B8EEC7CF8}">
   <dimension ref="A1:M106"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" style="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.5703125" customWidth="1"/>
-    <col min="9" max="9" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.75" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.25" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.625" customWidth="1"/>
+    <col min="9" max="9" width="7.125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="33" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.25" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4265,12 +4265,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{224174C6-79B8-40DF-BFBC-1FA41083861E}">
   <dimension ref="B3:E27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="33" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:5">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="C3">
         <f>SUM(作業工数見積もり!F3:F103)</f>
-        <v>46</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="4" spans="2:5">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.10154525386313466</v>
+        <v>-0.10264900662251655</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.10623556581986143</v>
+        <v>-0.10739030023094688</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.10900473933649289</v>
+        <v>-0.11018957345971564</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -4466,19 +4466,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:M77"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="32.7109375" style="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.85546875" style="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.140625" style="21" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" style="28" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" style="28" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.42578125" style="28" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" style="28" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.75" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.875" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.125" style="21" customWidth="1"/>
+    <col min="4" max="4" width="11.75" style="28" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.25" style="28" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.375" style="28" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.25" style="28" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="21"/>
-    <col min="10" max="10" width="15.5703125" style="21" customWidth="1"/>
+    <col min="10" max="10" width="15.625" style="21" customWidth="1"/>
     <col min="11" max="11" width="33" style="21" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.28515625" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.25" style="21" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="19" style="21" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="21"/>
   </cols>
@@ -4678,7 +4678,7 @@
         <v>34</v>
       </c>
       <c r="F9" s="28">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H9" s="28" t="s">
         <v>136</v>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="L12" s="21">
         <f>SUM(F3:F77)</f>
-        <v>46</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="13" spans="2:13">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="L13" s="21">
         <f>1*L12</f>
-        <v>46</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="14" spans="2:13">
@@ -6022,7 +6022,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="72" spans="2:9" ht="18.75">
+    <row r="72" spans="2:9">
       <c r="B72" s="44" t="s">
         <v>195</v>
       </c>
@@ -6152,7 +6152,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402AEDD2-674B-437A-B1BD-39BBE1464A75}">
   <dimension ref="B2:H10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="2:8">
       <c r="B2" s="52" t="s">
@@ -6347,14 +6347,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6593,21 +6591,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6632,9 +6629,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/コスト表.xlsx
+++ b/コスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\genki\Documents\GitHub\koukiteam\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tamari\Documents\GitHub\koukiteam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DEB384F-77D0-4D5A-9E90-F183A32DF056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED1B077D-837E-419F-B36E-F7884CB00317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1020" yWindow="810" windowWidth="26025" windowHeight="14460" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1125_元データ" sheetId="4" r:id="rId1"/>
@@ -1813,20 +1813,20 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="177" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1835,14 +1835,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1850,7 +1850,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1858,7 +1858,7 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1866,7 +1866,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1874,7 +1874,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2118,8 +2118,8 @@
   <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2486,18 +2486,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1662411A-9E28-47BA-80A0-FB5B8EEC7CF8}">
   <dimension ref="A1:M106"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.75" style="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.25" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.625" customWidth="1"/>
-    <col min="9" max="9" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.5703125" customWidth="1"/>
+    <col min="9" max="9" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="33" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2575,11 +2575,11 @@
       </c>
       <c r="K4" s="2">
         <f ca="1">NETWORKDAYS(K5,K6)</f>
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L4" s="3">
         <f ca="1" xml:space="preserve"> K3 / K4</f>
-        <v>5.4752066115702477E-2</v>
+        <v>5.4639175257731959E-2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="K6" s="1">
         <f ca="1">TODAY()</f>
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2684,11 +2684,11 @@
       </c>
       <c r="L9" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K9)</f>
-        <v>-453</v>
+        <v>-454</v>
       </c>
       <c r="M9" s="3">
         <f ca="1">($K$2 - $K$3) / L9</f>
-        <v>-0.20309050772626933</v>
+        <v>-0.20264317180616739</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -2715,11 +2715,11 @@
       </c>
       <c r="L10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K10)</f>
-        <v>-433</v>
+        <v>-434</v>
       </c>
       <c r="M10" s="3">
         <f ca="1">($K$2 - $K$3) / L10</f>
-        <v>-0.21247113163972287</v>
+        <v>-0.2119815668202765</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2746,11 +2746,11 @@
       </c>
       <c r="L11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K11)</f>
-        <v>-422</v>
+        <v>-423</v>
       </c>
       <c r="M11" s="3">
         <f ca="1">($K$2 - $K$3) / L11</f>
-        <v>-0.21800947867298578</v>
+        <v>-0.21749408983451538</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -4265,12 +4265,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{224174C6-79B8-40DF-BFBC-1FA41083861E}">
   <dimension ref="B3:E27"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="33" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:5">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="C3">
         <f>SUM(作業工数見積もり!F3:F103)</f>
-        <v>46.5</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="4" spans="2:5">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -4343,11 +4343,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-453</v>
+        <v>-454</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.10264900662251655</v>
+        <v>-0.11123348017621146</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -4360,11 +4360,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-433</v>
+        <v>-434</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.10739030023094688</v>
+        <v>-0.11635944700460829</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -4377,11 +4377,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-422</v>
+        <v>-423</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.11018957345971564</v>
+        <v>-0.11938534278959811</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -4466,19 +4466,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:M77"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32.75" style="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.875" style="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.125" style="21" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="28" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.25" style="28" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.375" style="28" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.25" style="28" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.140625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" style="28" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" style="28" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.42578125" style="28" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" style="28" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="21"/>
-    <col min="10" max="10" width="15.625" style="21" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" style="21" customWidth="1"/>
     <col min="11" max="11" width="33" style="21" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.25" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.28515625" style="21" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="19" style="21" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="21"/>
   </cols>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="L12" s="21">
         <f>SUM(F3:F77)</f>
-        <v>46.5</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="13" spans="2:13">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="L13" s="21">
         <f>1*L12</f>
-        <v>46.5</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="14" spans="2:13">
@@ -5586,6 +5586,9 @@
       <c r="E50" s="28" t="s">
         <v>34</v>
       </c>
+      <c r="F50" s="28">
+        <v>2</v>
+      </c>
       <c r="H50" s="28" t="s">
         <v>136</v>
       </c>
@@ -5609,6 +5612,9 @@
       <c r="E51" s="28" t="s">
         <v>34</v>
       </c>
+      <c r="F51" s="28">
+        <v>1</v>
+      </c>
       <c r="H51" s="28" t="s">
         <v>136</v>
       </c>
@@ -5629,6 +5635,9 @@
       <c r="E52" s="28" t="s">
         <v>34</v>
       </c>
+      <c r="F52" s="28">
+        <v>1</v>
+      </c>
       <c r="H52" s="28" t="s">
         <v>136</v>
       </c>
@@ -6022,7 +6031,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="72" spans="2:9">
+    <row r="72" spans="2:9" ht="18.75">
       <c r="B72" s="44" t="s">
         <v>195</v>
       </c>
@@ -6152,7 +6161,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402AEDD2-674B-437A-B1BD-39BBE1464A75}">
   <dimension ref="B2:H10"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:8">
       <c r="B2" s="52" t="s">
@@ -6347,12 +6356,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6591,20 +6602,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6629,12 +6641,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/コスト表.xlsx
+++ b/コスト表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kubotananato\Documents\GitHub\koukiteam\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Taiki\Documents\GitHub\koukiteam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1248DC54-57BF-4749-B53B-41ACD4A06E99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{618DCD2D-4FE2-447A-B17F-8CD599D620DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1813,20 +1813,20 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="177" formatCode="0.000"/>
   </numFmts>
   <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="Calibri"/>
+      <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1835,14 +1835,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1850,7 +1850,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1858,7 +1858,7 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1866,7 +1866,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1874,7 +1874,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2118,8 +2118,8 @@
   <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2486,18 +2486,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1662411A-9E28-47BA-80A0-FB5B8EEC7CF8}">
   <dimension ref="A1:M106"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" style="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.5703125" customWidth="1"/>
-    <col min="9" max="9" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.75" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.25" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.625" customWidth="1"/>
+    <col min="9" max="9" width="7.125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="33" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.25" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2575,11 +2575,11 @@
       </c>
       <c r="K4" s="2">
         <f ca="1">NETWORKDAYS(K5,K6)</f>
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L4" s="3">
         <f ca="1" xml:space="preserve"> K3 / K4</f>
-        <v>5.4752066115702477E-2</v>
+        <v>5.4639175257731959E-2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="K6" s="1">
         <f ca="1">TODAY()</f>
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2684,11 +2684,11 @@
       </c>
       <c r="L9" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K9)</f>
-        <v>-453</v>
+        <v>-454</v>
       </c>
       <c r="M9" s="3">
         <f ca="1">($K$2 - $K$3) / L9</f>
-        <v>-0.20309050772626933</v>
+        <v>-0.20264317180616739</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -2715,11 +2715,11 @@
       </c>
       <c r="L10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K10)</f>
-        <v>-433</v>
+        <v>-434</v>
       </c>
       <c r="M10" s="3">
         <f ca="1">($K$2 - $K$3) / L10</f>
-        <v>-0.21247113163972287</v>
+        <v>-0.2119815668202765</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2746,11 +2746,11 @@
       </c>
       <c r="L11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K11)</f>
-        <v>-422</v>
+        <v>-423</v>
       </c>
       <c r="M11" s="3">
         <f ca="1">($K$2 - $K$3) / L11</f>
-        <v>-0.21800947867298578</v>
+        <v>-0.21749408983451538</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -4265,12 +4265,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{224174C6-79B8-40DF-BFBC-1FA41083861E}">
   <dimension ref="B3:E27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="33" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:5">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="C3">
         <f>SUM(作業工数見積もり!F3:F103)</f>
-        <v>46</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="4" spans="2:5">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -4343,11 +4343,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-453</v>
+        <v>-454</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.10154525386313466</v>
+        <v>-0.11784140969162996</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -4360,11 +4360,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-433</v>
+        <v>-434</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.10623556581986143</v>
+        <v>-0.12327188940092165</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -4377,11 +4377,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-422</v>
+        <v>-423</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.10900473933649289</v>
+        <v>-0.12647754137115838</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -4466,19 +4466,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:M77"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="32.7109375" style="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.85546875" style="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.140625" style="21" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" style="28" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" style="28" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.42578125" style="28" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" style="28" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.75" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.875" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.125" style="21" customWidth="1"/>
+    <col min="4" max="4" width="11.75" style="28" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.25" style="28" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.375" style="28" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.25" style="28" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="21"/>
-    <col min="10" max="10" width="15.5703125" style="21" customWidth="1"/>
+    <col min="10" max="10" width="15.625" style="21" customWidth="1"/>
     <col min="11" max="11" width="33" style="21" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.28515625" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.25" style="21" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="19" style="21" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="21"/>
   </cols>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="L12" s="21">
         <f>SUM(F3:F77)</f>
-        <v>46</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="13" spans="2:13">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="L13" s="21">
         <f>1*L12</f>
-        <v>46</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="14" spans="2:13">
@@ -5672,6 +5672,9 @@
       <c r="E54" s="28" t="s">
         <v>34</v>
       </c>
+      <c r="F54" s="28">
+        <v>2</v>
+      </c>
       <c r="H54" s="28" t="s">
         <v>136</v>
       </c>
@@ -5692,6 +5695,9 @@
       <c r="E55" s="28" t="s">
         <v>34</v>
       </c>
+      <c r="F55" s="28">
+        <v>2</v>
+      </c>
       <c r="H55" s="28" t="s">
         <v>136</v>
       </c>
@@ -5712,6 +5718,9 @@
       <c r="E56" s="28" t="s">
         <v>18</v>
       </c>
+      <c r="F56" s="28">
+        <v>1</v>
+      </c>
       <c r="H56" s="28" t="s">
         <v>136</v>
       </c>
@@ -5732,6 +5741,9 @@
       <c r="E57" s="28" t="s">
         <v>18</v>
       </c>
+      <c r="F57" s="28">
+        <v>1</v>
+      </c>
       <c r="H57" s="28" t="s">
         <v>136</v>
       </c>
@@ -5752,6 +5764,9 @@
       <c r="E58" s="28" t="s">
         <v>18</v>
       </c>
+      <c r="F58" s="28">
+        <v>0.5</v>
+      </c>
       <c r="H58" s="28" t="s">
         <v>136</v>
       </c>
@@ -5795,6 +5810,9 @@
       <c r="E60" s="28" t="s">
         <v>34</v>
       </c>
+      <c r="F60" s="28">
+        <v>0.5</v>
+      </c>
       <c r="H60" s="28" t="s">
         <v>136</v>
       </c>
@@ -5815,6 +5833,9 @@
       <c r="E61" s="28" t="s">
         <v>34</v>
       </c>
+      <c r="F61" s="28">
+        <v>0.5</v>
+      </c>
       <c r="H61" s="28" t="s">
         <v>136</v>
       </c>
@@ -6022,7 +6043,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="72" spans="2:9" ht="18.75">
+    <row r="72" spans="2:9">
       <c r="B72" s="44" t="s">
         <v>195</v>
       </c>
@@ -6152,7 +6173,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402AEDD2-674B-437A-B1BD-39BBE1464A75}">
   <dimension ref="B2:H10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="2:8">
       <c r="B2" s="52" t="s">
@@ -6347,14 +6368,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6593,21 +6612,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6632,9 +6650,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/コスト表.xlsx
+++ b/コスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tamari\Documents\GitHub\koukiteam\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kubotananato\Documents\GitHub\koukiteam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED1B077D-837E-419F-B36E-F7884CB00317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14CCB498-180E-4D42-9B76-B2F06D684E27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2460" yWindow="1995" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1125_元データ" sheetId="4" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="243">
   <si>
     <t>1コスト:3時間 (1日は基本2コスト)</t>
     <phoneticPr fontId="1"/>
@@ -1806,6 +1806,12 @@
       <t>ニチ</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>完了</t>
+  </si>
+  <si>
+    <t>作業中</t>
   </si>
 </sst>
 </file>
@@ -2575,11 +2581,11 @@
       </c>
       <c r="K4" s="2">
         <f ca="1">NETWORKDAYS(K5,K6)</f>
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L4" s="3">
         <f ca="1" xml:space="preserve"> K3 / K4</f>
-        <v>5.4639175257731959E-2</v>
+        <v>5.4526748971193417E-2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2619,7 +2625,7 @@
       </c>
       <c r="K6" s="1">
         <f ca="1">TODAY()</f>
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2684,11 +2690,11 @@
       </c>
       <c r="L9" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K9)</f>
-        <v>-454</v>
+        <v>-455</v>
       </c>
       <c r="M9" s="3">
         <f ca="1">($K$2 - $K$3) / L9</f>
-        <v>-0.20264317180616739</v>
+        <v>-0.2021978021978022</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -2715,11 +2721,11 @@
       </c>
       <c r="L10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K10)</f>
-        <v>-434</v>
+        <v>-435</v>
       </c>
       <c r="M10" s="3">
         <f ca="1">($K$2 - $K$3) / L10</f>
-        <v>-0.2119815668202765</v>
+        <v>-0.21149425287356322</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2746,11 +2752,11 @@
       </c>
       <c r="L11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K11)</f>
-        <v>-423</v>
+        <v>-424</v>
       </c>
       <c r="M11" s="3">
         <f ca="1">($K$2 - $K$3) / L11</f>
-        <v>-0.21749408983451538</v>
+        <v>-0.21698113207547171</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -4288,7 +4294,7 @@
       </c>
       <c r="C4">
         <f>SUMIF(作業工数見積もり!H3:H46,"完了",作業工数見積もり!F3:F46)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -4300,11 +4306,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>0</v>
+        <v>4.11522633744856E-3</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -4322,7 +4328,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -4343,11 +4349,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-454</v>
+        <v>-455</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.11123348017621146</v>
+        <v>-0.10659340659340659</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -4360,11 +4366,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-434</v>
+        <v>-435</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.11635944700460829</v>
+        <v>-0.11149425287356322</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -4377,11 +4383,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-423</v>
+        <v>-424</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.11938534278959811</v>
+        <v>-0.11438679245283019</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -4657,11 +4663,11 @@
       </c>
       <c r="L8" s="39">
         <f>COUNTIF(H3:H77,K8)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" s="40">
         <f>L8/L3</f>
-        <v>0</v>
+        <v>2.7027027027027029E-2</v>
       </c>
     </row>
     <row r="9" spans="2:13">
@@ -4691,11 +4697,11 @@
       </c>
       <c r="L9" s="39">
         <f>COUNTIF(H3:H77,K9)</f>
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="M9" s="31">
         <f>(L9+L10)/L3</f>
-        <v>1.0135135135135136</v>
+        <v>0.98648648648648651</v>
       </c>
     </row>
     <row r="10" spans="2:13">
@@ -4719,7 +4725,7 @@
       </c>
       <c r="L10" s="21">
         <f>COUNTIF(H3:H77,K10)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="2:13">
@@ -4755,8 +4761,11 @@
       <c r="F12" s="28">
         <v>1</v>
       </c>
+      <c r="G12" s="28">
+        <v>0.5</v>
+      </c>
       <c r="H12" s="28" t="s">
-        <v>136</v>
+        <v>241</v>
       </c>
       <c r="I12" s="21" t="s">
         <v>215</v>
@@ -4785,8 +4794,11 @@
       <c r="F13" s="28">
         <v>1</v>
       </c>
+      <c r="G13" s="28">
+        <v>0.5</v>
+      </c>
       <c r="H13" s="28" t="s">
-        <v>136</v>
+        <v>241</v>
       </c>
       <c r="I13" s="21" t="s">
         <v>215</v>
@@ -4943,7 +4955,7 @@
         <v>3</v>
       </c>
       <c r="H19" s="28" t="s">
-        <v>136</v>
+        <v>242</v>
       </c>
       <c r="I19" s="21" t="s">
         <v>215</v>
@@ -4990,7 +5002,7 @@
         <v>4</v>
       </c>
       <c r="H21" s="28" t="s">
-        <v>136</v>
+        <v>242</v>
       </c>
       <c r="I21" s="21" t="s">
         <v>215</v>
@@ -6356,14 +6368,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6602,21 +6612,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6641,9 +6650,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/コスト表.xlsx
+++ b/コスト表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kubotananato\Documents\GitHub\koukiteam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14CCB498-180E-4D42-9B76-B2F06D684E27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA6C2CB6-5C5B-492B-B87B-1E81C5E920C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2460" yWindow="1995" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4470" yWindow="900" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1125_元データ" sheetId="4" r:id="rId1"/>
@@ -2581,11 +2581,11 @@
       </c>
       <c r="K4" s="2">
         <f ca="1">NETWORKDAYS(K5,K6)</f>
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="L4" s="3">
         <f ca="1" xml:space="preserve"> K3 / K4</f>
-        <v>5.4526748971193417E-2</v>
+        <v>5.3427419354838711E-2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="K6" s="1">
         <f ca="1">TODAY()</f>
-        <v>46282</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2690,11 +2690,11 @@
       </c>
       <c r="L9" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K9)</f>
-        <v>-455</v>
+        <v>-465</v>
       </c>
       <c r="M9" s="3">
         <f ca="1">($K$2 - $K$3) / L9</f>
-        <v>-0.2021978021978022</v>
+        <v>-0.19784946236559139</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -2721,11 +2721,11 @@
       </c>
       <c r="L10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K10)</f>
-        <v>-435</v>
+        <v>-445</v>
       </c>
       <c r="M10" s="3">
         <f ca="1">($K$2 - $K$3) / L10</f>
-        <v>-0.21149425287356322</v>
+        <v>-0.20674157303370785</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2752,11 +2752,11 @@
       </c>
       <c r="L11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K11)</f>
-        <v>-424</v>
+        <v>-434</v>
       </c>
       <c r="M11" s="3">
         <f ca="1">($K$2 - $K$3) / L11</f>
-        <v>-0.21698113207547171</v>
+        <v>-0.2119815668202765</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="C4">
         <f>SUMIF(作業工数見積もり!H3:H46,"完了",作業工数見積もり!F3:F46)</f>
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -4306,11 +4306,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>4.11522633744856E-3</v>
+        <v>2.2177419354838711E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46282</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -4349,11 +4349,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-455</v>
+        <v>-465</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.10659340659340659</v>
+        <v>-8.4946236559139784E-2</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -4366,11 +4366,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-435</v>
+        <v>-445</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.11149425287356322</v>
+        <v>-8.8764044943820231E-2</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -4383,11 +4383,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-424</v>
+        <v>-434</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.11438679245283019</v>
+        <v>-9.1013824884792621E-2</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -4663,11 +4663,11 @@
       </c>
       <c r="L8" s="39">
         <f>COUNTIF(H3:H77,K8)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M8" s="40">
         <f>L8/L3</f>
-        <v>2.7027027027027029E-2</v>
+        <v>8.1081081081081086E-2</v>
       </c>
     </row>
     <row r="9" spans="2:13">
@@ -4697,11 +4697,11 @@
       </c>
       <c r="L9" s="39">
         <f>COUNTIF(H3:H77,K9)</f>
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="M9" s="31">
         <f>(L9+L10)/L3</f>
-        <v>0.98648648648648651</v>
+        <v>0.93243243243243246</v>
       </c>
     </row>
     <row r="10" spans="2:13">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="L10" s="21">
         <f>COUNTIF(H3:H77,K10)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="2:13">
@@ -4827,8 +4827,11 @@
       <c r="F14" s="28">
         <v>4</v>
       </c>
+      <c r="G14" s="28">
+        <v>2</v>
+      </c>
       <c r="H14" s="28" t="s">
-        <v>136</v>
+        <v>241</v>
       </c>
       <c r="I14" s="21" t="s">
         <v>215</v>
@@ -4954,8 +4957,11 @@
       <c r="F19" s="28">
         <v>3</v>
       </c>
+      <c r="G19" s="28">
+        <v>2</v>
+      </c>
       <c r="H19" s="28" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I19" s="21" t="s">
         <v>215</v>
@@ -5024,8 +5030,11 @@
       <c r="F22" s="28">
         <v>1</v>
       </c>
+      <c r="G22" s="28">
+        <v>0.5</v>
+      </c>
       <c r="H22" s="28" t="s">
-        <v>136</v>
+        <v>241</v>
       </c>
       <c r="I22" s="21" t="s">
         <v>215</v>
@@ -5064,8 +5073,11 @@
       <c r="F24" s="28">
         <v>1</v>
       </c>
+      <c r="G24" s="28">
+        <v>0.5</v>
+      </c>
       <c r="H24" s="28" t="s">
-        <v>136</v>
+        <v>241</v>
       </c>
       <c r="I24" s="21" t="s">
         <v>215</v>
@@ -6368,12 +6380,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6612,20 +6626,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6650,12 +6665,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/コスト表.xlsx
+++ b/コスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kubotananato\Documents\GitHub\koukiteam\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FukudaGenki\Documents\GitHub\koukiteam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA6C2CB6-5C5B-492B-B87B-1E81C5E920C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB38560B-65EE-45D1-A659-E8DB0CFCE9DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4470" yWindow="900" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="930" yWindow="1335" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1125_元データ" sheetId="4" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="244">
   <si>
     <t>1コスト:3時間 (1日は基本2コスト)</t>
     <phoneticPr fontId="1"/>
@@ -1812,6 +1812,13 @@
   </si>
   <si>
     <t>作業中</t>
+  </si>
+  <si>
+    <t>全員</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンイン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -1819,20 +1826,20 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="177" formatCode="0.000"/>
   </numFmts>
   <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="Calibri"/>
+      <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1841,14 +1848,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1856,7 +1863,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1864,7 +1871,7 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1872,7 +1879,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1880,7 +1887,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1892,7 +1899,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="27">
+  <fills count="29">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2049,6 +2056,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -2121,11 +2140,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2196,6 +2215,10 @@
     <xf numFmtId="0" fontId="0" fillId="26" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -2492,18 +2515,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1662411A-9E28-47BA-80A0-FB5B8EEC7CF8}">
   <dimension ref="A1:M106"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" style="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.5703125" customWidth="1"/>
-    <col min="9" max="9" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.75" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.25" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.625" customWidth="1"/>
+    <col min="9" max="9" width="7.125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="33" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.25" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2581,11 +2604,11 @@
       </c>
       <c r="K4" s="2">
         <f ca="1">NETWORKDAYS(K5,K6)</f>
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="L4" s="3">
         <f ca="1" xml:space="preserve"> K3 / K4</f>
-        <v>5.3427419354838711E-2</v>
+        <v>5.289421157684631E-2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2625,7 +2648,7 @@
       </c>
       <c r="K6" s="1">
         <f ca="1">TODAY()</f>
-        <v>46296</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2690,11 +2713,11 @@
       </c>
       <c r="L9" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K9)</f>
-        <v>-465</v>
+        <v>-470</v>
       </c>
       <c r="M9" s="3">
         <f ca="1">($K$2 - $K$3) / L9</f>
-        <v>-0.19784946236559139</v>
+        <v>-0.19574468085106383</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -2721,11 +2744,11 @@
       </c>
       <c r="L10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K10)</f>
-        <v>-445</v>
+        <v>-450</v>
       </c>
       <c r="M10" s="3">
         <f ca="1">($K$2 - $K$3) / L10</f>
-        <v>-0.20674157303370785</v>
+        <v>-0.20444444444444446</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2752,11 +2775,11 @@
       </c>
       <c r="L11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K11)</f>
-        <v>-434</v>
+        <v>-439</v>
       </c>
       <c r="M11" s="3">
         <f ca="1">($K$2 - $K$3) / L11</f>
-        <v>-0.2119815668202765</v>
+        <v>-0.20956719817767655</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -4271,12 +4294,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{224174C6-79B8-40DF-BFBC-1FA41083861E}">
   <dimension ref="B3:E27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="33" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:5">
@@ -4285,7 +4308,7 @@
       </c>
       <c r="C3">
         <f>SUM(作業工数見積もり!F3:F103)</f>
-        <v>50.5</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="4" spans="2:5">
@@ -4294,7 +4317,7 @@
       </c>
       <c r="C4">
         <f>SUMIF(作業工数見積もり!H3:H46,"完了",作業工数見積もり!F3:F46)</f>
-        <v>11</v>
+        <v>27.5</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -4306,11 +4329,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>2.2177419354838711E-2</v>
+        <v>5.4890219560878244E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -4328,7 +4351,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46296</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -4349,11 +4372,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-465</v>
+        <v>-470</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-8.4946236559139784E-2</v>
+        <v>-9.3617021276595741E-2</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -4366,11 +4389,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-445</v>
+        <v>-450</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-8.8764044943820231E-2</v>
+        <v>-9.7777777777777783E-2</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -4383,11 +4406,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-434</v>
+        <v>-439</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-9.1013824884792621E-2</v>
+        <v>-0.10022779043280182</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -4471,20 +4494,21 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A2:M77"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="32.7109375" style="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.85546875" style="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.140625" style="21" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" style="28" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" style="28" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.42578125" style="28" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" style="28" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.75" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.875" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.125" style="21" customWidth="1"/>
+    <col min="4" max="4" width="11.75" style="28" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.25" style="28" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.375" style="28" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.25" style="28" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="21"/>
-    <col min="10" max="10" width="15.5703125" style="21" customWidth="1"/>
+    <col min="10" max="10" width="15.625" style="21" customWidth="1"/>
     <col min="11" max="11" width="33" style="21" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.28515625" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.25" style="21" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="19" style="21" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="21"/>
   </cols>
@@ -4515,7 +4539,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="3" spans="2:13">
+    <row r="3" spans="2:13" hidden="1">
       <c r="B3" s="43" t="s">
         <v>137</v>
       </c>
@@ -4530,6 +4554,9 @@
       </c>
       <c r="H3" s="28" t="s">
         <v>136</v>
+      </c>
+      <c r="I3" s="21" t="s">
+        <v>216</v>
       </c>
       <c r="K3" s="34" t="s">
         <v>132</v>
@@ -4539,7 +4566,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="2:13">
+    <row r="4" spans="2:13" hidden="1">
       <c r="B4" s="43" t="s">
         <v>137</v>
       </c>
@@ -4603,8 +4630,11 @@
       <c r="F6" s="28">
         <v>1</v>
       </c>
+      <c r="G6" s="28">
+        <v>1</v>
+      </c>
       <c r="H6" s="28" t="s">
-        <v>136</v>
+        <v>241</v>
       </c>
       <c r="I6" s="21" t="s">
         <v>214</v>
@@ -4633,8 +4663,11 @@
       <c r="F7" s="28">
         <v>1</v>
       </c>
+      <c r="G7" s="28">
+        <v>1</v>
+      </c>
       <c r="H7" s="28" t="s">
-        <v>136</v>
+        <v>241</v>
       </c>
       <c r="I7" s="21" t="s">
         <v>214</v>
@@ -4642,7 +4675,7 @@
       <c r="K7" s="37"/>
       <c r="L7" s="39"/>
     </row>
-    <row r="8" spans="2:13">
+    <row r="8" spans="2:13" hidden="1">
       <c r="B8" s="44" t="s">
         <v>159</v>
       </c>
@@ -4655,19 +4688,28 @@
       <c r="E8" s="28" t="s">
         <v>18</v>
       </c>
+      <c r="F8" s="28">
+        <v>1</v>
+      </c>
+      <c r="G8" s="28">
+        <v>1</v>
+      </c>
       <c r="H8" s="28" t="s">
         <v>136</v>
       </c>
+      <c r="I8" s="21" t="s">
+        <v>214</v>
+      </c>
       <c r="K8" s="32" t="s">
         <v>35</v>
       </c>
       <c r="L8" s="39">
         <f>COUNTIF(H3:H77,K8)</f>
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="M8" s="40">
         <f>L8/L3</f>
-        <v>8.1081081081081086E-2</v>
+        <v>0.3108108108108108</v>
       </c>
     </row>
     <row r="9" spans="2:13">
@@ -4686,8 +4728,11 @@
       <c r="F9" s="28">
         <v>1</v>
       </c>
+      <c r="G9" s="28">
+        <v>1</v>
+      </c>
       <c r="H9" s="28" t="s">
-        <v>136</v>
+        <v>241</v>
       </c>
       <c r="I9" s="21" t="s">
         <v>214</v>
@@ -4697,14 +4742,14 @@
       </c>
       <c r="L9" s="39">
         <f>COUNTIF(H3:H77,K9)</f>
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="M9" s="31">
         <f>(L9+L10)/L3</f>
-        <v>0.93243243243243246</v>
-      </c>
-    </row>
-    <row r="10" spans="2:13">
+        <v>0.70270270270270274</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13" hidden="1">
       <c r="B10" s="44" t="s">
         <v>159</v>
       </c>
@@ -4717,9 +4762,18 @@
       <c r="E10" s="28" t="s">
         <v>18</v>
       </c>
+      <c r="F10" s="28">
+        <v>1</v>
+      </c>
+      <c r="G10" s="28">
+        <v>1</v>
+      </c>
       <c r="H10" s="28" t="s">
         <v>136</v>
       </c>
+      <c r="I10" s="21" t="s">
+        <v>214</v>
+      </c>
       <c r="K10" s="34" t="s">
         <v>134</v>
       </c>
@@ -4728,7 +4782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="2:13">
+    <row r="11" spans="2:13" hidden="1">
       <c r="B11" s="44" t="s">
         <v>159</v>
       </c>
@@ -4741,8 +4795,17 @@
       <c r="E11" s="28" t="s">
         <v>18</v>
       </c>
+      <c r="F11" s="28">
+        <v>1</v>
+      </c>
+      <c r="G11" s="28">
+        <v>1</v>
+      </c>
       <c r="H11" s="28" t="s">
         <v>136</v>
+      </c>
+      <c r="I11" s="21" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="12" spans="2:13">
@@ -4775,7 +4838,7 @@
       </c>
       <c r="L12" s="21">
         <f>SUM(F3:F77)</f>
-        <v>50.5</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="13" spans="2:13">
@@ -4808,7 +4871,7 @@
       </c>
       <c r="L13" s="21">
         <f>1*L12</f>
-        <v>50.5</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="14" spans="2:13">
@@ -4866,10 +4929,10 @@
       </c>
       <c r="L15" s="21">
         <f>COUNTIF(I3:I77, K15)</f>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="2:13">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13" hidden="1">
       <c r="B16" s="45" t="s">
         <v>141</v>
       </c>
@@ -4885,15 +4948,18 @@
       <c r="H16" s="28" t="s">
         <v>136</v>
       </c>
+      <c r="I16" s="21" t="s">
+        <v>215</v>
+      </c>
       <c r="K16" s="21" t="s">
         <v>230</v>
       </c>
       <c r="L16" s="21">
         <f>COUNTIF(I3:I77, K16)</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="2:12">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" hidden="1">
       <c r="B17" s="45" t="s">
         <v>141</v>
       </c>
@@ -4909,15 +4975,18 @@
       <c r="H17" s="28" t="s">
         <v>136</v>
       </c>
+      <c r="I17" s="21" t="s">
+        <v>215</v>
+      </c>
       <c r="K17" s="21" t="s">
         <v>231</v>
       </c>
       <c r="L17" s="21">
         <f>COUNTIF(I3:I77, K17)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="2:12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" hidden="1">
       <c r="B18" s="45" t="s">
         <v>141</v>
       </c>
@@ -4932,6 +5001,9 @@
       </c>
       <c r="H18" s="28" t="s">
         <v>136</v>
+      </c>
+      <c r="I18" s="21" t="s">
+        <v>215</v>
       </c>
       <c r="K18" s="21" t="s">
         <v>232</v>
@@ -4971,10 +5043,10 @@
       </c>
       <c r="L19" s="21">
         <f>COUNTIF(I3:I77, K19)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="2:12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" hidden="1">
       <c r="B20" s="45" t="s">
         <v>141</v>
       </c>
@@ -4989,6 +5061,9 @@
       </c>
       <c r="H20" s="28" t="s">
         <v>136</v>
+      </c>
+      <c r="I20" s="21" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="21" spans="2:12">
@@ -5040,7 +5115,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="23" spans="2:12">
+    <row r="23" spans="2:12" hidden="1">
       <c r="B23" s="45" t="s">
         <v>141</v>
       </c>
@@ -5055,6 +5130,9 @@
       </c>
       <c r="H23" s="28" t="s">
         <v>136</v>
+      </c>
+      <c r="I23" s="21" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="24" spans="2:12">
@@ -5083,7 +5161,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="25" spans="2:12">
+    <row r="25" spans="2:12" hidden="1">
       <c r="B25" s="45" t="s">
         <v>141</v>
       </c>
@@ -5099,8 +5177,11 @@
       <c r="H25" s="28" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="26" spans="2:12">
+      <c r="I25" s="21" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" hidden="1">
       <c r="B26" s="45" t="s">
         <v>141</v>
       </c>
@@ -5115,6 +5196,9 @@
       </c>
       <c r="H26" s="28" t="s">
         <v>136</v>
+      </c>
+      <c r="I26" s="21" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="27" spans="2:12">
@@ -5133,8 +5217,11 @@
       <c r="F27" s="28">
         <v>1</v>
       </c>
+      <c r="G27" s="28">
+        <v>1</v>
+      </c>
       <c r="H27" s="28" t="s">
-        <v>136</v>
+        <v>241</v>
       </c>
       <c r="I27" s="21" t="s">
         <v>214</v>
@@ -5156,8 +5243,11 @@
       <c r="F28" s="28">
         <v>1</v>
       </c>
+      <c r="G28" s="28">
+        <v>1</v>
+      </c>
       <c r="H28" s="28" t="s">
-        <v>136</v>
+        <v>241</v>
       </c>
       <c r="I28" s="21" t="s">
         <v>214</v>
@@ -5179,8 +5269,11 @@
       <c r="F29" s="28">
         <v>1</v>
       </c>
+      <c r="G29" s="28">
+        <v>1</v>
+      </c>
       <c r="H29" s="28" t="s">
-        <v>136</v>
+        <v>241</v>
       </c>
       <c r="I29" s="21" t="s">
         <v>214</v>
@@ -5202,8 +5295,11 @@
       <c r="F30" s="28">
         <v>0.5</v>
       </c>
+      <c r="G30" s="28">
+        <v>0.5</v>
+      </c>
       <c r="H30" s="28" t="s">
-        <v>136</v>
+        <v>241</v>
       </c>
       <c r="I30" s="21" t="s">
         <v>214</v>
@@ -5225,14 +5321,17 @@
       <c r="F31" s="28">
         <v>0.5</v>
       </c>
+      <c r="G31" s="28">
+        <v>0.5</v>
+      </c>
       <c r="H31" s="28" t="s">
-        <v>136</v>
+        <v>241</v>
       </c>
       <c r="I31" s="21" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="32" spans="2:12">
+    <row r="32" spans="2:12" hidden="1">
       <c r="B32" s="46" t="s">
         <v>152</v>
       </c>
@@ -5245,11 +5344,20 @@
       <c r="E32" s="28" t="s">
         <v>18</v>
       </c>
+      <c r="F32" s="28">
+        <v>1</v>
+      </c>
+      <c r="G32" s="28">
+        <v>1</v>
+      </c>
       <c r="H32" s="28" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="33" spans="2:9">
+      <c r="I32" s="21" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" hidden="1">
       <c r="B33" s="46" t="s">
         <v>152</v>
       </c>
@@ -5262,8 +5370,17 @@
       <c r="E33" s="28" t="s">
         <v>18</v>
       </c>
+      <c r="F33" s="28">
+        <v>1</v>
+      </c>
+      <c r="G33" s="28">
+        <v>1</v>
+      </c>
       <c r="H33" s="28" t="s">
         <v>136</v>
+      </c>
+      <c r="I33" s="21" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="34" spans="2:9">
@@ -5282,14 +5399,17 @@
       <c r="F34" s="28">
         <v>0.5</v>
       </c>
+      <c r="G34" s="28">
+        <v>0.5</v>
+      </c>
       <c r="H34" s="28" t="s">
-        <v>136</v>
+        <v>241</v>
       </c>
       <c r="I34" s="21" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="35" spans="2:9">
+    <row r="35" spans="2:9" hidden="1">
       <c r="B35" s="46" t="s">
         <v>152</v>
       </c>
@@ -5302,8 +5422,17 @@
       <c r="E35" s="28" t="s">
         <v>18</v>
       </c>
+      <c r="F35" s="28">
+        <v>2</v>
+      </c>
+      <c r="G35" s="28">
+        <v>2</v>
+      </c>
       <c r="H35" s="28" t="s">
         <v>136</v>
+      </c>
+      <c r="I35" s="21" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="36" spans="2:9">
@@ -5329,7 +5458,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="37" spans="2:9">
+    <row r="37" spans="2:9" hidden="1">
       <c r="B37" s="47" t="s">
         <v>165</v>
       </c>
@@ -5342,13 +5471,20 @@
       <c r="E37" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F37" s="21"/>
-      <c r="G37" s="21"/>
+      <c r="F37" s="17">
+        <v>1</v>
+      </c>
+      <c r="G37" s="17">
+        <v>1</v>
+      </c>
       <c r="H37" s="28" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="38" spans="2:9">
+      <c r="I37" s="21" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" hidden="1">
       <c r="B38" s="47" t="s">
         <v>165</v>
       </c>
@@ -5361,13 +5497,20 @@
       <c r="E38" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F38" s="21"/>
-      <c r="G38" s="21"/>
+      <c r="F38" s="17">
+        <v>2</v>
+      </c>
+      <c r="G38" s="17">
+        <v>2</v>
+      </c>
       <c r="H38" s="28" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="39" spans="2:9">
+      <c r="I38" s="21" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" hidden="1">
       <c r="B39" s="47" t="s">
         <v>165</v>
       </c>
@@ -5380,13 +5523,20 @@
       <c r="E39" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F39" s="21"/>
-      <c r="G39" s="21"/>
+      <c r="F39" s="17">
+        <v>1</v>
+      </c>
+      <c r="G39" s="17">
+        <v>1</v>
+      </c>
       <c r="H39" s="28" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="40" spans="2:9">
+      <c r="I39" s="21" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" hidden="1">
       <c r="B40" s="47" t="s">
         <v>165</v>
       </c>
@@ -5399,13 +5549,20 @@
       <c r="E40" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F40" s="21"/>
-      <c r="G40" s="21"/>
+      <c r="F40" s="17">
+        <v>2</v>
+      </c>
+      <c r="G40" s="17">
+        <v>2</v>
+      </c>
       <c r="H40" s="28" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="41" spans="2:9">
+      <c r="I40" s="21" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" hidden="1">
       <c r="B41" s="47" t="s">
         <v>165</v>
       </c>
@@ -5418,8 +5575,17 @@
       <c r="E41" s="28" t="s">
         <v>18</v>
       </c>
+      <c r="F41" s="28">
+        <v>3</v>
+      </c>
+      <c r="G41" s="28">
+        <v>3</v>
+      </c>
       <c r="H41" s="28" t="s">
         <v>136</v>
+      </c>
+      <c r="I41" s="21" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="42" spans="2:9">
@@ -5438,8 +5604,11 @@
       <c r="F42" s="28">
         <v>2</v>
       </c>
+      <c r="G42" s="28">
+        <v>2</v>
+      </c>
       <c r="H42" s="28" t="s">
-        <v>136</v>
+        <v>241</v>
       </c>
       <c r="I42" s="21" t="s">
         <v>214</v>
@@ -5461,8 +5630,11 @@
       <c r="F43" s="28">
         <v>2</v>
       </c>
+      <c r="G43" s="28">
+        <v>2</v>
+      </c>
       <c r="H43" s="28" t="s">
-        <v>136</v>
+        <v>241</v>
       </c>
       <c r="I43" s="21" t="s">
         <v>214</v>
@@ -5484,8 +5656,11 @@
       <c r="F44" s="28">
         <v>2</v>
       </c>
+      <c r="G44" s="28">
+        <v>2</v>
+      </c>
       <c r="H44" s="28" t="s">
-        <v>136</v>
+        <v>241</v>
       </c>
       <c r="I44" s="21" t="s">
         <v>214</v>
@@ -5507,8 +5682,11 @@
       <c r="F45" s="28">
         <v>1</v>
       </c>
+      <c r="G45" s="28">
+        <v>1</v>
+      </c>
       <c r="H45" s="28" t="s">
-        <v>136</v>
+        <v>241</v>
       </c>
       <c r="I45" s="21" t="s">
         <v>214</v>
@@ -5530,8 +5708,11 @@
       <c r="F46" s="28">
         <v>2</v>
       </c>
+      <c r="G46" s="28">
+        <v>2</v>
+      </c>
       <c r="H46" s="28" t="s">
-        <v>136</v>
+        <v>241</v>
       </c>
       <c r="I46" s="21" t="s">
         <v>214</v>
@@ -5553,14 +5734,17 @@
       <c r="F47" s="28">
         <v>1</v>
       </c>
+      <c r="G47" s="28">
+        <v>1</v>
+      </c>
       <c r="H47" s="28" t="s">
-        <v>136</v>
+        <v>241</v>
       </c>
       <c r="I47" s="21" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="48" spans="2:9">
+    <row r="48" spans="2:9" hidden="1">
       <c r="B48" s="48" t="s">
         <v>167</v>
       </c>
@@ -5573,11 +5757,20 @@
       <c r="E48" s="28" t="s">
         <v>18</v>
       </c>
+      <c r="F48" s="28">
+        <v>2</v>
+      </c>
+      <c r="G48" s="28">
+        <v>2</v>
+      </c>
       <c r="H48" s="28" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="49" spans="1:9">
+      <c r="I48" s="21" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" hidden="1">
       <c r="B49" s="48" t="s">
         <v>167</v>
       </c>
@@ -5590,8 +5783,17 @@
       <c r="E49" s="28" t="s">
         <v>18</v>
       </c>
+      <c r="F49" s="28">
+        <v>3</v>
+      </c>
+      <c r="G49" s="28">
+        <v>3</v>
+      </c>
       <c r="H49" s="28" t="s">
-        <v>136</v>
+        <v>241</v>
+      </c>
+      <c r="I49" s="21" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -5685,8 +5887,11 @@
       <c r="F53" s="28">
         <v>2</v>
       </c>
+      <c r="G53" s="28">
+        <v>2</v>
+      </c>
       <c r="H53" s="28" t="s">
-        <v>136</v>
+        <v>241</v>
       </c>
       <c r="I53" s="21" t="s">
         <v>224</v>
@@ -5732,7 +5937,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" hidden="1">
       <c r="B56" s="29" t="s">
         <v>181</v>
       </c>
@@ -5752,7 +5957,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:9" hidden="1">
       <c r="B57" s="29" t="s">
         <v>181</v>
       </c>
@@ -5772,7 +5977,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:9" hidden="1">
       <c r="B58" s="29" t="s">
         <v>181</v>
       </c>
@@ -5792,7 +5997,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:9" hidden="1">
       <c r="B59" s="29" t="s">
         <v>181</v>
       </c>
@@ -5924,7 +6129,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="65" spans="2:9">
+    <row r="65" spans="2:9" hidden="1">
       <c r="B65" s="43" t="s">
         <v>186</v>
       </c>
@@ -5987,7 +6192,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="68" spans="2:9">
+    <row r="68" spans="2:9" hidden="1">
       <c r="B68" s="43" t="s">
         <v>186</v>
       </c>
@@ -6003,8 +6208,11 @@
       <c r="H68" s="28" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="69" spans="2:9">
+      <c r="I68" s="21" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="69" spans="2:9" hidden="1">
       <c r="B69" s="44" t="s">
         <v>195</v>
       </c>
@@ -6020,8 +6228,11 @@
       <c r="H69" s="28" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="70" spans="2:9">
+      <c r="I69" s="21" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="70" spans="2:9" hidden="1">
       <c r="B70" s="44" t="s">
         <v>195</v>
       </c>
@@ -6037,8 +6248,11 @@
       <c r="H70" s="28" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="71" spans="2:9">
+      <c r="I70" s="21" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="71" spans="2:9" hidden="1">
       <c r="B71" s="44" t="s">
         <v>195</v>
       </c>
@@ -6054,8 +6268,11 @@
       <c r="H71" s="28" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="72" spans="2:9" ht="18.75">
+      <c r="I71" s="21" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="72" spans="2:9" hidden="1">
       <c r="B72" s="44" t="s">
         <v>195</v>
       </c>
@@ -6071,8 +6288,11 @@
       <c r="H72" s="28" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="73" spans="2:9">
+      <c r="I72" s="21" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="73" spans="2:9" hidden="1">
       <c r="B73" s="51" t="s">
         <v>199</v>
       </c>
@@ -6088,8 +6308,11 @@
       <c r="H73" s="28" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="74" spans="2:9">
+      <c r="I73" s="21" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="74" spans="2:9" hidden="1">
       <c r="B74" s="51" t="s">
         <v>199</v>
       </c>
@@ -6107,8 +6330,11 @@
       <c r="H74" s="28" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="75" spans="2:9">
+      <c r="I74" s="21" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="75" spans="2:9" hidden="1">
       <c r="B75" s="51" t="s">
         <v>199</v>
       </c>
@@ -6126,8 +6352,11 @@
       <c r="H75" s="28" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="76" spans="2:9">
+      <c r="I75" s="21" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="76" spans="2:9" hidden="1">
       <c r="B76" s="51" t="s">
         <v>199</v>
       </c>
@@ -6145,8 +6374,11 @@
       <c r="H76" s="28" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="77" spans="2:9">
+      <c r="I76" s="21" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="77" spans="2:9" hidden="1">
       <c r="B77" s="51" t="s">
         <v>199</v>
       </c>
@@ -6162,9 +6394,18 @@
       <c r="H77" s="28" t="s">
         <v>136</v>
       </c>
+      <c r="I77" s="21" t="s">
+        <v>243</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:I77" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:I77" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="プロト"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H77" xr:uid="{E1CFE88F-4F87-4696-BE21-1133C2AEB8C1}">
@@ -6185,7 +6426,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402AEDD2-674B-437A-B1BD-39BBE1464A75}">
   <dimension ref="B2:H10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="2:8">
       <c r="B2" s="52" t="s">
@@ -6274,102 +6515,102 @@
       </c>
     </row>
     <row r="6" spans="2:8">
-      <c r="B6">
+      <c r="B6" s="53">
         <v>20</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="53">
         <v>21</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="53">
         <v>22</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="53">
         <v>23</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="53">
         <v>24</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="53">
         <v>25</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="53">
         <v>26</v>
       </c>
     </row>
     <row r="7" spans="2:8">
-      <c r="B7">
+      <c r="B7" s="53">
         <v>27</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="53">
         <v>28</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="53">
         <v>29</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="53">
         <v>30</v>
       </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7">
+      <c r="F7" s="54">
+        <v>1</v>
+      </c>
+      <c r="G7" s="54">
         <v>2</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="54">
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="2:8">
-      <c r="B8">
+      <c r="B8" s="54">
         <v>4</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="54">
         <v>5</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="54">
         <v>6</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="54">
         <v>7</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="54">
         <v>8</v>
       </c>
-      <c r="G8">
-        <v>9</v>
-      </c>
-      <c r="H8">
+      <c r="G8" s="54">
+        <v>9</v>
+      </c>
+      <c r="H8" s="54">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="2:8">
-      <c r="B9">
+      <c r="B9" s="54">
         <v>11</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="54">
         <v>12</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="54">
         <v>13</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="54">
         <v>14</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="54">
         <v>15</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="55">
         <v>16</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="55">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="2:8">
-      <c r="B10">
-        <v>18</v>
-      </c>
-      <c r="C10">
+      <c r="B10" s="56">
+        <v>18</v>
+      </c>
+      <c r="C10" s="57">
         <v>19</v>
       </c>
     </row>
@@ -6380,14 +6621,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6626,21 +6865,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6665,9 +6903,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/コスト表.xlsx
+++ b/コスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FukudaGenki\Documents\GitHub\koukiteam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB38560B-65EE-45D1-A659-E8DB0CFCE9DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{161E2831-B923-4881-8A08-E7ADD7B8643B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="930" yWindow="1335" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1125_元データ" sheetId="4" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="244">
   <si>
     <t>1コスト:3時間 (1日は基本2コスト)</t>
     <phoneticPr fontId="1"/>
@@ -1811,12 +1811,16 @@
     <t>完了</t>
   </si>
   <si>
-    <t>作業中</t>
-  </si>
-  <si>
     <t>全員</t>
     <rPh sb="0" eb="2">
       <t>ゼンイン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→アルファへ移動</t>
+    <rPh sb="6" eb="8">
+      <t>イドウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4308,7 +4312,7 @@
       </c>
       <c r="C3">
         <f>SUM(作業工数見積もり!F3:F103)</f>
-        <v>71.5</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="2:5">
@@ -4317,7 +4321,7 @@
       </c>
       <c r="C4">
         <f>SUMIF(作業工数見積もり!H3:H46,"完了",作業工数見積もり!F3:F46)</f>
-        <v>27.5</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -4333,7 +4337,7 @@
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>5.4890219560878244E-2</v>
+        <v>6.5868263473053898E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -4376,7 +4380,7 @@
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-9.3617021276595741E-2</v>
+        <v>-0.12553191489361701</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -4393,7 +4397,7 @@
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-9.7777777777777783E-2</v>
+        <v>-0.13111111111111112</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -4410,7 +4414,7 @@
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.10022779043280182</v>
+        <v>-0.13439635535307518</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -4539,7 +4543,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="3" spans="2:13" hidden="1">
+    <row r="3" spans="2:13">
       <c r="B3" s="43" t="s">
         <v>137</v>
       </c>
@@ -4590,7 +4594,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="2:13">
+    <row r="5" spans="2:13" hidden="1">
       <c r="B5" s="43" t="s">
         <v>137</v>
       </c>
@@ -4604,7 +4608,7 @@
         <v>34</v>
       </c>
       <c r="H5" s="28" t="s">
-        <v>136</v>
+        <v>241</v>
       </c>
       <c r="K5" s="36" t="s">
         <v>1</v>
@@ -4614,7 +4618,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="2:13">
+    <row r="6" spans="2:13" hidden="1">
       <c r="B6" s="44" t="s">
         <v>159</v>
       </c>
@@ -4647,7 +4651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:13">
+    <row r="7" spans="2:13" hidden="1">
       <c r="B7" s="44" t="s">
         <v>159</v>
       </c>
@@ -4675,7 +4679,7 @@
       <c r="K7" s="37"/>
       <c r="L7" s="39"/>
     </row>
-    <row r="8" spans="2:13" hidden="1">
+    <row r="8" spans="2:13">
       <c r="B8" s="44" t="s">
         <v>159</v>
       </c>
@@ -4691,9 +4695,6 @@
       <c r="F8" s="28">
         <v>1</v>
       </c>
-      <c r="G8" s="28">
-        <v>1</v>
-      </c>
       <c r="H8" s="28" t="s">
         <v>136</v>
       </c>
@@ -4705,14 +4706,14 @@
       </c>
       <c r="L8" s="39">
         <f>COUNTIF(H3:H77,K8)</f>
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="M8" s="40">
         <f>L8/L3</f>
-        <v>0.3108108108108108</v>
-      </c>
-    </row>
-    <row r="9" spans="2:13">
+        <v>0.47297297297297297</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13" hidden="1">
       <c r="B9" s="44" t="s">
         <v>159</v>
       </c>
@@ -4742,14 +4743,14 @@
       </c>
       <c r="L9" s="39">
         <f>COUNTIF(H3:H77,K9)</f>
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="M9" s="31">
         <f>(L9+L10)/L3</f>
-        <v>0.70270270270270274</v>
-      </c>
-    </row>
-    <row r="10" spans="2:13" hidden="1">
+        <v>0.54054054054054057</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13">
       <c r="B10" s="44" t="s">
         <v>159</v>
       </c>
@@ -4765,9 +4766,6 @@
       <c r="F10" s="28">
         <v>1</v>
       </c>
-      <c r="G10" s="28">
-        <v>1</v>
-      </c>
       <c r="H10" s="28" t="s">
         <v>136</v>
       </c>
@@ -4779,10 +4777,10 @@
       </c>
       <c r="L10" s="21">
         <f>COUNTIF(H3:H77,K10)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="2:13" hidden="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13">
       <c r="B11" s="44" t="s">
         <v>159</v>
       </c>
@@ -4798,9 +4796,6 @@
       <c r="F11" s="28">
         <v>1</v>
       </c>
-      <c r="G11" s="28">
-        <v>1</v>
-      </c>
       <c r="H11" s="28" t="s">
         <v>136</v>
       </c>
@@ -4808,7 +4803,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="12" spans="2:13">
+    <row r="12" spans="2:13" hidden="1">
       <c r="B12" s="45" t="s">
         <v>141</v>
       </c>
@@ -4838,10 +4833,10 @@
       </c>
       <c r="L12" s="21">
         <f>SUM(F3:F77)</f>
-        <v>71.5</v>
-      </c>
-    </row>
-    <row r="13" spans="2:13">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" hidden="1">
       <c r="B13" s="45" t="s">
         <v>141</v>
       </c>
@@ -4871,10 +4866,10 @@
       </c>
       <c r="L13" s="21">
         <f>1*L12</f>
-        <v>71.5</v>
-      </c>
-    </row>
-    <row r="14" spans="2:13">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" hidden="1">
       <c r="B14" s="45" t="s">
         <v>141</v>
       </c>
@@ -4901,7 +4896,7 @@
       </c>
       <c r="J14" s="38"/>
     </row>
-    <row r="15" spans="2:13">
+    <row r="15" spans="2:13" hidden="1">
       <c r="B15" s="45" t="s">
         <v>141</v>
       </c>
@@ -4918,7 +4913,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="28" t="s">
-        <v>136</v>
+        <v>241</v>
       </c>
       <c r="I15" s="21" t="s">
         <v>215</v>
@@ -4932,7 +4927,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="2:13" hidden="1">
+    <row r="16" spans="2:13">
       <c r="B16" s="45" t="s">
         <v>141</v>
       </c>
@@ -4944,6 +4939,9 @@
       </c>
       <c r="E16" s="28" t="s">
         <v>18</v>
+      </c>
+      <c r="F16" s="28">
+        <v>2</v>
       </c>
       <c r="H16" s="28" t="s">
         <v>136</v>
@@ -4959,7 +4957,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="2:12" hidden="1">
+    <row r="17" spans="2:12">
       <c r="B17" s="45" t="s">
         <v>141</v>
       </c>
@@ -4972,6 +4970,9 @@
       <c r="E17" s="28" t="s">
         <v>18</v>
       </c>
+      <c r="F17" s="28">
+        <v>1</v>
+      </c>
       <c r="H17" s="28" t="s">
         <v>136</v>
       </c>
@@ -4983,10 +4984,10 @@
       </c>
       <c r="L17" s="21">
         <f>COUNTIF(I3:I77, K17)</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="2:12" hidden="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12">
       <c r="B18" s="45" t="s">
         <v>141</v>
       </c>
@@ -4998,6 +4999,9 @@
       </c>
       <c r="E18" s="28" t="s">
         <v>18</v>
+      </c>
+      <c r="F18" s="28">
+        <v>2</v>
       </c>
       <c r="H18" s="28" t="s">
         <v>136</v>
@@ -5013,7 +5017,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="2:12">
+    <row r="19" spans="2:12" hidden="1">
       <c r="B19" s="45" t="s">
         <v>141</v>
       </c>
@@ -5043,10 +5047,10 @@
       </c>
       <c r="L19" s="21">
         <f>COUNTIF(I3:I77, K19)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="2:12" hidden="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12">
       <c r="B20" s="45" t="s">
         <v>141</v>
       </c>
@@ -5059,6 +5063,9 @@
       <c r="E20" s="28" t="s">
         <v>18</v>
       </c>
+      <c r="F20" s="28">
+        <v>0.5</v>
+      </c>
       <c r="H20" s="28" t="s">
         <v>136</v>
       </c>
@@ -5066,7 +5073,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="21" spans="2:12">
+    <row r="21" spans="2:12" hidden="1">
       <c r="B21" s="45" t="s">
         <v>141</v>
       </c>
@@ -5083,13 +5090,13 @@
         <v>4</v>
       </c>
       <c r="H21" s="28" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I21" s="21" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="22" spans="2:12">
+    <row r="22" spans="2:12" hidden="1">
       <c r="B22" s="45" t="s">
         <v>141</v>
       </c>
@@ -5115,7 +5122,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="23" spans="2:12" hidden="1">
+    <row r="23" spans="2:12">
       <c r="B23" s="45" t="s">
         <v>141</v>
       </c>
@@ -5128,6 +5135,9 @@
       <c r="E23" s="28" t="s">
         <v>18</v>
       </c>
+      <c r="F23" s="28">
+        <v>2</v>
+      </c>
       <c r="H23" s="28" t="s">
         <v>136</v>
       </c>
@@ -5135,7 +5145,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="24" spans="2:12">
+    <row r="24" spans="2:12" hidden="1">
       <c r="B24" s="45" t="s">
         <v>141</v>
       </c>
@@ -5161,7 +5171,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="25" spans="2:12" hidden="1">
+    <row r="25" spans="2:12">
       <c r="B25" s="45" t="s">
         <v>141</v>
       </c>
@@ -5174,6 +5184,9 @@
       <c r="E25" s="28" t="s">
         <v>18</v>
       </c>
+      <c r="F25" s="28">
+        <v>0.5</v>
+      </c>
       <c r="H25" s="28" t="s">
         <v>136</v>
       </c>
@@ -5181,7 +5194,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="26" spans="2:12" hidden="1">
+    <row r="26" spans="2:12">
       <c r="B26" s="45" t="s">
         <v>141</v>
       </c>
@@ -5194,6 +5207,9 @@
       <c r="E26" s="28" t="s">
         <v>18</v>
       </c>
+      <c r="F26" s="28">
+        <v>2</v>
+      </c>
       <c r="H26" s="28" t="s">
         <v>136</v>
       </c>
@@ -5201,7 +5217,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="27" spans="2:12">
+    <row r="27" spans="2:12" hidden="1">
       <c r="B27" s="46" t="s">
         <v>152</v>
       </c>
@@ -5227,7 +5243,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="28" spans="2:12">
+    <row r="28" spans="2:12" hidden="1">
       <c r="B28" s="46" t="s">
         <v>152</v>
       </c>
@@ -5253,7 +5269,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="29" spans="2:12">
+    <row r="29" spans="2:12" hidden="1">
       <c r="B29" s="46" t="s">
         <v>152</v>
       </c>
@@ -5279,7 +5295,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="30" spans="2:12">
+    <row r="30" spans="2:12" hidden="1">
       <c r="B30" s="46" t="s">
         <v>152</v>
       </c>
@@ -5305,7 +5321,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="31" spans="2:12">
+    <row r="31" spans="2:12" hidden="1">
       <c r="B31" s="46" t="s">
         <v>152</v>
       </c>
@@ -5331,7 +5347,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="32" spans="2:12" hidden="1">
+    <row r="32" spans="2:12">
       <c r="B32" s="46" t="s">
         <v>152</v>
       </c>
@@ -5347,9 +5363,6 @@
       <c r="F32" s="28">
         <v>1</v>
       </c>
-      <c r="G32" s="28">
-        <v>1</v>
-      </c>
       <c r="H32" s="28" t="s">
         <v>136</v>
       </c>
@@ -5357,7 +5370,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="33" spans="2:9" hidden="1">
+    <row r="33" spans="2:9">
       <c r="B33" s="46" t="s">
         <v>152</v>
       </c>
@@ -5373,9 +5386,6 @@
       <c r="F33" s="28">
         <v>1</v>
       </c>
-      <c r="G33" s="28">
-        <v>1</v>
-      </c>
       <c r="H33" s="28" t="s">
         <v>136</v>
       </c>
@@ -5383,7 +5393,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="34" spans="2:9">
+    <row r="34" spans="2:9" hidden="1">
       <c r="B34" s="46" t="s">
         <v>152</v>
       </c>
@@ -5409,7 +5419,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="35" spans="2:9" hidden="1">
+    <row r="35" spans="2:9">
       <c r="B35" s="46" t="s">
         <v>152</v>
       </c>
@@ -5425,9 +5435,6 @@
       <c r="F35" s="28">
         <v>2</v>
       </c>
-      <c r="G35" s="28">
-        <v>2</v>
-      </c>
       <c r="H35" s="28" t="s">
         <v>136</v>
       </c>
@@ -5435,7 +5442,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="36" spans="2:9">
+    <row r="36" spans="2:9" hidden="1">
       <c r="B36" s="46" t="s">
         <v>152</v>
       </c>
@@ -5452,13 +5459,13 @@
         <v>0.5</v>
       </c>
       <c r="H36" s="28" t="s">
-        <v>136</v>
+        <v>241</v>
       </c>
       <c r="I36" s="21" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="37" spans="2:9" hidden="1">
+    <row r="37" spans="2:9">
       <c r="B37" s="47" t="s">
         <v>165</v>
       </c>
@@ -5474,9 +5481,7 @@
       <c r="F37" s="17">
         <v>1</v>
       </c>
-      <c r="G37" s="17">
-        <v>1</v>
-      </c>
+      <c r="G37" s="17"/>
       <c r="H37" s="28" t="s">
         <v>136</v>
       </c>
@@ -5484,7 +5489,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="38" spans="2:9" hidden="1">
+    <row r="38" spans="2:9">
       <c r="B38" s="47" t="s">
         <v>165</v>
       </c>
@@ -5500,9 +5505,7 @@
       <c r="F38" s="17">
         <v>2</v>
       </c>
-      <c r="G38" s="17">
-        <v>2</v>
-      </c>
+      <c r="G38" s="17"/>
       <c r="H38" s="28" t="s">
         <v>136</v>
       </c>
@@ -5510,7 +5513,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="39" spans="2:9" hidden="1">
+    <row r="39" spans="2:9">
       <c r="B39" s="47" t="s">
         <v>165</v>
       </c>
@@ -5526,9 +5529,7 @@
       <c r="F39" s="17">
         <v>1</v>
       </c>
-      <c r="G39" s="17">
-        <v>1</v>
-      </c>
+      <c r="G39" s="17"/>
       <c r="H39" s="28" t="s">
         <v>136</v>
       </c>
@@ -5536,7 +5537,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="40" spans="2:9" hidden="1">
+    <row r="40" spans="2:9">
       <c r="B40" s="47" t="s">
         <v>165</v>
       </c>
@@ -5552,9 +5553,7 @@
       <c r="F40" s="17">
         <v>2</v>
       </c>
-      <c r="G40" s="17">
-        <v>2</v>
-      </c>
+      <c r="G40" s="17"/>
       <c r="H40" s="28" t="s">
         <v>136</v>
       </c>
@@ -5562,7 +5561,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="41" spans="2:9" hidden="1">
+    <row r="41" spans="2:9">
       <c r="B41" s="47" t="s">
         <v>165</v>
       </c>
@@ -5578,9 +5577,6 @@
       <c r="F41" s="28">
         <v>3</v>
       </c>
-      <c r="G41" s="28">
-        <v>3</v>
-      </c>
       <c r="H41" s="28" t="s">
         <v>136</v>
       </c>
@@ -5588,7 +5584,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="42" spans="2:9">
+    <row r="42" spans="2:9" hidden="1">
       <c r="B42" s="48" t="s">
         <v>167</v>
       </c>
@@ -5614,7 +5610,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="43" spans="2:9">
+    <row r="43" spans="2:9" hidden="1">
       <c r="B43" s="48" t="s">
         <v>167</v>
       </c>
@@ -5640,7 +5636,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="44" spans="2:9">
+    <row r="44" spans="2:9" hidden="1">
       <c r="B44" s="48" t="s">
         <v>167</v>
       </c>
@@ -5666,7 +5662,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="45" spans="2:9">
+    <row r="45" spans="2:9" hidden="1">
       <c r="B45" s="48" t="s">
         <v>167</v>
       </c>
@@ -5692,7 +5688,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="46" spans="2:9">
+    <row r="46" spans="2:9" hidden="1">
       <c r="B46" s="48" t="s">
         <v>167</v>
       </c>
@@ -5718,7 +5714,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="47" spans="2:9">
+    <row r="47" spans="2:9" hidden="1">
       <c r="B47" s="48" t="s">
         <v>167</v>
       </c>
@@ -5744,7 +5740,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="48" spans="2:9" hidden="1">
+    <row r="48" spans="2:9">
       <c r="B48" s="48" t="s">
         <v>167</v>
       </c>
@@ -5760,9 +5756,6 @@
       <c r="F48" s="28">
         <v>2</v>
       </c>
-      <c r="G48" s="28">
-        <v>2</v>
-      </c>
       <c r="H48" s="28" t="s">
         <v>136</v>
       </c>
@@ -5770,7 +5763,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="49" spans="1:9" hidden="1">
+    <row r="49" spans="1:10">
       <c r="B49" s="48" t="s">
         <v>167</v>
       </c>
@@ -5796,7 +5789,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:10" hidden="1">
       <c r="A50" s="21" t="s">
         <v>221</v>
       </c>
@@ -5816,13 +5809,13 @@
         <v>2</v>
       </c>
       <c r="H50" s="28" t="s">
-        <v>136</v>
+        <v>241</v>
       </c>
       <c r="I50" s="21" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:10" hidden="1">
       <c r="A51" s="21" t="s">
         <v>213</v>
       </c>
@@ -5842,13 +5835,13 @@
         <v>1</v>
       </c>
       <c r="H51" s="28" t="s">
-        <v>136</v>
+        <v>241</v>
       </c>
       <c r="I51" s="21" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:10" hidden="1">
       <c r="B52" s="50" t="s">
         <v>188</v>
       </c>
@@ -5865,13 +5858,13 @@
         <v>1</v>
       </c>
       <c r="H52" s="28" t="s">
-        <v>136</v>
+        <v>241</v>
       </c>
       <c r="I52" s="21" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" hidden="1">
       <c r="B53" s="50" t="s">
         <v>188</v>
       </c>
@@ -5897,7 +5890,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:10" hidden="1">
       <c r="B54" s="50" t="s">
         <v>188</v>
       </c>
@@ -5916,8 +5909,11 @@
       <c r="I54" s="21" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="55" spans="1:9">
+      <c r="J54" s="21" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" hidden="1">
       <c r="B55" s="50" t="s">
         <v>188</v>
       </c>
@@ -5936,8 +5932,11 @@
       <c r="I55" s="21" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="56" spans="1:9" hidden="1">
+      <c r="J55" s="21" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
       <c r="B56" s="29" t="s">
         <v>181</v>
       </c>
@@ -5950,6 +5949,9 @@
       <c r="E56" s="28" t="s">
         <v>18</v>
       </c>
+      <c r="F56" s="28">
+        <v>1</v>
+      </c>
       <c r="H56" s="28" t="s">
         <v>136</v>
       </c>
@@ -5957,7 +5959,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="57" spans="1:9" hidden="1">
+    <row r="57" spans="1:10">
       <c r="B57" s="29" t="s">
         <v>181</v>
       </c>
@@ -5970,6 +5972,9 @@
       <c r="E57" s="28" t="s">
         <v>18</v>
       </c>
+      <c r="F57" s="28">
+        <v>1</v>
+      </c>
       <c r="H57" s="28" t="s">
         <v>136</v>
       </c>
@@ -5977,7 +5982,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="58" spans="1:9" hidden="1">
+    <row r="58" spans="1:10">
       <c r="B58" s="29" t="s">
         <v>181</v>
       </c>
@@ -5990,6 +5995,9 @@
       <c r="E58" s="28" t="s">
         <v>18</v>
       </c>
+      <c r="F58" s="28">
+        <v>1</v>
+      </c>
       <c r="H58" s="28" t="s">
         <v>136</v>
       </c>
@@ -5997,7 +6005,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="59" spans="1:9" hidden="1">
+    <row r="59" spans="1:10">
       <c r="B59" s="29" t="s">
         <v>181</v>
       </c>
@@ -6020,7 +6028,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:10" hidden="1">
       <c r="B60" s="29" t="s">
         <v>181</v>
       </c>
@@ -6040,7 +6048,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:10" hidden="1">
       <c r="B61" s="29" t="s">
         <v>181</v>
       </c>
@@ -6060,7 +6068,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:10" hidden="1">
       <c r="B62" s="43" t="s">
         <v>186</v>
       </c>
@@ -6077,13 +6085,13 @@
         <v>2</v>
       </c>
       <c r="H62" s="28" t="s">
-        <v>136</v>
+        <v>241</v>
       </c>
       <c r="I62" s="21" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:10" hidden="1">
       <c r="B63" s="43" t="s">
         <v>186</v>
       </c>
@@ -6100,13 +6108,13 @@
         <v>2</v>
       </c>
       <c r="H63" s="28" t="s">
-        <v>136</v>
+        <v>241</v>
       </c>
       <c r="I63" s="21" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:10" hidden="1">
       <c r="B64" s="43" t="s">
         <v>186</v>
       </c>
@@ -6123,7 +6131,7 @@
         <v>1.5</v>
       </c>
       <c r="H64" s="28" t="s">
-        <v>136</v>
+        <v>241</v>
       </c>
       <c r="I64" s="21" t="s">
         <v>226</v>
@@ -6146,7 +6154,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="66" spans="2:9">
+    <row r="66" spans="2:9" hidden="1">
       <c r="B66" s="43" t="s">
         <v>186</v>
       </c>
@@ -6163,13 +6171,13 @@
         <v>2</v>
       </c>
       <c r="H66" s="28" t="s">
-        <v>136</v>
+        <v>241</v>
       </c>
       <c r="I66" s="21" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="67" spans="2:9">
+    <row r="67" spans="2:9" hidden="1">
       <c r="B67" s="43" t="s">
         <v>186</v>
       </c>
@@ -6186,13 +6194,13 @@
         <v>2</v>
       </c>
       <c r="H67" s="28" t="s">
-        <v>136</v>
+        <v>241</v>
       </c>
       <c r="I67" s="21" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="68" spans="2:9" hidden="1">
+    <row r="68" spans="2:9">
       <c r="B68" s="43" t="s">
         <v>186</v>
       </c>
@@ -6205,6 +6213,9 @@
       <c r="E68" s="28" t="s">
         <v>18</v>
       </c>
+      <c r="F68" s="28">
+        <v>1</v>
+      </c>
       <c r="H68" s="28" t="s">
         <v>136</v>
       </c>
@@ -6212,7 +6223,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="69" spans="2:9" hidden="1">
+    <row r="69" spans="2:9">
       <c r="B69" s="44" t="s">
         <v>195</v>
       </c>
@@ -6225,6 +6236,9 @@
       <c r="E69" s="28" t="s">
         <v>18</v>
       </c>
+      <c r="F69" s="28">
+        <v>1</v>
+      </c>
       <c r="H69" s="28" t="s">
         <v>136</v>
       </c>
@@ -6232,7 +6246,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="70" spans="2:9" hidden="1">
+    <row r="70" spans="2:9">
       <c r="B70" s="44" t="s">
         <v>195</v>
       </c>
@@ -6245,6 +6259,9 @@
       <c r="E70" s="28" t="s">
         <v>18</v>
       </c>
+      <c r="F70" s="28">
+        <v>1</v>
+      </c>
       <c r="H70" s="28" t="s">
         <v>136</v>
       </c>
@@ -6252,7 +6269,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="71" spans="2:9" hidden="1">
+    <row r="71" spans="2:9">
       <c r="B71" s="44" t="s">
         <v>195</v>
       </c>
@@ -6265,6 +6282,9 @@
       <c r="E71" s="28" t="s">
         <v>18</v>
       </c>
+      <c r="F71" s="28">
+        <v>1</v>
+      </c>
       <c r="H71" s="28" t="s">
         <v>136</v>
       </c>
@@ -6272,7 +6292,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="72" spans="2:9" hidden="1">
+    <row r="72" spans="2:9">
       <c r="B72" s="44" t="s">
         <v>195</v>
       </c>
@@ -6285,6 +6305,9 @@
       <c r="E72" s="28" t="s">
         <v>18</v>
       </c>
+      <c r="F72" s="28">
+        <v>1</v>
+      </c>
       <c r="H72" s="28" t="s">
         <v>136</v>
       </c>
@@ -6292,7 +6315,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="73" spans="2:9" hidden="1">
+    <row r="73" spans="2:9">
       <c r="B73" s="51" t="s">
         <v>199</v>
       </c>
@@ -6305,14 +6328,17 @@
       <c r="E73" s="28" t="s">
         <v>18</v>
       </c>
+      <c r="F73" s="28">
+        <v>0.5</v>
+      </c>
       <c r="H73" s="28" t="s">
         <v>136</v>
       </c>
       <c r="I73" s="21" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="74" spans="2:9" hidden="1">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="74" spans="2:9">
       <c r="B74" s="51" t="s">
         <v>199</v>
       </c>
@@ -6325,16 +6351,18 @@
       <c r="E74" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F74" s="21"/>
+      <c r="F74" s="28">
+        <v>0.5</v>
+      </c>
       <c r="G74" s="21"/>
       <c r="H74" s="28" t="s">
         <v>136</v>
       </c>
       <c r="I74" s="21" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="75" spans="2:9" hidden="1">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="75" spans="2:9">
       <c r="B75" s="51" t="s">
         <v>199</v>
       </c>
@@ -6347,16 +6375,18 @@
       <c r="E75" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F75" s="21"/>
+      <c r="F75" s="28">
+        <v>0.5</v>
+      </c>
       <c r="G75" s="21"/>
       <c r="H75" s="28" t="s">
         <v>136</v>
       </c>
       <c r="I75" s="21" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="76" spans="2:9" hidden="1">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="76" spans="2:9">
       <c r="B76" s="51" t="s">
         <v>199</v>
       </c>
@@ -6369,16 +6399,18 @@
       <c r="E76" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F76" s="21"/>
+      <c r="F76" s="28">
+        <v>0.5</v>
+      </c>
       <c r="G76" s="21"/>
       <c r="H76" s="28" t="s">
         <v>136</v>
       </c>
       <c r="I76" s="21" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="77" spans="2:9" hidden="1">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="77" spans="2:9">
       <c r="B77" s="51" t="s">
         <v>199</v>
       </c>
@@ -6391,18 +6423,21 @@
       <c r="E77" s="28" t="s">
         <v>18</v>
       </c>
+      <c r="F77" s="28">
+        <v>0.5</v>
+      </c>
       <c r="H77" s="28" t="s">
         <v>136</v>
       </c>
       <c r="I77" s="21" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:I77" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="4">
       <filters>
-        <filter val="プロト"/>
+        <filter val="アルファ"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -6621,12 +6656,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6865,20 +6902,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6903,12 +6941,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/コスト表.xlsx
+++ b/コスト表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FukudaGenki\Documents\GitHub\koukiteam\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tamari\Documents\GitHub\koukiteam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{161E2831-B923-4881-8A08-E7ADD7B8643B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED1B077D-837E-419F-B36E-F7884CB00317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1125_元データ" sheetId="4" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="241">
   <si>
     <t>1コスト:3時間 (1日は基本2コスト)</t>
     <phoneticPr fontId="1"/>
@@ -1804,23 +1804,6 @@
     <t>日</t>
     <rPh sb="0" eb="1">
       <t>ニチ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>完了</t>
-  </si>
-  <si>
-    <t>全員</t>
-    <rPh sb="0" eb="2">
-      <t>ゼンイン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>→アルファへ移動</t>
-    <rPh sb="6" eb="8">
-      <t>イドウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1830,20 +1813,20 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="177" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1852,14 +1835,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1867,7 +1850,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1875,7 +1858,7 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1883,7 +1866,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1891,7 +1874,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1903,7 +1886,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="29">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2060,18 +2043,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -2144,11 +2115,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2219,10 +2190,6 @@
     <xf numFmtId="0" fontId="0" fillId="26" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -2519,18 +2486,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1662411A-9E28-47BA-80A0-FB5B8EEC7CF8}">
   <dimension ref="A1:M106"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.75" style="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.25" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.625" customWidth="1"/>
-    <col min="9" max="9" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.5703125" customWidth="1"/>
+    <col min="9" max="9" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="33" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2608,11 +2575,11 @@
       </c>
       <c r="K4" s="2">
         <f ca="1">NETWORKDAYS(K5,K6)</f>
-        <v>501</v>
+        <v>485</v>
       </c>
       <c r="L4" s="3">
         <f ca="1" xml:space="preserve"> K3 / K4</f>
-        <v>5.289421157684631E-2</v>
+        <v>5.4639175257731959E-2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2652,7 +2619,7 @@
       </c>
       <c r="K6" s="1">
         <f ca="1">TODAY()</f>
-        <v>46303</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2717,11 +2684,11 @@
       </c>
       <c r="L9" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K9)</f>
-        <v>-470</v>
+        <v>-454</v>
       </c>
       <c r="M9" s="3">
         <f ca="1">($K$2 - $K$3) / L9</f>
-        <v>-0.19574468085106383</v>
+        <v>-0.20264317180616739</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -2748,11 +2715,11 @@
       </c>
       <c r="L10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K10)</f>
-        <v>-450</v>
+        <v>-434</v>
       </c>
       <c r="M10" s="3">
         <f ca="1">($K$2 - $K$3) / L10</f>
-        <v>-0.20444444444444446</v>
+        <v>-0.2119815668202765</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2779,11 +2746,11 @@
       </c>
       <c r="L11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K11)</f>
-        <v>-439</v>
+        <v>-423</v>
       </c>
       <c r="M11" s="3">
         <f ca="1">($K$2 - $K$3) / L11</f>
-        <v>-0.20956719817767655</v>
+        <v>-0.21749408983451538</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -4298,12 +4265,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{224174C6-79B8-40DF-BFBC-1FA41083861E}">
   <dimension ref="B3:E27"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="33" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:5">
@@ -4312,7 +4279,7 @@
       </c>
       <c r="C3">
         <f>SUM(作業工数見積もり!F3:F103)</f>
-        <v>92</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="4" spans="2:5">
@@ -4321,7 +4288,7 @@
       </c>
       <c r="C4">
         <f>SUMIF(作業工数見積もり!H3:H46,"完了",作業工数見積もり!F3:F46)</f>
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -4333,11 +4300,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>501</v>
+        <v>485</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>6.5868263473053898E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -4355,7 +4322,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46303</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -4376,11 +4343,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-470</v>
+        <v>-454</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.12553191489361701</v>
+        <v>-0.11123348017621146</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -4393,11 +4360,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-450</v>
+        <v>-434</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.13111111111111112</v>
+        <v>-0.11635944700460829</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -4410,11 +4377,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-439</v>
+        <v>-423</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.13439635535307518</v>
+        <v>-0.11938534278959811</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -4498,21 +4465,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A2:M77"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32.75" style="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.875" style="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.125" style="21" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="28" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.25" style="28" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.375" style="28" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.25" style="28" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.140625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" style="28" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" style="28" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.42578125" style="28" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" style="28" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="21"/>
-    <col min="10" max="10" width="15.625" style="21" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" style="21" customWidth="1"/>
     <col min="11" max="11" width="33" style="21" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.25" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.28515625" style="21" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="19" style="21" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="21"/>
   </cols>
@@ -4559,9 +4525,6 @@
       <c r="H3" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="I3" s="21" t="s">
-        <v>216</v>
-      </c>
       <c r="K3" s="34" t="s">
         <v>132</v>
       </c>
@@ -4570,7 +4533,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="2:13" hidden="1">
+    <row r="4" spans="2:13">
       <c r="B4" s="43" t="s">
         <v>137</v>
       </c>
@@ -4594,7 +4557,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="2:13" hidden="1">
+    <row r="5" spans="2:13">
       <c r="B5" s="43" t="s">
         <v>137</v>
       </c>
@@ -4608,7 +4571,7 @@
         <v>34</v>
       </c>
       <c r="H5" s="28" t="s">
-        <v>241</v>
+        <v>136</v>
       </c>
       <c r="K5" s="36" t="s">
         <v>1</v>
@@ -4618,7 +4581,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="2:13" hidden="1">
+    <row r="6" spans="2:13">
       <c r="B6" s="44" t="s">
         <v>159</v>
       </c>
@@ -4634,11 +4597,8 @@
       <c r="F6" s="28">
         <v>1</v>
       </c>
-      <c r="G6" s="28">
-        <v>1</v>
-      </c>
       <c r="H6" s="28" t="s">
-        <v>241</v>
+        <v>136</v>
       </c>
       <c r="I6" s="21" t="s">
         <v>214</v>
@@ -4651,7 +4611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:13" hidden="1">
+    <row r="7" spans="2:13">
       <c r="B7" s="44" t="s">
         <v>159</v>
       </c>
@@ -4667,11 +4627,8 @@
       <c r="F7" s="28">
         <v>1</v>
       </c>
-      <c r="G7" s="28">
-        <v>1</v>
-      </c>
       <c r="H7" s="28" t="s">
-        <v>241</v>
+        <v>136</v>
       </c>
       <c r="I7" s="21" t="s">
         <v>214</v>
@@ -4692,28 +4649,22 @@
       <c r="E8" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="28">
-        <v>1</v>
-      </c>
       <c r="H8" s="28" t="s">
         <v>136</v>
-      </c>
-      <c r="I8" s="21" t="s">
-        <v>214</v>
       </c>
       <c r="K8" s="32" t="s">
         <v>35</v>
       </c>
       <c r="L8" s="39">
         <f>COUNTIF(H3:H77,K8)</f>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="M8" s="40">
         <f>L8/L3</f>
-        <v>0.47297297297297297</v>
-      </c>
-    </row>
-    <row r="9" spans="2:13" hidden="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13">
       <c r="B9" s="44" t="s">
         <v>159</v>
       </c>
@@ -4729,11 +4680,8 @@
       <c r="F9" s="28">
         <v>1</v>
       </c>
-      <c r="G9" s="28">
-        <v>1</v>
-      </c>
       <c r="H9" s="28" t="s">
-        <v>241</v>
+        <v>136</v>
       </c>
       <c r="I9" s="21" t="s">
         <v>214</v>
@@ -4743,11 +4691,11 @@
       </c>
       <c r="L9" s="39">
         <f>COUNTIF(H3:H77,K9)</f>
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="M9" s="31">
         <f>(L9+L10)/L3</f>
-        <v>0.54054054054054057</v>
+        <v>1.0135135135135136</v>
       </c>
     </row>
     <row r="10" spans="2:13">
@@ -4763,14 +4711,8 @@
       <c r="E10" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="28">
-        <v>1</v>
-      </c>
       <c r="H10" s="28" t="s">
         <v>136</v>
-      </c>
-      <c r="I10" s="21" t="s">
-        <v>214</v>
       </c>
       <c r="K10" s="34" t="s">
         <v>134</v>
@@ -4793,17 +4735,11 @@
       <c r="E11" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="28">
-        <v>1</v>
-      </c>
       <c r="H11" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="I11" s="21" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="12" spans="2:13" hidden="1">
+    </row>
+    <row r="12" spans="2:13">
       <c r="B12" s="45" t="s">
         <v>141</v>
       </c>
@@ -4819,11 +4755,8 @@
       <c r="F12" s="28">
         <v>1</v>
       </c>
-      <c r="G12" s="28">
-        <v>0.5</v>
-      </c>
       <c r="H12" s="28" t="s">
-        <v>241</v>
+        <v>136</v>
       </c>
       <c r="I12" s="21" t="s">
         <v>215</v>
@@ -4833,10 +4766,10 @@
       </c>
       <c r="L12" s="21">
         <f>SUM(F3:F77)</f>
-        <v>92</v>
-      </c>
-    </row>
-    <row r="13" spans="2:13" hidden="1">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13">
       <c r="B13" s="45" t="s">
         <v>141</v>
       </c>
@@ -4852,11 +4785,8 @@
       <c r="F13" s="28">
         <v>1</v>
       </c>
-      <c r="G13" s="28">
-        <v>0.5</v>
-      </c>
       <c r="H13" s="28" t="s">
-        <v>241</v>
+        <v>136</v>
       </c>
       <c r="I13" s="21" t="s">
         <v>215</v>
@@ -4866,10 +4796,10 @@
       </c>
       <c r="L13" s="21">
         <f>1*L12</f>
-        <v>92</v>
-      </c>
-    </row>
-    <row r="14" spans="2:13" hidden="1">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13">
       <c r="B14" s="45" t="s">
         <v>141</v>
       </c>
@@ -4885,18 +4815,15 @@
       <c r="F14" s="28">
         <v>4</v>
       </c>
-      <c r="G14" s="28">
-        <v>2</v>
-      </c>
       <c r="H14" s="28" t="s">
-        <v>241</v>
+        <v>136</v>
       </c>
       <c r="I14" s="21" t="s">
         <v>215</v>
       </c>
       <c r="J14" s="38"/>
     </row>
-    <row r="15" spans="2:13" hidden="1">
+    <row r="15" spans="2:13">
       <c r="B15" s="45" t="s">
         <v>141</v>
       </c>
@@ -4913,7 +4840,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="28" t="s">
-        <v>241</v>
+        <v>136</v>
       </c>
       <c r="I15" s="21" t="s">
         <v>215</v>
@@ -4924,7 +4851,7 @@
       </c>
       <c r="L15" s="21">
         <f>COUNTIF(I3:I77, K15)</f>
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="2:13">
@@ -4940,21 +4867,15 @@
       <c r="E16" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F16" s="28">
-        <v>2</v>
-      </c>
       <c r="H16" s="28" t="s">
         <v>136</v>
-      </c>
-      <c r="I16" s="21" t="s">
-        <v>215</v>
       </c>
       <c r="K16" s="21" t="s">
         <v>230</v>
       </c>
       <c r="L16" s="21">
         <f>COUNTIF(I3:I77, K16)</f>
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="2:12">
@@ -4970,21 +4891,15 @@
       <c r="E17" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F17" s="28">
-        <v>1</v>
-      </c>
       <c r="H17" s="28" t="s">
         <v>136</v>
-      </c>
-      <c r="I17" s="21" t="s">
-        <v>215</v>
       </c>
       <c r="K17" s="21" t="s">
         <v>231</v>
       </c>
       <c r="L17" s="21">
         <f>COUNTIF(I3:I77, K17)</f>
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="2:12">
@@ -5000,14 +4915,8 @@
       <c r="E18" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="28">
-        <v>2</v>
-      </c>
       <c r="H18" s="28" t="s">
         <v>136</v>
-      </c>
-      <c r="I18" s="21" t="s">
-        <v>215</v>
       </c>
       <c r="K18" s="21" t="s">
         <v>232</v>
@@ -5017,7 +4926,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="2:12" hidden="1">
+    <row r="19" spans="2:12">
       <c r="B19" s="45" t="s">
         <v>141</v>
       </c>
@@ -5033,11 +4942,8 @@
       <c r="F19" s="28">
         <v>3</v>
       </c>
-      <c r="G19" s="28">
-        <v>2</v>
-      </c>
       <c r="H19" s="28" t="s">
-        <v>241</v>
+        <v>136</v>
       </c>
       <c r="I19" s="21" t="s">
         <v>215</v>
@@ -5063,17 +4969,11 @@
       <c r="E20" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F20" s="28">
-        <v>0.5</v>
-      </c>
       <c r="H20" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="I20" s="21" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="21" spans="2:12" hidden="1">
+    </row>
+    <row r="21" spans="2:12">
       <c r="B21" s="45" t="s">
         <v>141</v>
       </c>
@@ -5090,13 +4990,13 @@
         <v>4</v>
       </c>
       <c r="H21" s="28" t="s">
-        <v>241</v>
+        <v>136</v>
       </c>
       <c r="I21" s="21" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="22" spans="2:12" hidden="1">
+    <row r="22" spans="2:12">
       <c r="B22" s="45" t="s">
         <v>141</v>
       </c>
@@ -5112,11 +5012,8 @@
       <c r="F22" s="28">
         <v>1</v>
       </c>
-      <c r="G22" s="28">
-        <v>0.5</v>
-      </c>
       <c r="H22" s="28" t="s">
-        <v>241</v>
+        <v>136</v>
       </c>
       <c r="I22" s="21" t="s">
         <v>215</v>
@@ -5135,17 +5032,11 @@
       <c r="E23" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F23" s="28">
-        <v>2</v>
-      </c>
       <c r="H23" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="I23" s="21" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="24" spans="2:12" hidden="1">
+    </row>
+    <row r="24" spans="2:12">
       <c r="B24" s="45" t="s">
         <v>141</v>
       </c>
@@ -5161,11 +5052,8 @@
       <c r="F24" s="28">
         <v>1</v>
       </c>
-      <c r="G24" s="28">
-        <v>0.5</v>
-      </c>
       <c r="H24" s="28" t="s">
-        <v>241</v>
+        <v>136</v>
       </c>
       <c r="I24" s="21" t="s">
         <v>215</v>
@@ -5184,14 +5072,8 @@
       <c r="E25" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F25" s="28">
-        <v>0.5</v>
-      </c>
       <c r="H25" s="28" t="s">
         <v>136</v>
-      </c>
-      <c r="I25" s="21" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="26" spans="2:12">
@@ -5207,17 +5089,11 @@
       <c r="E26" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F26" s="28">
-        <v>2</v>
-      </c>
       <c r="H26" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="I26" s="21" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="27" spans="2:12" hidden="1">
+    </row>
+    <row r="27" spans="2:12">
       <c r="B27" s="46" t="s">
         <v>152</v>
       </c>
@@ -5233,17 +5109,14 @@
       <c r="F27" s="28">
         <v>1</v>
       </c>
-      <c r="G27" s="28">
-        <v>1</v>
-      </c>
       <c r="H27" s="28" t="s">
-        <v>241</v>
+        <v>136</v>
       </c>
       <c r="I27" s="21" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="28" spans="2:12" hidden="1">
+    <row r="28" spans="2:12">
       <c r="B28" s="46" t="s">
         <v>152</v>
       </c>
@@ -5259,17 +5132,14 @@
       <c r="F28" s="28">
         <v>1</v>
       </c>
-      <c r="G28" s="28">
-        <v>1</v>
-      </c>
       <c r="H28" s="28" t="s">
-        <v>241</v>
+        <v>136</v>
       </c>
       <c r="I28" s="21" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="29" spans="2:12" hidden="1">
+    <row r="29" spans="2:12">
       <c r="B29" s="46" t="s">
         <v>152</v>
       </c>
@@ -5285,17 +5155,14 @@
       <c r="F29" s="28">
         <v>1</v>
       </c>
-      <c r="G29" s="28">
-        <v>1</v>
-      </c>
       <c r="H29" s="28" t="s">
-        <v>241</v>
+        <v>136</v>
       </c>
       <c r="I29" s="21" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="30" spans="2:12" hidden="1">
+    <row r="30" spans="2:12">
       <c r="B30" s="46" t="s">
         <v>152</v>
       </c>
@@ -5311,17 +5178,14 @@
       <c r="F30" s="28">
         <v>0.5</v>
       </c>
-      <c r="G30" s="28">
-        <v>0.5</v>
-      </c>
       <c r="H30" s="28" t="s">
-        <v>241</v>
+        <v>136</v>
       </c>
       <c r="I30" s="21" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="31" spans="2:12" hidden="1">
+    <row r="31" spans="2:12">
       <c r="B31" s="46" t="s">
         <v>152</v>
       </c>
@@ -5337,11 +5201,8 @@
       <c r="F31" s="28">
         <v>0.5</v>
       </c>
-      <c r="G31" s="28">
-        <v>0.5</v>
-      </c>
       <c r="H31" s="28" t="s">
-        <v>241</v>
+        <v>136</v>
       </c>
       <c r="I31" s="21" t="s">
         <v>214</v>
@@ -5360,14 +5221,8 @@
       <c r="E32" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F32" s="28">
-        <v>1</v>
-      </c>
       <c r="H32" s="28" t="s">
         <v>136</v>
-      </c>
-      <c r="I32" s="21" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="33" spans="2:9">
@@ -5383,17 +5238,11 @@
       <c r="E33" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F33" s="28">
-        <v>1</v>
-      </c>
       <c r="H33" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="I33" s="21" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="34" spans="2:9" hidden="1">
+    </row>
+    <row r="34" spans="2:9">
       <c r="B34" s="46" t="s">
         <v>152</v>
       </c>
@@ -5409,11 +5258,8 @@
       <c r="F34" s="28">
         <v>0.5</v>
       </c>
-      <c r="G34" s="28">
-        <v>0.5</v>
-      </c>
       <c r="H34" s="28" t="s">
-        <v>241</v>
+        <v>136</v>
       </c>
       <c r="I34" s="21" t="s">
         <v>214</v>
@@ -5432,17 +5278,11 @@
       <c r="E35" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F35" s="28">
-        <v>2</v>
-      </c>
       <c r="H35" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="I35" s="21" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="36" spans="2:9" hidden="1">
+    </row>
+    <row r="36" spans="2:9">
       <c r="B36" s="46" t="s">
         <v>152</v>
       </c>
@@ -5459,7 +5299,7 @@
         <v>0.5</v>
       </c>
       <c r="H36" s="28" t="s">
-        <v>241</v>
+        <v>136</v>
       </c>
       <c r="I36" s="21" t="s">
         <v>216</v>
@@ -5478,15 +5318,10 @@
       <c r="E37" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F37" s="17">
-        <v>1</v>
-      </c>
-      <c r="G37" s="17"/>
+      <c r="F37" s="21"/>
+      <c r="G37" s="21"/>
       <c r="H37" s="28" t="s">
         <v>136</v>
-      </c>
-      <c r="I37" s="21" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="38" spans="2:9">
@@ -5502,15 +5337,10 @@
       <c r="E38" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F38" s="17">
-        <v>2</v>
-      </c>
-      <c r="G38" s="17"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
       <c r="H38" s="28" t="s">
         <v>136</v>
-      </c>
-      <c r="I38" s="21" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="39" spans="2:9">
@@ -5526,15 +5356,10 @@
       <c r="E39" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F39" s="17">
-        <v>1</v>
-      </c>
-      <c r="G39" s="17"/>
+      <c r="F39" s="21"/>
+      <c r="G39" s="21"/>
       <c r="H39" s="28" t="s">
         <v>136</v>
-      </c>
-      <c r="I39" s="21" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="40" spans="2:9">
@@ -5550,15 +5375,10 @@
       <c r="E40" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F40" s="17">
-        <v>2</v>
-      </c>
-      <c r="G40" s="17"/>
+      <c r="F40" s="21"/>
+      <c r="G40" s="21"/>
       <c r="H40" s="28" t="s">
         <v>136</v>
-      </c>
-      <c r="I40" s="21" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="41" spans="2:9">
@@ -5574,17 +5394,11 @@
       <c r="E41" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F41" s="28">
-        <v>3</v>
-      </c>
       <c r="H41" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="I41" s="21" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="42" spans="2:9" hidden="1">
+    </row>
+    <row r="42" spans="2:9">
       <c r="B42" s="48" t="s">
         <v>167</v>
       </c>
@@ -5600,17 +5414,14 @@
       <c r="F42" s="28">
         <v>2</v>
       </c>
-      <c r="G42" s="28">
-        <v>2</v>
-      </c>
       <c r="H42" s="28" t="s">
-        <v>241</v>
+        <v>136</v>
       </c>
       <c r="I42" s="21" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="43" spans="2:9" hidden="1">
+    <row r="43" spans="2:9">
       <c r="B43" s="48" t="s">
         <v>167</v>
       </c>
@@ -5626,17 +5437,14 @@
       <c r="F43" s="28">
         <v>2</v>
       </c>
-      <c r="G43" s="28">
-        <v>2</v>
-      </c>
       <c r="H43" s="28" t="s">
-        <v>241</v>
+        <v>136</v>
       </c>
       <c r="I43" s="21" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="44" spans="2:9" hidden="1">
+    <row r="44" spans="2:9">
       <c r="B44" s="48" t="s">
         <v>167</v>
       </c>
@@ -5652,17 +5460,14 @@
       <c r="F44" s="28">
         <v>2</v>
       </c>
-      <c r="G44" s="28">
-        <v>2</v>
-      </c>
       <c r="H44" s="28" t="s">
-        <v>241</v>
+        <v>136</v>
       </c>
       <c r="I44" s="21" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="45" spans="2:9" hidden="1">
+    <row r="45" spans="2:9">
       <c r="B45" s="48" t="s">
         <v>167</v>
       </c>
@@ -5678,17 +5483,14 @@
       <c r="F45" s="28">
         <v>1</v>
       </c>
-      <c r="G45" s="28">
-        <v>1</v>
-      </c>
       <c r="H45" s="28" t="s">
-        <v>241</v>
+        <v>136</v>
       </c>
       <c r="I45" s="21" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="46" spans="2:9" hidden="1">
+    <row r="46" spans="2:9">
       <c r="B46" s="48" t="s">
         <v>167</v>
       </c>
@@ -5704,17 +5506,14 @@
       <c r="F46" s="28">
         <v>2</v>
       </c>
-      <c r="G46" s="28">
-        <v>2</v>
-      </c>
       <c r="H46" s="28" t="s">
-        <v>241</v>
+        <v>136</v>
       </c>
       <c r="I46" s="21" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="47" spans="2:9" hidden="1">
+    <row r="47" spans="2:9">
       <c r="B47" s="48" t="s">
         <v>167</v>
       </c>
@@ -5730,11 +5529,8 @@
       <c r="F47" s="28">
         <v>1</v>
       </c>
-      <c r="G47" s="28">
-        <v>1</v>
-      </c>
       <c r="H47" s="28" t="s">
-        <v>241</v>
+        <v>136</v>
       </c>
       <c r="I47" s="21" t="s">
         <v>214</v>
@@ -5753,17 +5549,11 @@
       <c r="E48" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F48" s="28">
-        <v>2</v>
-      </c>
       <c r="H48" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="I48" s="21" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10">
+    </row>
+    <row r="49" spans="1:9">
       <c r="B49" s="48" t="s">
         <v>167</v>
       </c>
@@ -5776,20 +5566,11 @@
       <c r="E49" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F49" s="28">
-        <v>3</v>
-      </c>
-      <c r="G49" s="28">
-        <v>3</v>
-      </c>
       <c r="H49" s="28" t="s">
-        <v>241</v>
-      </c>
-      <c r="I49" s="21" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" hidden="1">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
       <c r="A50" s="21" t="s">
         <v>221</v>
       </c>
@@ -5809,13 +5590,13 @@
         <v>2</v>
       </c>
       <c r="H50" s="28" t="s">
-        <v>241</v>
+        <v>136</v>
       </c>
       <c r="I50" s="21" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="51" spans="1:10" hidden="1">
+    <row r="51" spans="1:9">
       <c r="A51" s="21" t="s">
         <v>213</v>
       </c>
@@ -5835,13 +5616,13 @@
         <v>1</v>
       </c>
       <c r="H51" s="28" t="s">
-        <v>241</v>
+        <v>136</v>
       </c>
       <c r="I51" s="21" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="52" spans="1:10" hidden="1">
+    <row r="52" spans="1:9">
       <c r="B52" s="50" t="s">
         <v>188</v>
       </c>
@@ -5858,13 +5639,13 @@
         <v>1</v>
       </c>
       <c r="H52" s="28" t="s">
-        <v>241</v>
+        <v>136</v>
       </c>
       <c r="I52" s="21" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" hidden="1">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
       <c r="B53" s="50" t="s">
         <v>188</v>
       </c>
@@ -5880,17 +5661,14 @@
       <c r="F53" s="28">
         <v>2</v>
       </c>
-      <c r="G53" s="28">
-        <v>2</v>
-      </c>
       <c r="H53" s="28" t="s">
-        <v>241</v>
+        <v>136</v>
       </c>
       <c r="I53" s="21" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="54" spans="1:10" hidden="1">
+    <row r="54" spans="1:9">
       <c r="B54" s="50" t="s">
         <v>188</v>
       </c>
@@ -5909,11 +5687,8 @@
       <c r="I54" s="21" t="s">
         <v>222</v>
       </c>
-      <c r="J54" s="21" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" hidden="1">
+    </row>
+    <row r="55" spans="1:9">
       <c r="B55" s="50" t="s">
         <v>188</v>
       </c>
@@ -5932,11 +5707,8 @@
       <c r="I55" s="21" t="s">
         <v>222</v>
       </c>
-      <c r="J55" s="21" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10">
+    </row>
+    <row r="56" spans="1:9">
       <c r="B56" s="29" t="s">
         <v>181</v>
       </c>
@@ -5949,9 +5721,6 @@
       <c r="E56" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F56" s="28">
-        <v>1</v>
-      </c>
       <c r="H56" s="28" t="s">
         <v>136</v>
       </c>
@@ -5959,7 +5728,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:9">
       <c r="B57" s="29" t="s">
         <v>181</v>
       </c>
@@ -5972,9 +5741,6 @@
       <c r="E57" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F57" s="28">
-        <v>1</v>
-      </c>
       <c r="H57" s="28" t="s">
         <v>136</v>
       </c>
@@ -5982,7 +5748,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:9">
       <c r="B58" s="29" t="s">
         <v>181</v>
       </c>
@@ -5995,9 +5761,6 @@
       <c r="E58" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F58" s="28">
-        <v>1</v>
-      </c>
       <c r="H58" s="28" t="s">
         <v>136</v>
       </c>
@@ -6005,7 +5768,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:9">
       <c r="B59" s="29" t="s">
         <v>181</v>
       </c>
@@ -6028,7 +5791,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="60" spans="1:10" hidden="1">
+    <row r="60" spans="1:9">
       <c r="B60" s="29" t="s">
         <v>181</v>
       </c>
@@ -6048,7 +5811,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="61" spans="1:10" hidden="1">
+    <row r="61" spans="1:9">
       <c r="B61" s="29" t="s">
         <v>181</v>
       </c>
@@ -6068,7 +5831,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="62" spans="1:10" hidden="1">
+    <row r="62" spans="1:9">
       <c r="B62" s="43" t="s">
         <v>186</v>
       </c>
@@ -6085,13 +5848,13 @@
         <v>2</v>
       </c>
       <c r="H62" s="28" t="s">
-        <v>241</v>
+        <v>136</v>
       </c>
       <c r="I62" s="21" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="63" spans="1:10" hidden="1">
+    <row r="63" spans="1:9">
       <c r="B63" s="43" t="s">
         <v>186</v>
       </c>
@@ -6108,13 +5871,13 @@
         <v>2</v>
       </c>
       <c r="H63" s="28" t="s">
-        <v>241</v>
+        <v>136</v>
       </c>
       <c r="I63" s="21" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="64" spans="1:10" hidden="1">
+    <row r="64" spans="1:9">
       <c r="B64" s="43" t="s">
         <v>186</v>
       </c>
@@ -6131,13 +5894,13 @@
         <v>1.5</v>
       </c>
       <c r="H64" s="28" t="s">
-        <v>241</v>
+        <v>136</v>
       </c>
       <c r="I64" s="21" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="65" spans="2:9" hidden="1">
+    <row r="65" spans="2:9">
       <c r="B65" s="43" t="s">
         <v>186</v>
       </c>
@@ -6154,7 +5917,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="66" spans="2:9" hidden="1">
+    <row r="66" spans="2:9">
       <c r="B66" s="43" t="s">
         <v>186</v>
       </c>
@@ -6171,13 +5934,13 @@
         <v>2</v>
       </c>
       <c r="H66" s="28" t="s">
-        <v>241</v>
+        <v>136</v>
       </c>
       <c r="I66" s="21" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="67" spans="2:9" hidden="1">
+    <row r="67" spans="2:9">
       <c r="B67" s="43" t="s">
         <v>186</v>
       </c>
@@ -6194,7 +5957,7 @@
         <v>2</v>
       </c>
       <c r="H67" s="28" t="s">
-        <v>241</v>
+        <v>136</v>
       </c>
       <c r="I67" s="21" t="s">
         <v>226</v>
@@ -6213,14 +5976,8 @@
       <c r="E68" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F68" s="28">
-        <v>1</v>
-      </c>
       <c r="H68" s="28" t="s">
         <v>136</v>
-      </c>
-      <c r="I68" s="21" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="69" spans="2:9">
@@ -6236,14 +5993,8 @@
       <c r="E69" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F69" s="28">
-        <v>1</v>
-      </c>
       <c r="H69" s="28" t="s">
         <v>136</v>
-      </c>
-      <c r="I69" s="21" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="70" spans="2:9">
@@ -6259,14 +6010,8 @@
       <c r="E70" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F70" s="28">
-        <v>1</v>
-      </c>
       <c r="H70" s="28" t="s">
         <v>136</v>
-      </c>
-      <c r="I70" s="21" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="71" spans="2:9">
@@ -6282,17 +6027,11 @@
       <c r="E71" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F71" s="28">
-        <v>1</v>
-      </c>
       <c r="H71" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="I71" s="21" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="72" spans="2:9">
+    </row>
+    <row r="72" spans="2:9" ht="18.75">
       <c r="B72" s="44" t="s">
         <v>195</v>
       </c>
@@ -6305,14 +6044,8 @@
       <c r="E72" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F72" s="28">
-        <v>1</v>
-      </c>
       <c r="H72" s="28" t="s">
         <v>136</v>
-      </c>
-      <c r="I72" s="21" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="73" spans="2:9">
@@ -6328,14 +6061,8 @@
       <c r="E73" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F73" s="28">
-        <v>0.5</v>
-      </c>
       <c r="H73" s="28" t="s">
         <v>136</v>
-      </c>
-      <c r="I73" s="21" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="74" spans="2:9">
@@ -6351,15 +6078,10 @@
       <c r="E74" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F74" s="28">
-        <v>0.5</v>
-      </c>
+      <c r="F74" s="21"/>
       <c r="G74" s="21"/>
       <c r="H74" s="28" t="s">
         <v>136</v>
-      </c>
-      <c r="I74" s="21" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="75" spans="2:9">
@@ -6375,15 +6097,10 @@
       <c r="E75" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F75" s="28">
-        <v>0.5</v>
-      </c>
+      <c r="F75" s="21"/>
       <c r="G75" s="21"/>
       <c r="H75" s="28" t="s">
         <v>136</v>
-      </c>
-      <c r="I75" s="21" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="76" spans="2:9">
@@ -6399,15 +6116,10 @@
       <c r="E76" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F76" s="28">
-        <v>0.5</v>
-      </c>
+      <c r="F76" s="21"/>
       <c r="G76" s="21"/>
       <c r="H76" s="28" t="s">
         <v>136</v>
-      </c>
-      <c r="I76" s="21" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="77" spans="2:9">
@@ -6423,24 +6135,12 @@
       <c r="E77" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F77" s="28">
-        <v>0.5</v>
-      </c>
       <c r="H77" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="I77" s="21" t="s">
-        <v>242</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:I77" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="アルファ"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A2:I77" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H77" xr:uid="{E1CFE88F-4F87-4696-BE21-1133C2AEB8C1}">
@@ -6461,7 +6161,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402AEDD2-674B-437A-B1BD-39BBE1464A75}">
   <dimension ref="B2:H10"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:8">
       <c r="B2" s="52" t="s">
@@ -6550,102 +6250,102 @@
       </c>
     </row>
     <row r="6" spans="2:8">
-      <c r="B6" s="53">
+      <c r="B6">
         <v>20</v>
       </c>
-      <c r="C6" s="53">
+      <c r="C6">
         <v>21</v>
       </c>
-      <c r="D6" s="53">
+      <c r="D6">
         <v>22</v>
       </c>
-      <c r="E6" s="53">
+      <c r="E6">
         <v>23</v>
       </c>
-      <c r="F6" s="53">
+      <c r="F6">
         <v>24</v>
       </c>
-      <c r="G6" s="53">
+      <c r="G6">
         <v>25</v>
       </c>
-      <c r="H6" s="53">
+      <c r="H6">
         <v>26</v>
       </c>
     </row>
     <row r="7" spans="2:8">
-      <c r="B7" s="53">
+      <c r="B7">
         <v>27</v>
       </c>
-      <c r="C7" s="53">
+      <c r="C7">
         <v>28</v>
       </c>
-      <c r="D7" s="53">
+      <c r="D7">
         <v>29</v>
       </c>
-      <c r="E7" s="53">
+      <c r="E7">
         <v>30</v>
       </c>
-      <c r="F7" s="54">
+      <c r="F7">
         <v>1</v>
       </c>
-      <c r="G7" s="54">
+      <c r="G7">
         <v>2</v>
       </c>
-      <c r="H7" s="54">
+      <c r="H7">
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="2:8">
-      <c r="B8" s="54">
+      <c r="B8">
         <v>4</v>
       </c>
-      <c r="C8" s="54">
+      <c r="C8">
         <v>5</v>
       </c>
-      <c r="D8" s="54">
+      <c r="D8">
         <v>6</v>
       </c>
-      <c r="E8" s="54">
+      <c r="E8">
         <v>7</v>
       </c>
-      <c r="F8" s="54">
+      <c r="F8">
         <v>8</v>
       </c>
-      <c r="G8" s="54">
-        <v>9</v>
-      </c>
-      <c r="H8" s="54">
+      <c r="G8">
+        <v>9</v>
+      </c>
+      <c r="H8">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="2:8">
-      <c r="B9" s="54">
+      <c r="B9">
         <v>11</v>
       </c>
-      <c r="C9" s="54">
+      <c r="C9">
         <v>12</v>
       </c>
-      <c r="D9" s="54">
+      <c r="D9">
         <v>13</v>
       </c>
-      <c r="E9" s="54">
+      <c r="E9">
         <v>14</v>
       </c>
-      <c r="F9" s="54">
+      <c r="F9">
         <v>15</v>
       </c>
-      <c r="G9" s="55">
+      <c r="G9">
         <v>16</v>
       </c>
-      <c r="H9" s="55">
+      <c r="H9">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="2:8">
-      <c r="B10" s="56">
-        <v>18</v>
-      </c>
-      <c r="C10" s="57">
+      <c r="B10">
+        <v>18</v>
+      </c>
+      <c r="C10">
         <v>19</v>
       </c>
     </row>
